--- a/data/OLS_all.xlsx
+++ b/data/OLS_all.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,162 +441,162 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>565</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>871</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>605</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>712</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>410</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>725</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>871</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>584</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>470</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>494</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>771</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>426</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>428</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>214</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>470</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>541</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>678</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>584</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>712</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>799</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>625</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>337</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>541</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>494</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>657</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>342</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>410</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>678</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>605</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>565</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>426</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>334</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>549</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>771</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>229</t>
         </is>
       </c>
     </row>
@@ -613,100 +613,100 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
+        <v>0.1723395088323998</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.6247307195174493</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.1938819474364498</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
         <v>0.4523912106850495</v>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.2154243860404998</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
         <v>0.2800517018526497</v>
       </c>
-      <c r="K2" t="n">
-        <v>0.1938819474364498</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0.6247307195174493</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0.1723395088323998</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="n">
         <v>0.02154243860404998</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0.2154243860404998</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -722,94 +722,94 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
+        <v>0.2466325175488522</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.834756213242269</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.1138303927148549</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
         <v>0.3035477139062797</v>
       </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.01897173211914248</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.3035477139062797</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
         <v>1.233162587744261</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.1138303927148549</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.01897173211914248</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0.834756213242269</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0.2466325175488522</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0.3035477139062797</v>
       </c>
       <c r="AH3" t="n">
         <v>0</v>
@@ -831,79 +831,79 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
+        <v>1.485391603240855</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.7979376381045912</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.01227596366314756</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.2332433095998036</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.01227596366314756</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>3.584581389639087</v>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.02455192732629511</v>
+      </c>
+      <c r="S4" t="n">
         <v>0.07365578197888534</v>
       </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.01227596366314756</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.01227596366314756</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
         <v>0.3068990915786889</v>
       </c>
-      <c r="K4" t="n">
-        <v>0.2332433095998036</v>
-      </c>
-      <c r="L4" t="n">
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
         <v>0.01227596366314756</v>
       </c>
-      <c r="M4" t="n">
-        <v>0.01227596366314756</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.01227596366314756</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.01227596366314756</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0.01227596366314756</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0.7979376381045912</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.485391603240855</v>
-      </c>
       <c r="AB4" t="n">
-        <v>0.02455192732629511</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -940,100 +940,100 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
+        <v>4.400907948960928</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.439055027877559</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.1410406152896842</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
         <v>2.053903960156026</v>
       </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
         <v>0.002203759613901316</v>
       </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.006611278841703947</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.002203759613901316</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.01542631729730921</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.2291909998457368</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.02203759613901316</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.004407519227802631</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
         <v>2.201555854287414</v>
       </c>
-      <c r="K5" t="n">
-        <v>0.1410406152896842</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.01542631729730921</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.004407519227802631</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.02203759613901316</v>
-      </c>
-      <c r="U5" t="n">
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
         <v>0.002203759613901316</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.439055027877559</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>4.400907948960928</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0.006611278841703947</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0.002203759613901316</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0.2291909998457368</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1049,59 +1049,59 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.740106755015645</v>
+        <v>1.073071967605375</v>
       </c>
       <c r="E6" t="n">
         <v>0.00184060371801951</v>
       </c>
       <c r="F6" t="n">
+        <v>1.006810233756672</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.2043070127001657</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.01288422602613657</v>
+      </c>
+      <c r="K6" t="n">
         <v>0.003681207436039021</v>
       </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
+      <c r="L6" t="n">
         <v>0.00184060371801951</v>
       </c>
-      <c r="I6" t="n">
+      <c r="M6" t="n">
+        <v>3.740106755015645</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.00184060371801951</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.007362414872078041</v>
+      </c>
+      <c r="S6" t="n">
         <v>0.003681207436039021</v>
       </c>
-      <c r="J6" t="n">
-        <v>0.9147800478556966</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.2043070127001657</v>
-      </c>
-      <c r="L6" t="n">
+      <c r="T6" t="n">
+        <v>0.00184060371801951</v>
+      </c>
+      <c r="U6" t="n">
         <v>0.03313086692435119</v>
       </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0.00184060371801951</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.01288422602613657</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
@@ -1109,40 +1109,40 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.00184060371801951</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.007362414872078041</v>
+        <v>0.3349898766795509</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.006810233756672</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.073071967605375</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
         <v>0.007362414872078041</v>
       </c>
       <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
         <v>0.00184060371801951</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.9147800478556966</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.00184060371801951</v>
+      </c>
+      <c r="AI6" t="n">
         <v>0.003681207436039021</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0.3349898766795509</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0.00184060371801951</v>
       </c>
     </row>
     <row r="7">
@@ -1267,100 +1267,100 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
+        <v>0.3904450103067782</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.4995756032496665</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.2182611858857766</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.009700497150478962</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.00242512428761974</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>0.4680489875106099</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
         <v>0.004850248575239481</v>
       </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.007275372862859222</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.2012853158724384</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
         <v>0.00242512428761974</v>
       </c>
-      <c r="J8" t="n">
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
         <v>0.2303868073238753</v>
       </c>
-      <c r="K8" t="n">
-        <v>0.2182611858857766</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.007275372862859222</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.009700497150478962</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0.00242512428761974</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0.4995756032496665</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0.3904450103067782</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
         <v>0.01455074572571844</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0.2012853158724384</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1485,94 +1485,94 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3989520066690485</v>
+        <v>0.3751339764201501</v>
       </c>
       <c r="E10" t="n">
         <v>0.002977253781112302</v>
       </c>
       <c r="F10" t="n">
+        <v>1.155174467071573</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.2768846016434441</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.005954507562224604</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.3989520066690485</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.005954507562224604</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.008931761343336906</v>
+      </c>
+      <c r="S10" t="n">
         <v>0.01488626890556151</v>
       </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
         <v>0.005954507562224604</v>
       </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.002977253781112302</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.4138382755746099</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.06549958318447065</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
         <v>0.2590210789567703</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.2768846016434441</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.005954507562224604</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0.002977253781112302</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.005954507562224604</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0.06549958318447065</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.155174467071573</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0.3751339764201501</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0.008931761343336906</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0.4138382755746099</v>
       </c>
       <c r="AH10" t="n">
         <v>0</v>
@@ -1606,7 +1606,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1615,7 +1615,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1657,16 +1657,16 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
         <v>0.57</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1712,7 +1712,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.920951650038373</v>
+        <v>0.1534919416730622</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1721,7 +1721,7 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.05116398055768739</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1736,7 +1736,7 @@
         <v>0.07674597083653108</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1534919416730622</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -1757,7 +1757,7 @@
         <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.920951650038373</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
@@ -1775,7 +1775,7 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>0.0255819902788437</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1790,13 +1790,13 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.0255819902788437</v>
+        <v>0.05116398055768739</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>11.97237145049885</v>
       </c>
       <c r="AI12" t="n">
-        <v>11.97237145049885</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1812,7 +1812,7 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>0.007745533409067438</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0.06712795621191779</v>
@@ -1821,16 +1821,16 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3020758029536301</v>
+        <v>0.002581844469689146</v>
       </c>
       <c r="H13" t="n">
-        <v>0.02323660022720231</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0.002581844469689146</v>
+        <v>0.005163688939378292</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1839,73 +1839,73 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>0.007745533409067438</v>
       </c>
       <c r="N13" t="n">
         <v>0.1187648456057007</v>
       </c>
       <c r="O13" t="n">
+        <v>0.02323660022720231</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.3020758029536301</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.02581844469689146</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.1962201796963751</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.005163688939378292</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.01807291128782402</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
         <v>0.002581844469689146</v>
       </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0.01807291128782402</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0.005163688939378292</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0.005163688939378292</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0.02581844469689146</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0.1962201796963751</v>
-      </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>0.1394196013632139</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.1394196013632139</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6947201270345376</v>
+        <v>0.01984914648670107</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6550218340611353</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0.03969829297340214</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1954,47 +1954,47 @@
         <v>0.05954743946010321</v>
       </c>
       <c r="O14" t="n">
+        <v>0.6550218340611353</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.6947201270345376</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.03969829297340214</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.1984914648670107</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
         <v>0.01984914648670107</v>
       </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0.01984914648670107</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0</v>
-      </c>
       <c r="AC14" t="n">
         <v>0</v>
       </c>
@@ -2002,19 +2002,19 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
         <v>0.03969829297340214</v>
       </c>
-      <c r="AF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0.1984914648670107</v>
-      </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>0.8535132989281461</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.8535132989281461</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -2039,16 +2039,16 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>13.50579539727868</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.03359650596337981</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1847807827985889</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -2063,7 +2063,7 @@
         <v>0.05039475894506971</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>0.03359650596337981</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -2084,13 +2084,13 @@
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>13.50579539727868</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>0.520745842432387</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
@@ -2111,19 +2111,19 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.520745842432387</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>0.1847807827985889</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>4.905089870653452</v>
       </c>
       <c r="AI15" t="n">
-        <v>4.905089870653452</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -2148,16 +2148,16 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>3.651496199364957</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.04810930433945925</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>0.00962186086789185</v>
       </c>
       <c r="J16" t="n">
-        <v>0.00962186086789185</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -2172,7 +2172,7 @@
         <v>2.362166843067449</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>0.04810930433945925</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -2193,26 +2193,26 @@
         <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>3.651496199364957</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.0577311652073511</v>
       </c>
       <c r="Y16" t="n">
+        <v>0.02405465216972963</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
         <v>0.03367651303762147</v>
       </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
       <c r="AC16" t="n">
         <v>0</v>
       </c>
@@ -2220,19 +2220,19 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.0577311652073511</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
         <v>0.00962186086789185</v>
       </c>
-      <c r="AG16" t="n">
-        <v>0.02405465216972963</v>
-      </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>2.732608486481285</v>
       </c>
       <c r="AI16" t="n">
-        <v>2.732608486481285</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2257,16 +2257,16 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9429813846680022</v>
+        <v>0.01465774173059071</v>
       </c>
       <c r="H17" t="n">
-        <v>0.01710069868568916</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>0.01465774173059071</v>
       </c>
       <c r="J17" t="n">
-        <v>0.01221478477549226</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -2281,7 +2281,7 @@
         <v>0.08550349342844579</v>
       </c>
       <c r="O17" t="n">
-        <v>0.01465774173059071</v>
+        <v>0.01710069868568916</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -2302,26 +2302,26 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.9429813846680022</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.06595983778765818</v>
       </c>
       <c r="Y17" t="n">
+        <v>0.06107392387746129</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
         <v>0.002442956955098451</v>
       </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
       <c r="AC17" t="n">
         <v>0</v>
       </c>
@@ -2329,19 +2329,19 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.06595983778765818</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.01465774173059071</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.06107392387746129</v>
+        <v>0.01221478477549226</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>0.9258806859823131</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.9258806859823131</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2366,7 +2366,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>1.058761249338274</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -2411,7 +2411,7 @@
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.058761249338274</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
@@ -2447,10 +2447,10 @@
         <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>0.9528851244044468</v>
       </c>
       <c r="AI18" t="n">
-        <v>0.9528851244044468</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2466,100 +2466,100 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
+        <v>0.2642506606266515</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.006669183339625</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.849754624386561</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.06291682395872657</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
         <v>0.1761671070844344</v>
       </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>2.705423430225242</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.01258336479174531</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0.01258336479174531</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0.01258336479174531</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
         <v>0.1510003775009437</v>
       </c>
-      <c r="K19" t="n">
-        <v>1.849754624386561</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
         <v>0.01258336479174531</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0.06291682395872657</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0.01258336479174531</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0.01258336479174531</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.006669183339625</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0.2642506606266515</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0.01258336479174531</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.705423430225242</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2665,10 +2665,10 @@
         <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>0.002897899747158247</v>
       </c>
       <c r="AI20" t="n">
-        <v>0.002897899747158247</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2696,7 +2696,7 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>0.01444669170759896</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2705,7 +2705,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0.01444669170759896</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2799,91 +2799,91 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.1494957484674708</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.002372948388372553</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.002372948388372553</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.4018192604310856</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
         <v>0.01186474194186276</v>
       </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0.2950365829543207</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
         <v>0.002372948388372553</v>
       </c>
-      <c r="I22" t="n">
-        <v>0.1494957484674708</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0.002372948388372553</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0.2950365829543207</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0.002372948388372553</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>0</v>
-      </c>
       <c r="AG22" t="n">
         <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>0.4018192604310856</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -2911,16 +2911,16 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>1.371539285168001</v>
+        <v>0.0101973181053383</v>
       </c>
       <c r="H23" t="n">
-        <v>0.02804262478968031</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>0.01529597715800744</v>
       </c>
       <c r="J23" t="n">
-        <v>0.005098659052669148</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2935,7 +2935,7 @@
         <v>0.1325651353693978</v>
       </c>
       <c r="O23" t="n">
-        <v>0.0101973181053383</v>
+        <v>0.02804262478968031</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
@@ -2956,26 +2956,26 @@
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.371539285168001</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>0.03314128384234946</v>
       </c>
       <c r="Y23" t="n">
+        <v>0.06118390863202978</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
         <v>0.1223678172640596</v>
       </c>
-      <c r="Z23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>0</v>
-      </c>
       <c r="AC23" t="n">
         <v>0</v>
       </c>
@@ -2983,19 +2983,19 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.03314128384234946</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.01529597715800744</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.06118390863202978</v>
+        <v>0.005098659052669148</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>0.8999133227961047</v>
       </c>
       <c r="AI23" t="n">
-        <v>0.8999133227961047</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -3020,16 +3020,16 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>3.251439819202449</v>
+        <v>0.0121503730164516</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0461714174625161</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0.009720298413161283</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -3044,7 +3044,7 @@
         <v>0.05346164127238706</v>
       </c>
       <c r="O24" t="n">
-        <v>0.0121503730164516</v>
+        <v>0.0461714174625161</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
@@ -3065,26 +3065,26 @@
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>3.251439819202449</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>0.06561201428883867</v>
       </c>
       <c r="Y24" t="n">
+        <v>0.3669412650968384</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
         <v>0.01944059682632257</v>
       </c>
-      <c r="Z24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>0</v>
-      </c>
       <c r="AC24" t="n">
         <v>0</v>
       </c>
@@ -3092,19 +3092,19 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>0.06561201428883867</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.3669412650968384</v>
+        <v>0.009720298413161283</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>2.605039974727224</v>
       </c>
       <c r="AI24" t="n">
-        <v>2.605039974727224</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -3120,7 +3120,7 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>0.004966229638458482</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -3129,91 +3129,91 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.09435836313071116</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
         <v>0.009932459276916964</v>
       </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
         <v>0.004966229638458482</v>
       </c>
-      <c r="K25" t="n">
-        <v>0.09435836313071116</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
         <v>0.004966229638458482</v>
       </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA25" t="n">
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
         <v>0.004966229638458482</v>
       </c>
-      <c r="AB25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD25" t="n">
+      <c r="AH25" t="n">
+        <v>0.124155740961462</v>
+      </c>
+      <c r="AI25" t="n">
         <v>0.009932459276916964</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>0.004966229638458482</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>0.124155740961462</v>
       </c>
     </row>
     <row r="26">
@@ -3229,100 +3229,100 @@
         <v>2</v>
       </c>
       <c r="D26" t="n">
-        <v>0.002874885004599816</v>
+        <v>0.005749770009199632</v>
       </c>
       <c r="E26" t="n">
         <v>0.2932382704691812</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>0.327736890524379</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>1.138454461821527</v>
       </c>
       <c r="H26" t="n">
+        <v>0.8107175712971482</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.02874885004599816</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.02299908003679853</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.002874885004599816</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
         <v>0.005749770009199632</v>
       </c>
-      <c r="I26" t="n">
-        <v>0.02299908003679853</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0.8107175712971482</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.04024839006439743</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.03737350505979761</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
         <v>0.008624655013799448</v>
       </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1.138454461821527</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0.03737350505979761</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0.8825896964121436</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0.06324747010119594</v>
+      </c>
+      <c r="AC26" t="n">
         <v>0.4312327506899724</v>
       </c>
-      <c r="S26" t="n">
-        <v>0.02874885004599816</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>0.06324747010119594</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>0.327736890524379</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>0.005749770009199632</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>0.04024839006439743</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>0</v>
-      </c>
       <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0.002874885004599816</v>
+      </c>
+      <c r="AI26" t="n">
         <v>0.0718721251149954</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>0.8825896964121436</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>0.002874885004599816</v>
       </c>
     </row>
     <row r="27">
@@ -3377,58 +3377,58 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
+        <v>0.3166978965981368</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0.3998310944551476</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0.00395872370747671</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
         <v>0.001319574569158903</v>
       </c>
-      <c r="R27" t="n">
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
         <v>0.001319574569158903</v>
       </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0.00395872370747671</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>0</v>
-      </c>
       <c r="AG27" t="n">
-        <v>0.3998310944551476</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>0.3166978965981368</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3556,100 +3556,100 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>0.007825644637477012</v>
+        <v>0.01173846695621552</v>
       </c>
       <c r="E29" t="n">
         <v>0.4069335211488046</v>
       </c>
       <c r="F29" t="n">
+        <v>0.1486872481120632</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.475134014164417</v>
+      </c>
+      <c r="H29" t="n">
+        <v>5.157099816097351</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.1095590249246782</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.4030206988300661</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.007825644637477012</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.01173846695621552</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.1056462026059397</v>
+      </c>
+      <c r="S29" t="n">
         <v>0.05477951246233909</v>
       </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
+      <c r="T29" t="n">
+        <v>0.03521540086864655</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0.003912822318738506</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0.03130257854990805</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>7.160464843291465</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.498610948076848</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0.4617130336111437</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
         <v>0.01173846695621552</v>
       </c>
-      <c r="I29" t="n">
-        <v>0.4030206988300661</v>
-      </c>
-      <c r="J29" t="n">
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
         <v>0.03912822318738506</v>
       </c>
-      <c r="K29" t="n">
-        <v>5.157099816097351</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0.003912822318738506</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0.03130257854990805</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>1.475134014164417</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0.03521540086864655</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0.4617130336111437</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0.1095590249246782</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0.01173846695621552</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.498610948076848</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>0.1486872481120632</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0.01173846695621552</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0.1056462026059397</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD29" t="n">
+      <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="n">
         <v>1.737293109519897</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>7.160464843291465</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -3665,7 +3665,7 @@
         <v>3</v>
       </c>
       <c r="D30" t="n">
-        <v>0.01919017463058914</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
         <v>0.05757052389176742</v>
@@ -3674,7 +3674,7 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.1151410477835348</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -3683,7 +3683,7 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0.1151410477835348</v>
+        <v>0.01919017463058914</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -3692,7 +3692,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>0.01919017463058914</v>
       </c>
       <c r="N30" t="n">
         <v>1.823066589905968</v>
@@ -3710,7 +3710,7 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0.01919017463058914</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
         <v>0</v>
@@ -3719,16 +3719,16 @@
         <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>0.1151410477835348</v>
       </c>
       <c r="W30" t="n">
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>0.268662444828248</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>0.134331222414124</v>
       </c>
       <c r="Z30" t="n">
         <v>0</v>
@@ -3746,19 +3746,19 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.268662444828248</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
         <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.134331222414124</v>
+        <v>0.1151410477835348</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>0.5757052389176741</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.5757052389176741</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -3774,7 +3774,7 @@
         <v>2</v>
       </c>
       <c r="D31" t="n">
-        <v>0.004483098717833767</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
         <v>0.0403478884605039</v>
@@ -3783,10 +3783,10 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.192773244866852</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.01793239487133507</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -3801,13 +3801,13 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>0.004483098717833767</v>
       </c>
       <c r="N31" t="n">
         <v>0.1613915538420156</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>0.01793239487133507</v>
       </c>
       <c r="P31" t="n">
         <v>0</v>
@@ -3816,58 +3816,58 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0.192773244866852</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
         <v>0.008966197435667534</v>
       </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0</v>
-      </c>
       <c r="Y31" t="n">
+        <v>0.6276338204967273</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
         <v>0.008966197435667534</v>
       </c>
-      <c r="Z31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0</v>
-      </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>0.008966197435667534</v>
       </c>
       <c r="AD31" t="n">
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.008966197435667534</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
         <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.6276338204967273</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>0.1748408499955169</v>
       </c>
       <c r="AI31" t="n">
-        <v>0.1748408499955169</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -3992,7 +3992,7 @@
         <v>3</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>0.03951007506914263</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -4004,88 +4004,88 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
+        <v>0.1481627815092849</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
         <v>0.09877518767285659</v>
       </c>
-      <c r="I33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" t="n">
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0.009877518767285657</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0.01975503753457131</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0.0493875938364283</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.009877518767285657</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
         <v>0.02963255630185697</v>
       </c>
-      <c r="K33" t="n">
-        <v>0.1481627815092849</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0.01975503753457131</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" t="n">
-        <v>0</v>
-      </c>
-      <c r="X33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>0.03951007506914263</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>0.009877518767285657</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>0.009877518767285657</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>0.0493875938364283</v>
-      </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>0.0691426313709996</v>
       </c>
       <c r="AI33" t="n">
-        <v>0.0691426313709996</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -4101,7 +4101,7 @@
         <v>2</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>0.9750812567713976</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -4113,29 +4113,29 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
+        <v>0.5958829902491874</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
         <v>0.1625135427952329</v>
       </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0.5958829902491874</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
       <c r="P34" t="n">
         <v>0</v>
       </c>
@@ -4164,13 +4164,13 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>0.6771397616468039</v>
       </c>
       <c r="Z34" t="n">
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.9750812567713976</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
         <v>0</v>
@@ -4188,7 +4188,7 @@
         <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.6771397616468039</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
         <v>0</v>
@@ -4300,10 +4300,10 @@
         <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="AI35" t="n">
-        <v>0.55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -4319,7 +4319,7 @@
         <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>0.2098559953686953</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -4340,20 +4340,20 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
         <v>0.01447282726680657</v>
       </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
       <c r="P36" t="n">
         <v>0</v>
       </c>
@@ -4361,41 +4361,41 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.432809899413851</v>
+      </c>
+      <c r="Z36" t="n">
         <v>0.003618206816701643</v>
       </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" t="n">
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>3.097185035096606</v>
+      </c>
+      <c r="AC36" t="n">
         <v>0.003618206816701643</v>
       </c>
-      <c r="X36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>3.097185035096606</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>0.2098559953686953</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>0</v>
-      </c>
       <c r="AD36" t="n">
         <v>0</v>
       </c>
@@ -4406,7 +4406,7 @@
         <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.432809899413851</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
         <v>0</v>
@@ -4428,7 +4428,7 @@
         <v>2</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>0.06917501278233933</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -4440,88 +4440,88 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
+        <v>0.2917380973863876</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.006015218502812114</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
         <v>0.1323348070618665</v>
       </c>
-      <c r="I37" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0.2917380973863876</v>
-      </c>
-      <c r="L37" t="n">
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
         <v>0.006015218502812114</v>
       </c>
-      <c r="M37" t="n">
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0.006015218502812114</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
         <v>0.003007609251406057</v>
       </c>
-      <c r="N37" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0.006015218502812114</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" t="n">
-        <v>0</v>
-      </c>
-      <c r="W37" t="n">
-        <v>0</v>
-      </c>
       <c r="X37" t="n">
         <v>0</v>
       </c>
       <c r="Y37" t="n">
+        <v>0.8631838551535385</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="n">
         <v>0.0210532647598424</v>
       </c>
-      <c r="Z37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>0.06917501278233933</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>0.006015218502812114</v>
-      </c>
       <c r="AC37" t="n">
         <v>0</v>
       </c>
       <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="n">
         <v>0.03007609251406057</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>0.8631838551535385</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -4537,7 +4537,7 @@
         <v>2</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>0.04240328788570683</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -4549,88 +4549,88 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
+        <v>0.1908147954856807</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
         <v>0.08154478439559006</v>
       </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" t="n">
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
         <v>0.009785374127470806</v>
       </c>
-      <c r="K38" t="n">
-        <v>0.1908147954856807</v>
-      </c>
-      <c r="L38" t="n">
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
         <v>0.006523582751647205</v>
       </c>
-      <c r="M38" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" t="n">
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0.06686672320438386</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0.004892687063735403</v>
+      </c>
+      <c r="AC38" t="n">
         <v>0.008154478439559005</v>
       </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" t="n">
-        <v>0</v>
-      </c>
-      <c r="W38" t="n">
-        <v>0</v>
-      </c>
-      <c r="X38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>0.004892687063735403</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>0.04240328788570683</v>
-      </c>
-      <c r="AB38" t="n">
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="n">
         <v>0.009785374127470806</v>
       </c>
-      <c r="AC38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD38" t="n">
+      <c r="AH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="n">
         <v>0.001630895687911801</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>0.06686672320438386</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -4655,7 +4655,7 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0.5632897836795887</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -4700,7 +4700,7 @@
         <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>0.5632897836795887</v>
       </c>
       <c r="W39" t="n">
         <v>0</v>
@@ -4736,10 +4736,10 @@
         <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>0.04926108374384236</v>
       </c>
       <c r="AI39" t="n">
-        <v>0.04926108374384236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -4764,7 +4764,7 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0.07744339976524969</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -4809,7 +4809,7 @@
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>0.07744339976524969</v>
       </c>
       <c r="W40" t="n">
         <v>0</v>
@@ -4845,10 +4845,10 @@
         <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>0.1899783400491282</v>
       </c>
       <c r="AI40" t="n">
-        <v>0.1899783400491282</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -4985,7 +4985,7 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>0.007502719735904265</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -4994,7 +4994,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0.007502719735904265</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -5036,16 +5036,16 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB42" t="n">
         <v>0.003751359867952133</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5082,7 +5082,7 @@
         <v>2</v>
       </c>
       <c r="D43" t="n">
-        <v>0.04199916001679967</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
         <v>0.1679966400671987</v>
@@ -5091,7 +5091,7 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>4.262914741705166</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -5109,7 +5109,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>0.04199916001679967</v>
       </c>
       <c r="N43" t="n">
         <v>0.2099958000839983</v>
@@ -5136,7 +5136,7 @@
         <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>4.262914741705166</v>
       </c>
       <c r="W43" t="n">
         <v>0</v>
@@ -5145,17 +5145,17 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
+        <v>0.1679966400671987</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB43" t="n">
         <v>0.02099958000839983</v>
       </c>
-      <c r="Z43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>0</v>
-      </c>
       <c r="AC43" t="n">
         <v>0</v>
       </c>
@@ -5169,13 +5169,13 @@
         <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.1679966400671987</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.007979840403192</v>
       </c>
       <c r="AI43" t="n">
-        <v>1.007979840403192</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -5200,53 +5200,53 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="n">
         <v>0.04927079227433977</v>
       </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
-      <c r="R44" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" t="n">
-        <v>0</v>
-      </c>
-      <c r="U44" t="n">
-        <v>0</v>
-      </c>
-      <c r="V44" t="n">
-        <v>0</v>
-      </c>
       <c r="W44" t="n">
         <v>0</v>
       </c>
@@ -5281,10 +5281,10 @@
         <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>0.1675206937327552</v>
       </c>
       <c r="AI44" t="n">
-        <v>0.1675206937327552</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -5309,52 +5309,52 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" t="n">
         <v>4.41</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" t="n">
-        <v>0</v>
-      </c>
-      <c r="T45" t="n">
-        <v>0</v>
-      </c>
-      <c r="U45" t="n">
-        <v>0</v>
-      </c>
-      <c r="V45" t="n">
-        <v>0</v>
       </c>
       <c r="W45" t="n">
         <v>0</v>
@@ -5421,82 +5421,82 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>0.001347581764523563</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
       <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0.001347581764523563</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="n">
         <v>0.03638470764213619</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0.001347581764523563</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" t="n">
-        <v>0</v>
-      </c>
-      <c r="U46" t="n">
-        <v>0</v>
-      </c>
-      <c r="V46" t="n">
-        <v>0</v>
-      </c>
-      <c r="W46" t="n">
-        <v>0</v>
-      </c>
-      <c r="X46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>0.001347581764523563</v>
       </c>
       <c r="AH46" t="n">
         <v>0</v>
@@ -5581,16 +5581,16 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB47" t="n">
         <v>0.004311273981461522</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -5636,16 +5636,16 @@
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>0.09745037985760312</v>
+        <v>0.003977566524800128</v>
       </c>
       <c r="H48" t="n">
-        <v>0.005966349787200191</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>0.005966349787200191</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -5660,7 +5660,7 @@
         <v>0.5568593134720178</v>
       </c>
       <c r="O48" t="n">
-        <v>0.003977566524800128</v>
+        <v>0.005966349787200191</v>
       </c>
       <c r="P48" t="n">
         <v>0</v>
@@ -5669,58 +5669,58 @@
         <v>0</v>
       </c>
       <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0.09745037985760312</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" t="n">
+        <v>0.01193269957440038</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>0.04773079829760152</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC48" t="n">
         <v>0.001988783262400064</v>
       </c>
-      <c r="S48" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" t="n">
-        <v>0</v>
-      </c>
-      <c r="U48" t="n">
-        <v>0</v>
-      </c>
-      <c r="V48" t="n">
-        <v>0</v>
-      </c>
-      <c r="W48" t="n">
-        <v>0</v>
-      </c>
-      <c r="X48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>0</v>
-      </c>
       <c r="AD48" t="n">
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>0.01193269957440038</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
         <v>0</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.04773079829760152</v>
+        <v>0.005966349787200191</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>1.25293345531204</v>
       </c>
       <c r="AI48" t="n">
-        <v>1.25293345531204</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -5745,53 +5745,53 @@
         <v>0</v>
       </c>
       <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" t="n">
         <v>0.1264400112391121</v>
       </c>
-      <c r="H49" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
-      <c r="R49" t="n">
-        <v>0</v>
-      </c>
-      <c r="S49" t="n">
-        <v>0</v>
-      </c>
-      <c r="T49" t="n">
-        <v>0</v>
-      </c>
-      <c r="U49" t="n">
-        <v>0</v>
-      </c>
-      <c r="V49" t="n">
-        <v>0</v>
-      </c>
       <c r="W49" t="n">
         <v>0</v>
       </c>
@@ -5826,10 +5826,10 @@
         <v>0</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>0.01404889013767912</v>
       </c>
       <c r="AI49" t="n">
-        <v>0.01404889013767912</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -5854,52 +5854,52 @@
         <v>0</v>
       </c>
       <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" t="n">
         <v>5.7</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" t="n">
-        <v>0</v>
-      </c>
-      <c r="U50" t="n">
-        <v>0</v>
-      </c>
-      <c r="V50" t="n">
-        <v>0</v>
       </c>
       <c r="W50" t="n">
         <v>0</v>
@@ -5972,7 +5972,7 @@
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>0.04099598670866957</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
@@ -5999,7 +5999,7 @@
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>0.04099598670866957</v>
+        <v>0</v>
       </c>
       <c r="T51" t="n">
         <v>0</v>
@@ -6063,7 +6063,7 @@
         <v>2</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>0.005456331162926049</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
@@ -6117,34 +6117,34 @@
         <v>0</v>
       </c>
       <c r="V52" t="n">
+        <v>0</v>
+      </c>
+      <c r="W52" t="n">
+        <v>0</v>
+      </c>
+      <c r="X52" t="n">
+        <v>0.003637554108617366</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="n">
         <v>0.01273143938016078</v>
-      </c>
-      <c r="W52" t="n">
-        <v>0</v>
-      </c>
-      <c r="X52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>0.005456331162926049</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE52" t="n">
-        <v>0.003637554108617366</v>
       </c>
       <c r="AF52" t="n">
         <v>0</v>
@@ -6178,13 +6178,13 @@
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>0.0007963178263708611</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>0.0007963178263708611</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
@@ -6193,62 +6193,62 @@
         <v>0</v>
       </c>
       <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="n">
         <v>0.0007963178263708611</v>
       </c>
-      <c r="L53" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" t="n">
+        <v>0</v>
+      </c>
+      <c r="W53" t="n">
+        <v>0</v>
+      </c>
+      <c r="X53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>0.001194476739556292</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC53" t="n">
         <v>0.0003981589131854306</v>
       </c>
-      <c r="S53" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" t="n">
-        <v>0</v>
-      </c>
-      <c r="U53" t="n">
-        <v>0</v>
-      </c>
-      <c r="V53" t="n">
-        <v>0</v>
-      </c>
-      <c r="W53" t="n">
-        <v>0</v>
-      </c>
-      <c r="X53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>0.0007963178263708611</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>0</v>
-      </c>
       <c r="AD53" t="n">
         <v>0</v>
       </c>
@@ -6259,10 +6259,10 @@
         <v>0</v>
       </c>
       <c r="AG53" t="n">
-        <v>0.001194476739556292</v>
+        <v>0</v>
       </c>
       <c r="AH53" t="n">
-        <v>0.0007963178263708611</v>
+        <v>0</v>
       </c>
       <c r="AI53" t="n">
         <v>0</v>
@@ -6299,76 +6299,76 @@
         <v>0</v>
       </c>
       <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" t="n">
+        <v>0</v>
+      </c>
+      <c r="W54" t="n">
+        <v>0</v>
+      </c>
+      <c r="X54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="n">
         <v>0.264812975835816</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" t="n">
-        <v>0</v>
-      </c>
-      <c r="S54" t="n">
-        <v>0</v>
-      </c>
-      <c r="T54" t="n">
-        <v>0</v>
-      </c>
-      <c r="U54" t="n">
-        <v>0</v>
-      </c>
-      <c r="V54" t="n">
-        <v>0</v>
-      </c>
-      <c r="W54" t="n">
-        <v>0</v>
-      </c>
-      <c r="X54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG54" t="n">
-        <v>0</v>
       </c>
       <c r="AH54" t="n">
         <v>0</v>
@@ -6402,7 +6402,7 @@
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>0.001908396946564886</v>
       </c>
       <c r="I55" t="n">
         <v>0</v>
@@ -6411,7 +6411,7 @@
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>0.001908396946564886</v>
+        <v>0</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
@@ -6480,10 +6480,10 @@
         <v>0</v>
       </c>
       <c r="AH55" t="n">
-        <v>0</v>
+        <v>0.005725190839694656</v>
       </c>
       <c r="AI55" t="n">
-        <v>0.005725190839694656</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -6511,7 +6511,7 @@
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>0.01744652639659444</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
@@ -6520,7 +6520,7 @@
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>0.01744652639659444</v>
+        <v>0</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -6589,10 +6589,10 @@
         <v>0</v>
       </c>
       <c r="AH56" t="n">
-        <v>0</v>
+        <v>0.003489305279318887</v>
       </c>
       <c r="AI56" t="n">
-        <v>0.003489305279318887</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -6608,7 +6608,7 @@
         <v>3</v>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
+        <v>0.03110602952550695</v>
       </c>
       <c r="E57" t="n">
         <v>0</v>
@@ -6626,82 +6626,82 @@
         <v>0</v>
       </c>
       <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" t="n">
+        <v>0</v>
+      </c>
+      <c r="W57" t="n">
+        <v>0</v>
+      </c>
+      <c r="X57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>0.1723442176413222</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>0.9390658102700339</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="n">
         <v>0.09247738507583145</v>
       </c>
-      <c r="K57" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
-      <c r="R57" t="n">
-        <v>0.9390658102700339</v>
-      </c>
-      <c r="S57" t="n">
-        <v>0</v>
-      </c>
-      <c r="T57" t="n">
-        <v>0</v>
-      </c>
-      <c r="U57" t="n">
-        <v>0</v>
-      </c>
-      <c r="V57" t="n">
-        <v>0</v>
-      </c>
-      <c r="W57" t="n">
-        <v>0</v>
-      </c>
-      <c r="X57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>0.03110602952550695</v>
-      </c>
-      <c r="AB57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG57" t="n">
-        <v>0.1723442176413222</v>
-      </c>
       <c r="AH57" t="n">
-        <v>0</v>
+        <v>0.01849547701516629</v>
       </c>
       <c r="AI57" t="n">
-        <v>0.01849547701516629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -6717,7 +6717,7 @@
         <v>1</v>
       </c>
       <c r="D58" t="n">
-        <v>0.01542020046260601</v>
+        <v>0</v>
       </c>
       <c r="E58" t="n">
         <v>0.01542020046260601</v>
@@ -6726,16 +6726,16 @@
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>0.06168080185042405</v>
+        <v>0.01542020046260601</v>
       </c>
       <c r="H58" t="n">
-        <v>0.07710100231303006</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>0.04626060138781804</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
@@ -6744,43 +6744,43 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>0.01542020046260601</v>
       </c>
       <c r="N58" t="n">
         <v>0.1233616037008481</v>
       </c>
       <c r="O58" t="n">
+        <v>0.07710100231303006</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" t="n">
+        <v>0.06168080185042405</v>
+      </c>
+      <c r="W58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X58" t="n">
         <v>0.01542020046260601</v>
       </c>
-      <c r="P58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
-      <c r="R58" t="n">
-        <v>0</v>
-      </c>
-      <c r="S58" t="n">
-        <v>0.04626060138781804</v>
-      </c>
-      <c r="T58" t="n">
-        <v>0</v>
-      </c>
-      <c r="U58" t="n">
-        <v>0</v>
-      </c>
-      <c r="V58" t="n">
-        <v>0</v>
-      </c>
-      <c r="W58" t="n">
-        <v>0</v>
-      </c>
-      <c r="X58" t="n">
-        <v>0</v>
-      </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>1.264456437933693</v>
       </c>
       <c r="Z58" t="n">
         <v>0</v>
@@ -6798,19 +6798,19 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>0.01542020046260601</v>
+        <v>0</v>
       </c>
       <c r="AF58" t="n">
         <v>0</v>
       </c>
       <c r="AG58" t="n">
-        <v>1.264456437933693</v>
+        <v>0</v>
       </c>
       <c r="AH58" t="n">
-        <v>0</v>
+        <v>0.2158828064764842</v>
       </c>
       <c r="AI58" t="n">
-        <v>0.2158828064764842</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -6835,91 +6835,91 @@
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>8.93371757925072</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>1.325648414985591</v>
       </c>
       <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
         <v>0.01921229586935639</v>
       </c>
-      <c r="J59" t="n">
-        <v>0</v>
-      </c>
-      <c r="K59" t="n">
-        <v>1.325648414985591</v>
-      </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0.1152737752161383</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>0.1152737752161383</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" t="n">
+        <v>0</v>
+      </c>
+      <c r="W59" t="n">
         <v>0.07684918347742556</v>
       </c>
-      <c r="N59" t="n">
-        <v>0</v>
-      </c>
-      <c r="O59" t="n">
-        <v>8.93371757925072</v>
-      </c>
-      <c r="P59" t="n">
-        <v>0.1152737752161383</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
-      <c r="R59" t="n">
+      <c r="X59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>1.364073006724304</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>0.1536983669548511</v>
+      </c>
+      <c r="AC59" t="n">
         <v>3.150816522574448</v>
       </c>
-      <c r="S59" t="n">
-        <v>0</v>
-      </c>
-      <c r="T59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U59" t="n">
-        <v>0</v>
-      </c>
-      <c r="V59" t="n">
+      <c r="AD59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="n">
         <v>0.01921229586935639</v>
       </c>
-      <c r="W59" t="n">
-        <v>0</v>
-      </c>
-      <c r="X59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y59" t="n">
-        <v>0.1536983669548511</v>
-      </c>
-      <c r="Z59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB59" t="n">
-        <v>0.1152737752161383</v>
-      </c>
-      <c r="AC59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD59" t="n">
+      <c r="AF59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI59" t="n">
         <v>0.03842459173871278</v>
-      </c>
-      <c r="AE59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG59" t="n">
-        <v>1.364073006724304</v>
-      </c>
-      <c r="AH59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI59" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -6935,100 +6935,100 @@
         <v>1</v>
       </c>
       <c r="D60" t="n">
-        <v>0.007006971937077392</v>
+        <v>0.05255228952808044</v>
       </c>
       <c r="E60" t="n">
         <v>3.051536278597204</v>
       </c>
       <c r="F60" t="n">
+        <v>0.1681673264898574</v>
+      </c>
+      <c r="G60" t="n">
+        <v>10.57352065304979</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.9459412115054479</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0.02102091581123218</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0.02102091581123218</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0.007006971937077392</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0.007006971937077392</v>
+      </c>
+      <c r="P60" t="n">
         <v>0.003503485968538696</v>
       </c>
-      <c r="G60" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0.007006971937077392</v>
-      </c>
-      <c r="I60" t="n">
-        <v>0.02102091581123218</v>
-      </c>
-      <c r="J60" t="n">
-        <v>0.03503485968538696</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0.9459412115054479</v>
-      </c>
-      <c r="L60" t="n">
+      <c r="Q60" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0.07006971937077391</v>
+      </c>
+      <c r="S60" t="n">
         <v>0.003503485968538696</v>
       </c>
-      <c r="M60" t="n">
-        <v>0.04204183162246435</v>
-      </c>
-      <c r="N60" t="n">
-        <v>0</v>
-      </c>
-      <c r="O60" t="n">
-        <v>10.57352065304979</v>
-      </c>
-      <c r="P60" t="n">
+      <c r="T60" t="n">
         <v>0.2032021861752444</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
-      <c r="R60" t="n">
-        <v>3.619101005500473</v>
-      </c>
-      <c r="S60" t="n">
-        <v>0.02102091581123218</v>
-      </c>
-      <c r="T60" t="n">
-        <v>0.003503485968538696</v>
       </c>
       <c r="U60" t="n">
         <v>0.003503485968538696</v>
       </c>
       <c r="V60" t="n">
+        <v>0</v>
+      </c>
+      <c r="W60" t="n">
+        <v>0.04204183162246435</v>
+      </c>
+      <c r="X60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>1.261254948673931</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>0.003503485968538696</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>0.1331324668044704</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>3.619101005500473</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="n">
         <v>0.01051045790561609</v>
       </c>
-      <c r="W60" t="n">
-        <v>0</v>
-      </c>
-      <c r="X60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y60" t="n">
-        <v>0.1331324668044704</v>
-      </c>
-      <c r="Z60" t="n">
-        <v>0.1681673264898574</v>
-      </c>
-      <c r="AA60" t="n">
-        <v>0.05255228952808044</v>
-      </c>
-      <c r="AB60" t="n">
-        <v>0.07006971937077391</v>
-      </c>
-      <c r="AC60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD60" t="n">
+      <c r="AF60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="n">
+        <v>0.03503485968538696</v>
+      </c>
+      <c r="AH60" t="n">
+        <v>0.04204183162246435</v>
+      </c>
+      <c r="AI60" t="n">
         <v>0.1086080650246996</v>
-      </c>
-      <c r="AE60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG60" t="n">
-        <v>1.261254948673931</v>
-      </c>
-      <c r="AH60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI60" t="n">
-        <v>0.04204183162246435</v>
       </c>
     </row>
     <row r="61">
@@ -7044,7 +7044,7 @@
         <v>1</v>
       </c>
       <c r="D61" t="n">
-        <v>0.005338268265774583</v>
+        <v>0</v>
       </c>
       <c r="E61" t="n">
         <v>0.03380903234990569</v>
@@ -7053,16 +7053,16 @@
         <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>0.1334567066443646</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>0.003558845510516389</v>
+        <v>0</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>0.003558845510516389</v>
+        <v>0</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
@@ -7071,13 +7071,13 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>0.005338268265774583</v>
       </c>
       <c r="N61" t="n">
         <v>0.09786825153920069</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>0.003558845510516389</v>
       </c>
       <c r="P61" t="n">
         <v>0</v>
@@ -7086,58 +7086,58 @@
         <v>0</v>
       </c>
       <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V61" t="n">
+        <v>0.1334567066443646</v>
+      </c>
+      <c r="W61" t="n">
+        <v>0</v>
+      </c>
+      <c r="X61" t="n">
         <v>0.005338268265774583</v>
       </c>
-      <c r="S61" t="n">
-        <v>0</v>
-      </c>
-      <c r="T61" t="n">
-        <v>0</v>
-      </c>
-      <c r="U61" t="n">
-        <v>0</v>
-      </c>
-      <c r="V61" t="n">
-        <v>0</v>
-      </c>
-      <c r="W61" t="n">
-        <v>0</v>
-      </c>
-      <c r="X61" t="n">
-        <v>0</v>
-      </c>
       <c r="Y61" t="n">
+        <v>0.05872095092352041</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB61" t="n">
         <v>0.003558845510516389</v>
       </c>
-      <c r="Z61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB61" t="n">
-        <v>0</v>
-      </c>
       <c r="AC61" t="n">
-        <v>0</v>
+        <v>0.005338268265774583</v>
       </c>
       <c r="AD61" t="n">
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>0.005338268265774583</v>
+        <v>0</v>
       </c>
       <c r="AF61" t="n">
         <v>0</v>
       </c>
       <c r="AG61" t="n">
-        <v>0.05872095092352041</v>
+        <v>0.003558845510516389</v>
       </c>
       <c r="AH61" t="n">
-        <v>0</v>
+        <v>0.5195914445353927</v>
       </c>
       <c r="AI61" t="n">
-        <v>0.5195914445353927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -7159,88 +7159,88 @@
         <v>0.2789140944589066</v>
       </c>
       <c r="F62" t="n">
+        <v>0.05578281889178133</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.7809594644849386</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.2975083674228338</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0.05578281889178133</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0.07437709185570844</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0.1115656377835627</v>
+      </c>
+      <c r="S62" t="n">
         <v>0.03718854592785422</v>
       </c>
-      <c r="G62" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0.07437709185570844</v>
-      </c>
-      <c r="I62" t="n">
+      <c r="T62" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W62" t="n">
         <v>0.05578281889178133</v>
       </c>
-      <c r="J62" t="n">
-        <v>0</v>
-      </c>
-      <c r="K62" t="n">
-        <v>0.2975083674228338</v>
-      </c>
-      <c r="L62" t="n">
-        <v>0</v>
-      </c>
-      <c r="M62" t="n">
-        <v>0.05578281889178133</v>
-      </c>
-      <c r="N62" t="n">
-        <v>0</v>
-      </c>
-      <c r="O62" t="n">
-        <v>0.7809594644849386</v>
-      </c>
-      <c r="P62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
-      <c r="R62" t="n">
+      <c r="X62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>0.3904797322424693</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>0.03718854592785422</v>
+      </c>
+      <c r="AC62" t="n">
         <v>0.3161026403867608</v>
       </c>
-      <c r="S62" t="n">
-        <v>0</v>
-      </c>
-      <c r="T62" t="n">
-        <v>0</v>
-      </c>
-      <c r="U62" t="n">
-        <v>0</v>
-      </c>
-      <c r="V62" t="n">
+      <c r="AD62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="n">
         <v>0.01859427296392711</v>
       </c>
-      <c r="W62" t="n">
-        <v>0</v>
-      </c>
-      <c r="X62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y62" t="n">
-        <v>0.03718854592785422</v>
-      </c>
-      <c r="Z62" t="n">
-        <v>0.05578281889178133</v>
-      </c>
-      <c r="AA62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB62" t="n">
-        <v>0.1115656377835627</v>
-      </c>
-      <c r="AC62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE62" t="n">
-        <v>0</v>
-      </c>
       <c r="AF62" t="n">
         <v>0</v>
       </c>
       <c r="AG62" t="n">
-        <v>0.3904797322424693</v>
+        <v>0</v>
       </c>
       <c r="AH62" t="n">
         <v>0</v>
@@ -7262,100 +7262,100 @@
         <v>2</v>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
+        <v>0.00436109899694723</v>
       </c>
       <c r="E63" t="n">
         <v>0.3576101177496729</v>
       </c>
       <c r="F63" t="n">
+        <v>0.06541648495420846</v>
+      </c>
+      <c r="G63" t="n">
+        <v>1.626689925861317</v>
+      </c>
+      <c r="H63" t="n">
+        <v>1.142607937200175</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0.02616659398168339</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0.008722197993894461</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0.01308329699084169</v>
+      </c>
+      <c r="S63" t="n">
         <v>0.00436109899694723</v>
       </c>
-      <c r="G63" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" t="n">
-        <v>0.008722197993894461</v>
-      </c>
-      <c r="I63" t="n">
+      <c r="T63" t="n">
         <v>0.02616659398168339</v>
       </c>
-      <c r="J63" t="n">
+      <c r="U63" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" t="n">
+        <v>0</v>
+      </c>
+      <c r="W63" t="n">
+        <v>0.01308329699084169</v>
+      </c>
+      <c r="X63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>0.5276929786306149</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>0.07849978194505015</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>0.4491931966855648</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="n">
         <v>0.00436109899694723</v>
       </c>
-      <c r="K63" t="n">
-        <v>1.142607937200175</v>
-      </c>
-      <c r="L63" t="n">
-        <v>0</v>
-      </c>
-      <c r="M63" t="n">
-        <v>0.01308329699084169</v>
-      </c>
-      <c r="N63" t="n">
-        <v>0</v>
-      </c>
-      <c r="O63" t="n">
-        <v>1.626689925861317</v>
-      </c>
-      <c r="P63" t="n">
-        <v>0.02616659398168339</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
-      <c r="R63" t="n">
-        <v>0.4491931966855648</v>
-      </c>
-      <c r="S63" t="n">
-        <v>0</v>
-      </c>
-      <c r="T63" t="n">
-        <v>0</v>
-      </c>
-      <c r="U63" t="n">
-        <v>0</v>
-      </c>
-      <c r="V63" t="n">
-        <v>0</v>
-      </c>
-      <c r="W63" t="n">
-        <v>0</v>
-      </c>
-      <c r="X63" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y63" t="n">
-        <v>0.07849978194505015</v>
-      </c>
-      <c r="Z63" t="n">
-        <v>0.06541648495420846</v>
-      </c>
-      <c r="AA63" t="n">
+      <c r="AH63" t="n">
         <v>0.00436109899694723</v>
       </c>
-      <c r="AB63" t="n">
-        <v>0.01308329699084169</v>
-      </c>
-      <c r="AC63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD63" t="n">
+      <c r="AI63" t="n">
         <v>0.04797208896641954</v>
-      </c>
-      <c r="AE63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG63" t="n">
-        <v>0.5276929786306149</v>
-      </c>
-      <c r="AH63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI63" t="n">
-        <v>0.00436109899694723</v>
       </c>
     </row>
     <row r="64">
@@ -7371,100 +7371,100 @@
         <v>2</v>
       </c>
       <c r="D64" t="n">
-        <v>0.04623208506703652</v>
+        <v>0.02311604253351826</v>
       </c>
       <c r="E64" t="n">
         <v>0.4160887656033287</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>0.1618122977346279</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>1.363846509477578</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>1.109570041608877</v>
       </c>
       <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="n">
         <v>0.04623208506703652</v>
       </c>
-      <c r="J64" t="n">
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0.04623208506703652</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" t="n">
         <v>0.02311604253351826</v>
       </c>
-      <c r="K64" t="n">
-        <v>1.109570041608877</v>
-      </c>
-      <c r="L64" t="n">
-        <v>0</v>
-      </c>
-      <c r="M64" t="n">
+      <c r="S64" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" t="n">
+        <v>0</v>
+      </c>
+      <c r="W64" t="n">
         <v>0.02311604253351826</v>
       </c>
-      <c r="N64" t="n">
-        <v>0</v>
-      </c>
-      <c r="O64" t="n">
-        <v>1.363846509477578</v>
-      </c>
-      <c r="P64" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
-      <c r="R64" t="n">
+      <c r="X64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>0.6472491909385114</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>0.1386962552011096</v>
+      </c>
+      <c r="AC64" t="n">
         <v>0.3929727230698105</v>
       </c>
-      <c r="S64" t="n">
-        <v>0</v>
-      </c>
-      <c r="T64" t="n">
-        <v>0</v>
-      </c>
-      <c r="U64" t="n">
-        <v>0</v>
-      </c>
-      <c r="V64" t="n">
-        <v>0</v>
-      </c>
-      <c r="W64" t="n">
-        <v>0</v>
-      </c>
-      <c r="X64" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y64" t="n">
-        <v>0.1386962552011096</v>
-      </c>
-      <c r="Z64" t="n">
-        <v>0.1618122977346279</v>
-      </c>
-      <c r="AA64" t="n">
+      <c r="AD64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="n">
         <v>0.02311604253351826</v>
       </c>
-      <c r="AB64" t="n">
+      <c r="AH64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI64" t="n">
         <v>0.02311604253351826</v>
-      </c>
-      <c r="AC64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD64" t="n">
-        <v>0.02311604253351826</v>
-      </c>
-      <c r="AE64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG64" t="n">
-        <v>0.6472491909385114</v>
-      </c>
-      <c r="AH64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI64" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -7492,7 +7492,7 @@
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>7.76</v>
       </c>
       <c r="I65" t="n">
         <v>0</v>
@@ -7501,7 +7501,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>7.76</v>
+        <v>0</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -7589,34 +7589,34 @@
         <v>2</v>
       </c>
       <c r="D66" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.05443658138268917</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
         <v>0.326619488296135</v>
-      </c>
-      <c r="E66" t="n">
-        <v>0</v>
-      </c>
-      <c r="F66" t="n">
-        <v>0</v>
-      </c>
-      <c r="G66" t="n">
-        <v>0.5443658138268916</v>
-      </c>
-      <c r="H66" t="n">
-        <v>0.05443658138268917</v>
-      </c>
-      <c r="I66" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" t="n">
-        <v>0</v>
-      </c>
-      <c r="K66" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" t="n">
-        <v>0</v>
-      </c>
-      <c r="M66" t="n">
-        <v>0</v>
       </c>
       <c r="N66" t="n">
         <v>0.1633097441480675</v>
@@ -7631,58 +7631,58 @@
         <v>0</v>
       </c>
       <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>0</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
+      </c>
+      <c r="V66" t="n">
+        <v>0.5443658138268916</v>
+      </c>
+      <c r="W66" t="n">
+        <v>0</v>
+      </c>
+      <c r="X66" t="n">
+        <v>0.05443658138268917</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>0.1088731627653783</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC66" t="n">
         <v>0.1633097441480675</v>
       </c>
-      <c r="S66" t="n">
-        <v>0</v>
-      </c>
-      <c r="T66" t="n">
-        <v>0</v>
-      </c>
-      <c r="U66" t="n">
-        <v>0</v>
-      </c>
-      <c r="V66" t="n">
-        <v>0</v>
-      </c>
-      <c r="W66" t="n">
-        <v>0</v>
-      </c>
-      <c r="X66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC66" t="n">
-        <v>0</v>
-      </c>
       <c r="AD66" t="n">
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>0.05443658138268917</v>
+        <v>0</v>
       </c>
       <c r="AF66" t="n">
         <v>0</v>
       </c>
       <c r="AG66" t="n">
-        <v>0.1088731627653783</v>
+        <v>0</v>
       </c>
       <c r="AH66" t="n">
-        <v>0</v>
+        <v>0.2721829069134458</v>
       </c>
       <c r="AI66" t="n">
-        <v>0.2721829069134458</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -7710,7 +7710,7 @@
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="I67" t="n">
         <v>0</v>
@@ -7719,7 +7719,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
@@ -7819,29 +7819,29 @@
         <v>0</v>
       </c>
       <c r="H68" t="n">
+        <v>0.0293140512018761</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" t="n">
         <v>0.05374242720343951</v>
       </c>
-      <c r="I68" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" t="n">
-        <v>0</v>
-      </c>
-      <c r="K68" t="n">
-        <v>0.0293140512018761</v>
-      </c>
-      <c r="L68" t="n">
-        <v>0</v>
-      </c>
-      <c r="M68" t="n">
-        <v>0</v>
-      </c>
-      <c r="N68" t="n">
-        <v>0</v>
-      </c>
-      <c r="O68" t="n">
-        <v>0</v>
-      </c>
       <c r="P68" t="n">
         <v>0</v>
       </c>
@@ -7882,10 +7882,10 @@
         <v>0</v>
       </c>
       <c r="AC68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD68" t="n">
         <v>0.01465702560093805</v>
-      </c>
-      <c r="AD68" t="n">
-        <v>0</v>
       </c>
       <c r="AE68" t="n">
         <v>0</v>
@@ -7928,29 +7928,29 @@
         <v>0</v>
       </c>
       <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0.005292965648652941</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" t="n">
         <v>0.6298629121896998</v>
       </c>
-      <c r="I69" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" t="n">
-        <v>0</v>
-      </c>
-      <c r="K69" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" t="n">
-        <v>0</v>
-      </c>
-      <c r="M69" t="n">
-        <v>0</v>
-      </c>
-      <c r="N69" t="n">
-        <v>0</v>
-      </c>
-      <c r="O69" t="n">
-        <v>0</v>
-      </c>
       <c r="P69" t="n">
         <v>0</v>
       </c>
@@ -7961,7 +7961,7 @@
         <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>0.005292965648652941</v>
+        <v>0</v>
       </c>
       <c r="T69" t="n">
         <v>0</v>
@@ -7976,7 +7976,7 @@
         <v>0</v>
       </c>
       <c r="X69" t="n">
-        <v>0</v>
+        <v>0.02117186259461176</v>
       </c>
       <c r="Y69" t="n">
         <v>0</v>
@@ -7991,13 +7991,13 @@
         <v>0</v>
       </c>
       <c r="AC69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD69" t="n">
         <v>0.01058593129730588</v>
       </c>
-      <c r="AD69" t="n">
-        <v>0</v>
-      </c>
       <c r="AE69" t="n">
-        <v>0.02117186259461176</v>
+        <v>0</v>
       </c>
       <c r="AF69" t="n">
         <v>0</v>
@@ -8037,7 +8037,7 @@
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="I70" t="n">
         <v>0</v>
@@ -8046,7 +8046,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>5.23</v>
+        <v>0</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
@@ -8088,7 +8088,7 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>0</v>
+        <v>5.11</v>
       </c>
       <c r="Z70" t="n">
         <v>0</v>
@@ -8112,7 +8112,7 @@
         <v>0</v>
       </c>
       <c r="AG70" t="n">
-        <v>5.11</v>
+        <v>0</v>
       </c>
       <c r="AH70" t="n">
         <v>0</v>
@@ -8197,7 +8197,7 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z71" t="n">
         <v>0</v>
@@ -8212,22 +8212,22 @@
         <v>0</v>
       </c>
       <c r="AD71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI71" t="n">
         <v>2.3</v>
-      </c>
-      <c r="AE71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG71" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI71" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/OLS_all.xlsx
+++ b/data/OLS_all.xlsx
@@ -441,162 +441,162 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>470</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>605</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>771</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>541</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>871</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>410</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>725</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>426</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>678</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>584</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>428</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>494</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>712</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
           <t>565</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>871</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>605</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>712</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>337</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>79</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>410</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>725</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>584</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>470</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>494</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>771</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>426</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>428</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>549</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>342</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>541</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>678</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>625</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>657</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>799</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>334</t>
         </is>
       </c>
     </row>
@@ -613,7 +613,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1723395088323998</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -622,38 +622,38 @@
         <v>0.6247307195174493</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>0.02154243860404998</v>
       </c>
       <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.2154243860404998</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
         <v>0.1938819474364498</v>
       </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
         <v>0.4523912106850495</v>
       </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
@@ -676,10 +676,10 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.2154243860404998</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>0.2800517018526497</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -700,13 +700,13 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.2800517018526497</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>0.1723395088323998</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.02154243860404998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -722,7 +722,7 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2466325175488522</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -734,35 +734,35 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.3035477139062797</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
         <v>0.1138303927148549</v>
       </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
         <v>0.3035477139062797</v>
       </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -773,46 +773,46 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.233162587744261</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
         <v>0.01897173211914248</v>
       </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.3035477139062797</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
       <c r="AG3" t="n">
-        <v>1.233162587744261</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>0.2466325175488522</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -831,7 +831,7 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.485391603240855</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -840,88 +840,88 @@
         <v>0.7979376381045912</v>
       </c>
       <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.3068990915786889</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
         <v>0.01227596366314756</v>
       </c>
-      <c r="H4" t="n">
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0.2332433095998036</v>
       </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3.584581389639087</v>
+      </c>
+      <c r="R4" t="n">
         <v>0.01227596366314756</v>
       </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>3.584581389639087</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
         <v>0.02455192732629511</v>
       </c>
-      <c r="S4" t="n">
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
         <v>0.07365578197888534</v>
       </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
+      <c r="Z4" t="n">
+        <v>0.3068990915786889</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
         <v>0.01227596366314756</v>
       </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
         <v>0.01227596366314756</v>
       </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.3068990915786889</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
+      <c r="AF4" t="n">
         <v>0.01227596366314756</v>
       </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
       <c r="AG4" t="n">
-        <v>0.3068990915786889</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.485391603240855</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -940,7 +940,7 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.400907948960928</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -949,91 +949,91 @@
         <v>1.439055027877559</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>0.002203759613901316</v>
       </c>
       <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.2291909998457368</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.004407519227802631</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.02203759613901316</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
         <v>0.1410406152896842</v>
       </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
         <v>2.053903960156026</v>
       </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.006611278841703947</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
         <v>0.002203759613901316</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.006611278841703947</v>
-      </c>
-      <c r="S5" t="n">
+      <c r="Z5" t="n">
+        <v>2.201555854287414</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
         <v>0.002203759613901316</v>
       </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
         <v>0.01542631729730921</v>
       </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.2291909998457368</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0.02203759613901316</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0.004407519227802631</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
       <c r="AG5" t="n">
-        <v>2.201555854287414</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>4.400907948960928</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.002203759613901316</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1049,7 +1049,7 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.073071967605375</v>
+        <v>0.00184060371801951</v>
       </c>
       <c r="E6" t="n">
         <v>0.00184060371801951</v>
@@ -1058,28 +1058,28 @@
         <v>1.006810233756672</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>0.003681207436039021</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2043070127001657</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.3349898766795509</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01288422602613657</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.003681207436039021</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0.00184060371801951</v>
       </c>
       <c r="M6" t="n">
-        <v>3.740106755015645</v>
+        <v>0.2043070127001657</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>0.00184060371801951</v>
       </c>
       <c r="O6" t="n">
         <v>0.00184060371801951</v>
@@ -1088,58 +1088,58 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.740106755015645</v>
       </c>
       <c r="R6" t="n">
+        <v>0.01288422602613657</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
         <v>0.007362414872078041</v>
       </c>
-      <c r="S6" t="n">
+      <c r="W6" t="n">
+        <v>0.007362414872078041</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
         <v>0.003681207436039021</v>
       </c>
-      <c r="T6" t="n">
+      <c r="Z6" t="n">
+        <v>0.9147800478556966</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.03313086692435119</v>
+      </c>
+      <c r="AG6" t="n">
         <v>0.00184060371801951</v>
       </c>
-      <c r="U6" t="n">
-        <v>0.03313086692435119</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.3349898766795509</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0.007362414872078041</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0.00184060371801951</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0.9147800478556966</v>
-      </c>
       <c r="AH6" t="n">
-        <v>0.00184060371801951</v>
+        <v>1.073071967605375</v>
       </c>
       <c r="AI6" t="n">
         <v>0.003681207436039021</v>
@@ -1267,7 +1267,7 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3904450103067782</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -1276,91 +1276,91 @@
         <v>0.4995756032496665</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>0.01455074572571844</v>
       </c>
       <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.2012853158724384</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>0.2182611858857766</v>
       </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.4680489875106099</v>
+      </c>
+      <c r="R8" t="n">
         <v>0.009700497150478962</v>
       </c>
-      <c r="K8" t="n">
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
         <v>0.00242512428761974</v>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.4680489875106099</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
         <v>0.004850248575239481</v>
       </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
+      <c r="Z8" t="n">
+        <v>0.2303868073238753</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
         <v>0.007275372862859222</v>
       </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0.2012853158724384</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.3904450103067782</v>
+      </c>
+      <c r="AI8" t="n">
         <v>0.00242512428761974</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0.2303868073238753</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0.01455074572571844</v>
       </c>
     </row>
     <row r="9">
@@ -1485,10 +1485,10 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3751339764201501</v>
+        <v>0.005954507562224604</v>
       </c>
       <c r="E10" t="n">
-        <v>0.002977253781112302</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>1.155174467071573</v>
@@ -1497,85 +1497,85 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.4138382755746099</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.002977253781112302</v>
+      </c>
+      <c r="M10" t="n">
         <v>0.2768846016434441</v>
       </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.3989520066690485</v>
+      </c>
+      <c r="R10" t="n">
         <v>0.005954507562224604</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0.3989520066690485</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.008931761343336906</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.06549958318447065</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.01488626890556151</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.2590210789567703</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.002977253781112302</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
         <v>0.005954507562224604</v>
       </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.008931761343336906</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.01488626890556151</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0.005954507562224604</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0.002977253781112302</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0.4138382755746099</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0.06549958318447065</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
       <c r="AG10" t="n">
-        <v>0.2590210789567703</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>0.3751339764201501</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1606,23 +1606,23 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
         <v>2.42</v>
       </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.57</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.57</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1712,88 +1712,88 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.0255819902788437</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>11.97237145049885</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.920951650038373</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.0255819902788437</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.07674597083653108</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.05116398055768739</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
         <v>0.1534919416730622</v>
       </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0.07674597083653108</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0.920951650038373</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0.0255819902788437</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0.0255819902788437</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
       <c r="AF12" t="n">
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.05116398055768739</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>11.97237145049885</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -1812,97 +1812,97 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>0.02323660022720231</v>
       </c>
       <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.1962201796963751</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.01807291128782402</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>0.06712795621191779</v>
       </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.1394196013632139</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.007745533409067438</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.005163688939378292</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.3020758029536301</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.005163688939378292</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.1187648456057007</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
         <v>0.002581844469689146</v>
       </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.005163688939378292</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0.007745533409067438</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0.1187648456057007</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0.02323660022720231</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0.3020758029536301</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
         <v>0.02581844469689146</v>
       </c>
-      <c r="Y13" t="n">
-        <v>0.1962201796963751</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0.005163688939378292</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0.01807291128782402</v>
-      </c>
       <c r="AD13" t="n">
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>0.002581844469689146</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.002581844469689146</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.1394196013632139</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -1921,7 +1921,7 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>0.6550218340611353</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -1930,88 +1930,88 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.1984914648670107</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.8535132989281461</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.6947201270345376</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
         <v>0.01984914648670107</v>
       </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
+      <c r="X14" t="n">
         <v>0.05954743946010321</v>
       </c>
-      <c r="O14" t="n">
-        <v>0.6550218340611353</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0.6947201270345376</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
         <v>0.03969829297340214</v>
       </c>
-      <c r="Y14" t="n">
-        <v>0.1984914648670107</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0</v>
-      </c>
       <c r="AA14" t="n">
         <v>0</v>
       </c>
       <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0.03969829297340214</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
         <v>0.01984914648670107</v>
       </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>0</v>
-      </c>
       <c r="AF14" t="n">
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.03969829297340214</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.8535132989281461</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2030,7 +2030,7 @@
         <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>0.03359650596337981</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -2060,53 +2060,53 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>4.905089870653452</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>13.50579539727868</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
         <v>0.05039475894506971</v>
       </c>
-      <c r="O15" t="n">
-        <v>0.03359650596337981</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>13.50579539727868</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.1847807827985889</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
         <v>0.520745842432387</v>
       </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
       <c r="AD15" t="n">
         <v>0</v>
       </c>
@@ -2117,10 +2117,10 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.1847807827985889</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>4.905089870653452</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>0.04810930433945925</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -2154,68 +2154,68 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
+        <v>0.02405465216972963</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.732608486481285</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.651496199364957</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.03367651303762147</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.362166843067449</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
         <v>0.00962186086789185</v>
       </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>2.362166843067449</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0.04810930433945925</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>3.651496199364957</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
+      <c r="AA16" t="n">
+        <v>0.00962186086789185</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
         <v>0.0577311652073511</v>
       </c>
-      <c r="Y16" t="n">
-        <v>0.02405465216972963</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0.03367651303762147</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
       <c r="AD16" t="n">
         <v>0</v>
       </c>
@@ -2226,10 +2226,10 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.00962186086789185</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.732608486481285</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2248,7 +2248,7 @@
         <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>0.01710069868568916</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -2257,88 +2257,88 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.06107392387746129</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.9258806859823131</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.9429813846680022</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.002442956955098451</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.08550349342844579</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.01221478477549226</v>
+      </c>
+      <c r="AA17" t="n">
         <v>0.01465774173059071</v>
       </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0.06595983778765818</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
         <v>0.01465774173059071</v>
       </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0.08550349342844579</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0.01710069868568916</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0.9429813846680022</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0.06595983778765818</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0.06107392387746129</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0.002442956955098451</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0</v>
-      </c>
       <c r="AF17" t="n">
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.01221478477549226</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.9258806859823131</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2387,38 +2387,38 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.9528851244044468</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.058761249338274</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
         <v>0.2117522498676549</v>
       </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.058761249338274</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
       <c r="Y18" t="n">
         <v>0</v>
       </c>
@@ -2447,7 +2447,7 @@
         <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>0.9528851244044468</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2466,7 +2466,7 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2642506606266515</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -2475,41 +2475,41 @@
         <v>1.006669183339625</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>0.01258336479174531</v>
       </c>
       <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.705423430225242</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.01258336479174531</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
         <v>1.849754624386561</v>
       </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.01258336479174531</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.1761671070844344</v>
+      </c>
+      <c r="R19" t="n">
         <v>0.06291682395872657</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.1761671070844344</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
@@ -2523,43 +2523,43 @@
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.01258336479174531</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.705423430225242</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>0.1510003775009437</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.01258336479174531</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.01258336479174531</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.01258336479174531</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.1510003775009437</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>0.2642506606266515</v>
       </c>
       <c r="AI19" t="n">
-        <v>0.01258336479174531</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2605,38 +2605,38 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.002897899747158247</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
         <v>0.0002414916455965206</v>
       </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
       <c r="Y20" t="n">
         <v>0</v>
       </c>
@@ -2665,7 +2665,7 @@
         <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>0.002897899747158247</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -2696,22 +2696,22 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
         <v>0.01444669170759896</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2793,7 +2793,7 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>0.002372948388372553</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -2805,88 +2805,88 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>0.4018192604310856</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>0.2950365829543207</v>
       </c>
       <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.002372948388372553</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.002372948388372553</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0.01186474194186276</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="n">
         <v>0.1494957484674708</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0.002372948388372553</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0.002372948388372553</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0.4018192604310856</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0.01186474194186276</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>0.2950365829543207</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>0.002372948388372553</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2902,7 +2902,7 @@
         <v>3</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>0.02804262478968031</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -2911,88 +2911,88 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.06118390863202978</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.8999133227961047</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.371539285168001</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.1223678172640596</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0.1325651353693978</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0.005098659052669148</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0.01529597715800744</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0.03314128384234946</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
         <v>0.0101973181053383</v>
       </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.01529597715800744</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0.1325651353693978</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0.02804262478968031</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.371539285168001</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0.03314128384234946</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>0.06118390863202978</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>0.1223678172640596</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>0</v>
-      </c>
       <c r="AF23" t="n">
         <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.005098659052669148</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>0.8999133227961047</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3011,7 +3011,7 @@
         <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>0.0461714174625161</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -3020,88 +3020,88 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.3669412650968384</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>2.605039974727224</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3.251439819202449</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0.01944059682632257</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0.05346164127238706</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0.009720298413161283</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0.06561201428883867</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
         <v>0.0121503730164516</v>
       </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0.05346164127238706</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0.0461714174625161</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>3.251439819202449</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" t="n">
-        <v>0.06561201428883867</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>0.3669412650968384</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>0.01944059682632257</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>0</v>
-      </c>
       <c r="AF24" t="n">
         <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.009720298413161283</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.605039974727224</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3120,40 +3120,40 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.009932459276916964</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
         <v>0.004966229638458482</v>
       </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
         <v>0.09435836313071116</v>
       </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
       <c r="N25" t="n">
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>0.124155740961462</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -3168,25 +3168,25 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>0.009932459276916964</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>0.009932459276916964</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
         <v>0.004966229638458482</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>0</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3207,13 +3207,13 @@
         <v>0</v>
       </c>
       <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
         <v>0.004966229638458482</v>
       </c>
-      <c r="AH25" t="n">
-        <v>0.124155740961462</v>
-      </c>
       <c r="AI25" t="n">
-        <v>0.009932459276916964</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -3232,97 +3232,97 @@
         <v>0.005749770009199632</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2932382704691812</v>
+        <v>0.03737350505979761</v>
       </c>
       <c r="F26" t="n">
         <v>0.327736890524379</v>
       </c>
       <c r="G26" t="n">
+        <v>0.0718721251149954</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.8825896964121436</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.4312327506899724</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.2932382704691812</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.8107175712971482</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.002874885004599816</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.002874885004599816</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.02874885004599816</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.04024839006439743</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.06324747010119594</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0.008624655013799448</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
         <v>1.138454461821527</v>
       </c>
-      <c r="H26" t="n">
-        <v>0.8107175712971482</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.02874885004599816</v>
-      </c>
-      <c r="K26" t="n">
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0.005749770009199632</v>
+      </c>
+      <c r="AI26" t="n">
         <v>0.02299908003679853</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0.002874885004599816</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0.005749770009199632</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0.04024839006439743</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0.03737350505979761</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0.008624655013799448</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>0.8825896964121436</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>0.06324747010119594</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>0.4312327506899724</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>0.002874885004599816</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>0.0718721251149954</v>
       </c>
     </row>
     <row r="27">
@@ -3350,13 +3350,13 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>0.3166978965981368</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>0.3998310944551476</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>0.001319574569158903</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -3377,19 +3377,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.3166978965981368</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>0.001319574569158903</v>
       </c>
       <c r="T27" t="n">
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>0.00395872370747671</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -3401,10 +3401,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.3998310944551476</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.00395872370747671</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3413,7 +3413,7 @@
         <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.001319574569158903</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
         <v>0</v>
@@ -3422,7 +3422,7 @@
         <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.001319574569158903</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -3559,97 +3559,97 @@
         <v>0.01173846695621552</v>
       </c>
       <c r="E29" t="n">
-        <v>0.4069335211488046</v>
+        <v>0.03521540086864655</v>
       </c>
       <c r="F29" t="n">
         <v>0.1486872481120632</v>
       </c>
       <c r="G29" t="n">
+        <v>1.737293109519897</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>7.160464843291465</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.4617130336111437</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.4069335211488046</v>
+      </c>
+      <c r="M29" t="n">
+        <v>5.157099816097351</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.01173846695621552</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.007825644637477012</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.1095590249246782</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0.1056462026059397</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.498610948076848</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0.05477951246233909</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0.03912822318738506</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0.03130257854990805</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
         <v>1.475134014164417</v>
       </c>
-      <c r="H29" t="n">
-        <v>5.157099816097351</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.1095590249246782</v>
-      </c>
-      <c r="K29" t="n">
+      <c r="AF29" t="n">
+        <v>0.003912822318738506</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0.01173846695621552</v>
+      </c>
+      <c r="AI29" t="n">
         <v>0.4030206988300661</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0.007825644637477012</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0.01173846695621552</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0.1056462026059397</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0.05477951246233909</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0.03521540086864655</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0.003912822318738506</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0.03130257854990805</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>7.160464843291465</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.498610948076848</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>0.4617130336111437</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>0.01173846695621552</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>0.03912822318738506</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>1.737293109519897</v>
       </c>
     </row>
     <row r="30">
@@ -3668,80 +3668,80 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.134331222414124</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
         <v>0.05757052389176742</v>
       </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="n">
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.5757052389176741</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
         <v>0.01919017463058914</v>
       </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
+      <c r="R30" t="n">
         <v>0.01919017463058914</v>
       </c>
-      <c r="N30" t="n">
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0.1151410477835348</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
         <v>1.823066589905968</v>
       </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
         <v>0.1151410477835348</v>
       </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
         <v>0.268662444828248</v>
       </c>
-      <c r="Y30" t="n">
-        <v>0.134331222414124</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>0</v>
-      </c>
       <c r="AD30" t="n">
         <v>0</v>
       </c>
@@ -3752,10 +3752,10 @@
         <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.1151410477835348</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.5757052389176741</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -3774,70 +3774,70 @@
         <v>2</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>0.01793239487133507</v>
       </c>
       <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.6276338204967273</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.008966197435667534</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
         <v>0.0403478884605039</v>
       </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
       <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.1748408499955169</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
         <v>0.004483098717833767</v>
       </c>
-      <c r="N31" t="n">
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0.192773244866852</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0.008966197435667534</v>
+      </c>
+      <c r="X31" t="n">
         <v>0.1613915538420156</v>
       </c>
-      <c r="O31" t="n">
-        <v>0.01793239487133507</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0.192773244866852</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0.008966197435667534</v>
-      </c>
       <c r="Y31" t="n">
-        <v>0.6276338204967273</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
         <v>0</v>
@@ -3846,7 +3846,7 @@
         <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.008966197435667534</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
         <v>0.008966197435667534</v>
@@ -3864,7 +3864,7 @@
         <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.1748408499955169</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -3992,97 +3992,97 @@
         <v>3</v>
       </c>
       <c r="D33" t="n">
+        <v>0.09877518767285659</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.0493875938364283</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.1481627815092849</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.0691426313709996</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0.009877518767285657</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0.02963255630185697</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0.01975503753457131</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0.009877518767285657</v>
+      </c>
+      <c r="AH33" t="n">
         <v>0.03951007506914263</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.1481627815092849</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0.09877518767285659</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0.009877518767285657</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0.01975503753457131</v>
-      </c>
-      <c r="V33" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" t="n">
-        <v>0</v>
-      </c>
-      <c r="X33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>0.0493875938364283</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>0.009877518767285657</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>0.02963255630185697</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>0.0691426313709996</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4101,97 +4101,97 @@
         <v>2</v>
       </c>
       <c r="D34" t="n">
+        <v>0.1625135427952329</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.6771397616468039</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.5958829902491874</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
         <v>0.9750812567713976</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0.5958829902491874</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0.1625135427952329</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" t="n">
-        <v>0</v>
-      </c>
-      <c r="X34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>0.6771397616468039</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>0</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4243,7 +4243,7 @@
         <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
@@ -4300,7 +4300,7 @@
         <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -4319,97 +4319,97 @@
         <v>1</v>
       </c>
       <c r="D36" t="n">
+        <v>0.01447282726680657</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.432809899413851</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.003618206816701643</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.01447282726680657</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0.003618206816701643</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>3.097185035096606</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
         <v>0.2098559953686953</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0.01447282726680657</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0.01447282726680657</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" t="n">
-        <v>0</v>
-      </c>
-      <c r="X36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.432809899413851</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>0.003618206816701643</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>3.097185035096606</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>0.003618206816701643</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>0</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -4428,7 +4428,7 @@
         <v>2</v>
       </c>
       <c r="D37" t="n">
-        <v>0.06917501278233933</v>
+        <v>0.1323348070618665</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -4437,31 +4437,31 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>0.03007609251406057</v>
       </c>
       <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.8631838551535385</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
         <v>0.2917380973863876</v>
       </c>
-      <c r="I37" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0.006015218502812114</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0</v>
-      </c>
       <c r="N37" t="n">
         <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>0.1323348070618665</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
         <v>0</v>
@@ -4479,29 +4479,29 @@
         <v>0</v>
       </c>
       <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
         <v>0.006015218502812114</v>
       </c>
-      <c r="V37" t="n">
-        <v>0</v>
-      </c>
       <c r="W37" t="n">
+        <v>0.0210532647598424</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="n">
         <v>0.003007609251406057</v>
       </c>
-      <c r="X37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>0.8631838551535385</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>0.0210532647598424</v>
-      </c>
       <c r="AC37" t="n">
         <v>0</v>
       </c>
@@ -4512,16 +4512,16 @@
         <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>0.006015218502812114</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>0.06917501278233933</v>
       </c>
       <c r="AI37" t="n">
-        <v>0.03007609251406057</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -4537,100 +4537,100 @@
         <v>2</v>
       </c>
       <c r="D38" t="n">
+        <v>0.08154478439559006</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.001630895687911801</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.06686672320438386</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.008154478439559005</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.1908147954856807</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0.009785374127470806</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0.004892687063735403</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0.009785374127470806</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0.006523582751647205</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
         <v>0.04240328788570683</v>
       </c>
-      <c r="E38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0.1908147954856807</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0.08154478439559006</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0.009785374127470806</v>
-      </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0.006523582751647205</v>
-      </c>
-      <c r="V38" t="n">
-        <v>0</v>
-      </c>
-      <c r="W38" t="n">
-        <v>0</v>
-      </c>
-      <c r="X38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>0.06686672320438386</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>0.004892687063735403</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>0.008154478439559005</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>0.009785374127470806</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>0</v>
-      </c>
       <c r="AI38" t="n">
-        <v>0.001630895687911801</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -4649,65 +4649,65 @@
         <v>0</v>
       </c>
       <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
         <v>0.01713428999785821</v>
       </c>
-      <c r="F39" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
       <c r="M39" t="n">
         <v>0</v>
       </c>
       <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.04926108374384236</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0.5632897836795887</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
         <v>0.05782822874277147</v>
       </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0.5632897836795887</v>
-      </c>
-      <c r="W39" t="n">
-        <v>0</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0</v>
-      </c>
       <c r="Y39" t="n">
         <v>0</v>
       </c>
@@ -4736,7 +4736,7 @@
         <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>0.04926108374384236</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -4758,65 +4758,65 @@
         <v>0</v>
       </c>
       <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
         <v>0.001210053121332026</v>
       </c>
-      <c r="F40" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
       <c r="M40" t="n">
         <v>0</v>
       </c>
       <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.1899783400491282</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0.07744339976524969</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
         <v>0.07260318727992159</v>
       </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" t="n">
-        <v>0.07744339976524969</v>
-      </c>
-      <c r="W40" t="n">
-        <v>0</v>
-      </c>
-      <c r="X40" t="n">
-        <v>0</v>
-      </c>
       <c r="Y40" t="n">
         <v>0</v>
       </c>
@@ -4845,7 +4845,7 @@
         <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>0.1899783400491282</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -4985,23 +4985,23 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
         <v>0.007502719735904265</v>
       </c>
-      <c r="I42" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" t="n">
-        <v>0</v>
-      </c>
       <c r="N42" t="n">
         <v>0</v>
       </c>
@@ -5030,7 +5030,7 @@
         <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>0.003751359867952133</v>
       </c>
       <c r="X42" t="n">
         <v>0</v>
@@ -5045,7 +5045,7 @@
         <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.003751359867952133</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5085,20 +5085,20 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
         <v>0.1679966400671987</v>
       </c>
-      <c r="F43" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
-        <v>0</v>
-      </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
@@ -5106,46 +5106,46 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>0.1679966400671987</v>
       </c>
       <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>1.007979840403192</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
         <v>0.04199916001679967</v>
       </c>
-      <c r="N43" t="n">
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>4.262914741705166</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0.02099958000839983</v>
+      </c>
+      <c r="X43" t="n">
         <v>0.2099958000839983</v>
       </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" t="n">
-        <v>0</v>
-      </c>
-      <c r="U43" t="n">
-        <v>0</v>
-      </c>
-      <c r="V43" t="n">
-        <v>4.262914741705166</v>
-      </c>
-      <c r="W43" t="n">
-        <v>0</v>
-      </c>
-      <c r="X43" t="n">
-        <v>0</v>
-      </c>
       <c r="Y43" t="n">
-        <v>0.1679966400671987</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
         <v>0</v>
@@ -5154,7 +5154,7 @@
         <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.02099958000839983</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5172,7 +5172,7 @@
         <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.007979840403192</v>
+        <v>0</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -5224,7 +5224,7 @@
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>0.1675206937327552</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
@@ -5239,13 +5239,13 @@
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>0.04927079227433977</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>0.04927079227433977</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
         <v>0</v>
@@ -5281,7 +5281,7 @@
         <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>0.1675206937327552</v>
+        <v>0</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -5348,13 +5348,13 @@
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="U45" t="n">
         <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
         <v>0</v>
@@ -5421,11 +5421,11 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
         <v>0.001347581764523563</v>
       </c>
-      <c r="I46" t="n">
-        <v>0</v>
-      </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
@@ -5436,7 +5436,7 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>0.001347581764523563</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
@@ -5472,10 +5472,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.001347581764523563</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>0.03638470764213619</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -5496,7 +5496,7 @@
         <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.03638470764213619</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="n">
         <v>0</v>
@@ -5575,7 +5575,7 @@
         <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>0.004311273981461522</v>
       </c>
       <c r="X47" t="n">
         <v>0</v>
@@ -5590,7 +5590,7 @@
         <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>0.004311273981461522</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -5627,97 +5627,97 @@
         <v>3</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>0.005966349787200191</v>
       </c>
       <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.04773079829760152</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.001988783262400064</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
         <v>0.02585418241120083</v>
       </c>
-      <c r="F48" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" t="n">
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>1.25293345531204</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0.09745037985760312</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" t="n">
+        <v>0.5568593134720178</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>0.005966349787200191</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>0.01193269957440038</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="n">
         <v>0.003977566524800128</v>
       </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" t="n">
-        <v>0.5568593134720178</v>
-      </c>
-      <c r="O48" t="n">
-        <v>0.005966349787200191</v>
-      </c>
-      <c r="P48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" t="n">
-        <v>0</v>
-      </c>
-      <c r="U48" t="n">
-        <v>0</v>
-      </c>
-      <c r="V48" t="n">
-        <v>0.09745037985760312</v>
-      </c>
-      <c r="W48" t="n">
-        <v>0</v>
-      </c>
-      <c r="X48" t="n">
-        <v>0.01193269957440038</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>0.04773079829760152</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>0.001988783262400064</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>0</v>
-      </c>
       <c r="AF48" t="n">
         <v>0</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.005966349787200191</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.25293345531204</v>
+        <v>0</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -5769,7 +5769,7 @@
         <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>0.01404889013767912</v>
       </c>
       <c r="P49" t="n">
         <v>0</v>
@@ -5784,13 +5784,13 @@
         <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>0.1264400112391121</v>
       </c>
       <c r="U49" t="n">
         <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>0.1264400112391121</v>
+        <v>0</v>
       </c>
       <c r="W49" t="n">
         <v>0</v>
@@ -5826,7 +5826,7 @@
         <v>0</v>
       </c>
       <c r="AH49" t="n">
-        <v>0.01404889013767912</v>
+        <v>0</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
@@ -5893,13 +5893,13 @@
         <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="U50" t="n">
         <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="W50" t="n">
         <v>0</v>
@@ -5972,31 +5972,31 @@
         <v>0</v>
       </c>
       <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
         <v>0.04099598670866957</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" t="n">
-        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -6063,97 +6063,97 @@
         <v>2</v>
       </c>
       <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0.01273143938016078</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" t="n">
+        <v>0</v>
+      </c>
+      <c r="W52" t="n">
+        <v>0</v>
+      </c>
+      <c r="X52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>0.003637554108617366</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="n">
         <v>0.005456331162926049</v>
-      </c>
-      <c r="E52" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" t="n">
-        <v>0</v>
-      </c>
-      <c r="G52" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" t="n">
-        <v>0</v>
-      </c>
-      <c r="O52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
-      <c r="R52" t="n">
-        <v>0</v>
-      </c>
-      <c r="S52" t="n">
-        <v>0</v>
-      </c>
-      <c r="T52" t="n">
-        <v>0</v>
-      </c>
-      <c r="U52" t="n">
-        <v>0</v>
-      </c>
-      <c r="V52" t="n">
-        <v>0</v>
-      </c>
-      <c r="W52" t="n">
-        <v>0</v>
-      </c>
-      <c r="X52" t="n">
-        <v>0.003637554108617366</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE52" t="n">
-        <v>0.01273143938016078</v>
-      </c>
-      <c r="AF52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH52" t="n">
-        <v>0</v>
       </c>
       <c r="AI52" t="n">
         <v>0</v>
@@ -6187,10 +6187,10 @@
         <v>0.0007963178263708611</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>0.001194476739556292</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>0.0003981589131854306</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
@@ -6199,7 +6199,7 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>0.0007963178263708611</v>
       </c>
       <c r="N53" t="n">
         <v>0</v>
@@ -6211,7 +6211,7 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.0007963178263708611</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
@@ -6235,7 +6235,7 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>0.001194476739556292</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
         <v>0</v>
@@ -6247,7 +6247,7 @@
         <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>0.0003981589131854306</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
         <v>0</v>
@@ -6347,7 +6347,7 @@
         <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>0.264812975835816</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -6368,7 +6368,7 @@
         <v>0</v>
       </c>
       <c r="AG54" t="n">
-        <v>0.264812975835816</v>
+        <v>0</v>
       </c>
       <c r="AH54" t="n">
         <v>0</v>
@@ -6402,28 +6402,28 @@
         <v>0</v>
       </c>
       <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
         <v>0.001908396946564886</v>
       </c>
-      <c r="I55" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" t="n">
-        <v>0</v>
-      </c>
       <c r="N55" t="n">
         <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>0.005725190839694656</v>
       </c>
       <c r="P55" t="n">
         <v>0</v>
@@ -6480,7 +6480,7 @@
         <v>0</v>
       </c>
       <c r="AH55" t="n">
-        <v>0.005725190839694656</v>
+        <v>0</v>
       </c>
       <c r="AI55" t="n">
         <v>0</v>
@@ -6511,28 +6511,28 @@
         <v>0</v>
       </c>
       <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
         <v>0.01744652639659444</v>
       </c>
-      <c r="I56" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" t="n">
-        <v>0</v>
-      </c>
       <c r="N56" t="n">
         <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>0.003489305279318887</v>
       </c>
       <c r="P56" t="n">
         <v>0</v>
@@ -6589,7 +6589,7 @@
         <v>0</v>
       </c>
       <c r="AH56" t="n">
-        <v>0.003489305279318887</v>
+        <v>0</v>
       </c>
       <c r="AI56" t="n">
         <v>0</v>
@@ -6608,97 +6608,97 @@
         <v>3</v>
       </c>
       <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.1723442176413222</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0.9390658102700339</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0.01849547701516629</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" t="n">
+        <v>0</v>
+      </c>
+      <c r="W57" t="n">
+        <v>0</v>
+      </c>
+      <c r="X57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>0.09247738507583145</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH57" t="n">
         <v>0.03110602952550695</v>
-      </c>
-      <c r="E57" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" t="n">
-        <v>0</v>
-      </c>
-      <c r="G57" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
-      <c r="R57" t="n">
-        <v>0</v>
-      </c>
-      <c r="S57" t="n">
-        <v>0</v>
-      </c>
-      <c r="T57" t="n">
-        <v>0</v>
-      </c>
-      <c r="U57" t="n">
-        <v>0</v>
-      </c>
-      <c r="V57" t="n">
-        <v>0</v>
-      </c>
-      <c r="W57" t="n">
-        <v>0</v>
-      </c>
-      <c r="X57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>0.1723442176413222</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC57" t="n">
-        <v>0.9390658102700339</v>
-      </c>
-      <c r="AD57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG57" t="n">
-        <v>0.09247738507583145</v>
-      </c>
-      <c r="AH57" t="n">
-        <v>0.01849547701516629</v>
       </c>
       <c r="AI57" t="n">
         <v>0</v>
@@ -6717,89 +6717,89 @@
         <v>1</v>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>0.07710100231303006</v>
       </c>
       <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>1.264456437933693</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
         <v>0.01542020046260601</v>
       </c>
-      <c r="F58" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" t="n">
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0.2158828064764842</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="n">
         <v>0.01542020046260601</v>
       </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" t="n">
+      <c r="R58" t="n">
         <v>0.04626060138781804</v>
       </c>
-      <c r="K58" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" t="n">
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>0.06168080185042405</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" t="n">
+        <v>0</v>
+      </c>
+      <c r="W58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X58" t="n">
+        <v>0.1233616037008481</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC58" t="n">
         <v>0.01542020046260601</v>
       </c>
-      <c r="N58" t="n">
-        <v>0.1233616037008481</v>
-      </c>
-      <c r="O58" t="n">
-        <v>0.07710100231303006</v>
-      </c>
-      <c r="P58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
-      <c r="R58" t="n">
-        <v>0</v>
-      </c>
-      <c r="S58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T58" t="n">
-        <v>0</v>
-      </c>
-      <c r="U58" t="n">
-        <v>0</v>
-      </c>
-      <c r="V58" t="n">
-        <v>0.06168080185042405</v>
-      </c>
-      <c r="W58" t="n">
-        <v>0</v>
-      </c>
-      <c r="X58" t="n">
+      <c r="AD58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="n">
         <v>0.01542020046260601</v>
       </c>
-      <c r="Y58" t="n">
-        <v>1.264456437933693</v>
-      </c>
-      <c r="Z58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE58" t="n">
-        <v>0</v>
-      </c>
       <c r="AF58" t="n">
         <v>0</v>
       </c>
@@ -6807,7 +6807,7 @@
         <v>0</v>
       </c>
       <c r="AH58" t="n">
-        <v>0.2158828064764842</v>
+        <v>0</v>
       </c>
       <c r="AI58" t="n">
         <v>0</v>
@@ -6829,97 +6829,97 @@
         <v>0</v>
       </c>
       <c r="E59" t="n">
+        <v>0.1152737752161383</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.03842459173871278</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
+        <v>1.364073006724304</v>
+      </c>
+      <c r="J59" t="n">
+        <v>3.150816522574448</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
         <v>2.708933717579251</v>
       </c>
-      <c r="F59" t="n">
-        <v>0</v>
-      </c>
-      <c r="G59" t="n">
+      <c r="M59" t="n">
+        <v>1.325648414985591</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0.01921229586935639</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" t="n">
+        <v>0.1152737752161383</v>
+      </c>
+      <c r="W59" t="n">
+        <v>0.1536983669548511</v>
+      </c>
+      <c r="X59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>0.07684918347742556</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="n">
         <v>8.93371757925072</v>
       </c>
-      <c r="H59" t="n">
-        <v>1.325648414985591</v>
-      </c>
-      <c r="I59" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" t="n">
-        <v>0</v>
-      </c>
-      <c r="K59" t="n">
+      <c r="AF59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI59" t="n">
         <v>0.01921229586935639</v>
-      </c>
-      <c r="L59" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" t="n">
-        <v>0</v>
-      </c>
-      <c r="O59" t="n">
-        <v>0</v>
-      </c>
-      <c r="P59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
-      <c r="R59" t="n">
-        <v>0.1152737752161383</v>
-      </c>
-      <c r="S59" t="n">
-        <v>0</v>
-      </c>
-      <c r="T59" t="n">
-        <v>0.1152737752161383</v>
-      </c>
-      <c r="U59" t="n">
-        <v>0</v>
-      </c>
-      <c r="V59" t="n">
-        <v>0</v>
-      </c>
-      <c r="W59" t="n">
-        <v>0.07684918347742556</v>
-      </c>
-      <c r="X59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y59" t="n">
-        <v>1.364073006724304</v>
-      </c>
-      <c r="Z59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB59" t="n">
-        <v>0.1536983669548511</v>
-      </c>
-      <c r="AC59" t="n">
-        <v>3.150816522574448</v>
-      </c>
-      <c r="AD59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE59" t="n">
-        <v>0.01921229586935639</v>
-      </c>
-      <c r="AF59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI59" t="n">
-        <v>0.03842459173871278</v>
       </c>
     </row>
     <row r="60">
@@ -6935,100 +6935,100 @@
         <v>1</v>
       </c>
       <c r="D60" t="n">
-        <v>0.05255228952808044</v>
+        <v>0.007006971937077392</v>
       </c>
       <c r="E60" t="n">
-        <v>3.051536278597204</v>
+        <v>0.2032021861752444</v>
       </c>
       <c r="F60" t="n">
         <v>0.1681673264898574</v>
       </c>
       <c r="G60" t="n">
+        <v>0.1086080650246996</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
+        <v>1.261254948673931</v>
+      </c>
+      <c r="J60" t="n">
+        <v>3.619101005500473</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0.003503485968538696</v>
+      </c>
+      <c r="L60" t="n">
+        <v>3.051536278597204</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0.9459412115054479</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0.04204183162246435</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0.01051045790561609</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0.007006971937077392</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0.02102091581123218</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" t="n">
+        <v>0.07006971937077391</v>
+      </c>
+      <c r="W60" t="n">
+        <v>0.1331324668044704</v>
+      </c>
+      <c r="X60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>0.003503485968538696</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>0.03503485968538696</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>0.04204183162246435</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>0.003503485968538696</v>
+      </c>
+      <c r="AE60" t="n">
         <v>10.57352065304979</v>
       </c>
-      <c r="H60" t="n">
-        <v>0.9459412115054479</v>
-      </c>
-      <c r="I60" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" t="n">
+      <c r="AF60" t="n">
+        <v>0.003503485968538696</v>
+      </c>
+      <c r="AG60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH60" t="n">
+        <v>0.05255228952808044</v>
+      </c>
+      <c r="AI60" t="n">
         <v>0.02102091581123218</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0.02102091581123218</v>
-      </c>
-      <c r="L60" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" t="n">
-        <v>0.007006971937077392</v>
-      </c>
-      <c r="N60" t="n">
-        <v>0</v>
-      </c>
-      <c r="O60" t="n">
-        <v>0.007006971937077392</v>
-      </c>
-      <c r="P60" t="n">
-        <v>0.003503485968538696</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
-      <c r="R60" t="n">
-        <v>0.07006971937077391</v>
-      </c>
-      <c r="S60" t="n">
-        <v>0.003503485968538696</v>
-      </c>
-      <c r="T60" t="n">
-        <v>0.2032021861752444</v>
-      </c>
-      <c r="U60" t="n">
-        <v>0.003503485968538696</v>
-      </c>
-      <c r="V60" t="n">
-        <v>0</v>
-      </c>
-      <c r="W60" t="n">
-        <v>0.04204183162246435</v>
-      </c>
-      <c r="X60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y60" t="n">
-        <v>1.261254948673931</v>
-      </c>
-      <c r="Z60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA60" t="n">
-        <v>0.003503485968538696</v>
-      </c>
-      <c r="AB60" t="n">
-        <v>0.1331324668044704</v>
-      </c>
-      <c r="AC60" t="n">
-        <v>3.619101005500473</v>
-      </c>
-      <c r="AD60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE60" t="n">
-        <v>0.01051045790561609</v>
-      </c>
-      <c r="AF60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG60" t="n">
-        <v>0.03503485968538696</v>
-      </c>
-      <c r="AH60" t="n">
-        <v>0.04204183162246435</v>
-      </c>
-      <c r="AI60" t="n">
-        <v>0.1086080650246996</v>
       </c>
     </row>
     <row r="61">
@@ -7044,79 +7044,79 @@
         <v>1</v>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>0.003558845510516389</v>
       </c>
       <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.05872095092352041</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0.005338268265774583</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
         <v>0.03380903234990569</v>
       </c>
-      <c r="F61" t="n">
-        <v>0</v>
-      </c>
-      <c r="G61" t="n">
-        <v>0</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" t="n">
-        <v>0</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" t="n">
-        <v>0</v>
-      </c>
       <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0.5195914445353927</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="n">
         <v>0.005338268265774583</v>
       </c>
-      <c r="N61" t="n">
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>0.1334567066443646</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V61" t="n">
+        <v>0</v>
+      </c>
+      <c r="W61" t="n">
+        <v>0.003558845510516389</v>
+      </c>
+      <c r="X61" t="n">
         <v>0.09786825153920069</v>
       </c>
-      <c r="O61" t="n">
+      <c r="Y61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z61" t="n">
         <v>0.003558845510516389</v>
       </c>
-      <c r="P61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
-      <c r="R61" t="n">
-        <v>0</v>
-      </c>
-      <c r="S61" t="n">
-        <v>0</v>
-      </c>
-      <c r="T61" t="n">
-        <v>0</v>
-      </c>
-      <c r="U61" t="n">
-        <v>0</v>
-      </c>
-      <c r="V61" t="n">
-        <v>0.1334567066443646</v>
-      </c>
-      <c r="W61" t="n">
-        <v>0</v>
-      </c>
-      <c r="X61" t="n">
-        <v>0.005338268265774583</v>
-      </c>
-      <c r="Y61" t="n">
-        <v>0.05872095092352041</v>
-      </c>
-      <c r="Z61" t="n">
-        <v>0</v>
-      </c>
       <c r="AA61" t="n">
         <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>0.003558845510516389</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
         <v>0.005338268265774583</v>
@@ -7131,10 +7131,10 @@
         <v>0</v>
       </c>
       <c r="AG61" t="n">
-        <v>0.003558845510516389</v>
+        <v>0</v>
       </c>
       <c r="AH61" t="n">
-        <v>0.5195914445353927</v>
+        <v>0</v>
       </c>
       <c r="AI61" t="n">
         <v>0</v>
@@ -7153,100 +7153,100 @@
         <v>2</v>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
+        <v>0.07437709185570844</v>
       </c>
       <c r="E62" t="n">
-        <v>0.2789140944589066</v>
+        <v>0</v>
       </c>
       <c r="F62" t="n">
         <v>0.05578281889178133</v>
       </c>
       <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.3904797322424693</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0.3161026403867608</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0.2789140944589066</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0.2975083674228338</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0.01859427296392711</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" t="n">
+        <v>0.1115656377835627</v>
+      </c>
+      <c r="W62" t="n">
+        <v>0.03718854592785422</v>
+      </c>
+      <c r="X62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>0.03718854592785422</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>0.05578281889178133</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="n">
         <v>0.7809594644849386</v>
       </c>
-      <c r="H62" t="n">
-        <v>0.2975083674228338</v>
-      </c>
-      <c r="I62" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" t="n">
-        <v>0</v>
-      </c>
-      <c r="K62" t="n">
+      <c r="AF62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI62" t="n">
         <v>0.05578281889178133</v>
-      </c>
-      <c r="L62" t="n">
-        <v>0</v>
-      </c>
-      <c r="M62" t="n">
-        <v>0</v>
-      </c>
-      <c r="N62" t="n">
-        <v>0</v>
-      </c>
-      <c r="O62" t="n">
-        <v>0.07437709185570844</v>
-      </c>
-      <c r="P62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
-      <c r="R62" t="n">
-        <v>0.1115656377835627</v>
-      </c>
-      <c r="S62" t="n">
-        <v>0.03718854592785422</v>
-      </c>
-      <c r="T62" t="n">
-        <v>0</v>
-      </c>
-      <c r="U62" t="n">
-        <v>0</v>
-      </c>
-      <c r="V62" t="n">
-        <v>0</v>
-      </c>
-      <c r="W62" t="n">
-        <v>0.05578281889178133</v>
-      </c>
-      <c r="X62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y62" t="n">
-        <v>0.3904797322424693</v>
-      </c>
-      <c r="Z62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB62" t="n">
-        <v>0.03718854592785422</v>
-      </c>
-      <c r="AC62" t="n">
-        <v>0.3161026403867608</v>
-      </c>
-      <c r="AD62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE62" t="n">
-        <v>0.01859427296392711</v>
-      </c>
-      <c r="AF62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI62" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -7262,100 +7262,100 @@
         <v>2</v>
       </c>
       <c r="D63" t="n">
-        <v>0.00436109899694723</v>
+        <v>0.008722197993894461</v>
       </c>
       <c r="E63" t="n">
-        <v>0.3576101177496729</v>
+        <v>0.02616659398168339</v>
       </c>
       <c r="F63" t="n">
         <v>0.06541648495420846</v>
       </c>
       <c r="G63" t="n">
+        <v>0.04797208896641954</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.5276929786306149</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0.4491931966855648</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0.3576101177496729</v>
+      </c>
+      <c r="M63" t="n">
+        <v>1.142607937200175</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0.00436109899694723</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" t="n">
+        <v>0.01308329699084169</v>
+      </c>
+      <c r="W63" t="n">
+        <v>0.07849978194505015</v>
+      </c>
+      <c r="X63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>0.00436109899694723</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>0.00436109899694723</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>0.01308329699084169</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="n">
         <v>1.626689925861317</v>
       </c>
-      <c r="H63" t="n">
-        <v>1.142607937200175</v>
-      </c>
-      <c r="I63" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" t="n">
-        <v>0.02616659398168339</v>
-      </c>
-      <c r="L63" t="n">
-        <v>0</v>
-      </c>
-      <c r="M63" t="n">
-        <v>0</v>
-      </c>
-      <c r="N63" t="n">
-        <v>0</v>
-      </c>
-      <c r="O63" t="n">
-        <v>0.008722197993894461</v>
-      </c>
-      <c r="P63" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
-      <c r="R63" t="n">
-        <v>0.01308329699084169</v>
-      </c>
-      <c r="S63" t="n">
-        <v>0.00436109899694723</v>
-      </c>
-      <c r="T63" t="n">
-        <v>0.02616659398168339</v>
-      </c>
-      <c r="U63" t="n">
-        <v>0</v>
-      </c>
-      <c r="V63" t="n">
-        <v>0</v>
-      </c>
-      <c r="W63" t="n">
-        <v>0.01308329699084169</v>
-      </c>
-      <c r="X63" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y63" t="n">
-        <v>0.5276929786306149</v>
-      </c>
-      <c r="Z63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB63" t="n">
-        <v>0.07849978194505015</v>
-      </c>
-      <c r="AC63" t="n">
-        <v>0.4491931966855648</v>
-      </c>
-      <c r="AD63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE63" t="n">
-        <v>0</v>
-      </c>
       <c r="AF63" t="n">
         <v>0</v>
       </c>
       <c r="AG63" t="n">
-        <v>0.00436109899694723</v>
+        <v>0</v>
       </c>
       <c r="AH63" t="n">
         <v>0.00436109899694723</v>
       </c>
       <c r="AI63" t="n">
-        <v>0.04797208896641954</v>
+        <v>0.02616659398168339</v>
       </c>
     </row>
     <row r="64">
@@ -7371,100 +7371,100 @@
         <v>2</v>
       </c>
       <c r="D64" t="n">
-        <v>0.02311604253351826</v>
+        <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>0.4160887656033287</v>
+        <v>0</v>
       </c>
       <c r="F64" t="n">
         <v>0.1618122977346279</v>
       </c>
       <c r="G64" t="n">
+        <v>0.02311604253351826</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.6472491909385114</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0.3929727230698105</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0.4160887656033287</v>
+      </c>
+      <c r="M64" t="n">
+        <v>1.109570041608877</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0.04623208506703652</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" t="n">
+        <v>0.02311604253351826</v>
+      </c>
+      <c r="W64" t="n">
+        <v>0.1386962552011096</v>
+      </c>
+      <c r="X64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>0.02311604253351826</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>0.02311604253351826</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="n">
         <v>1.363846509477578</v>
       </c>
-      <c r="H64" t="n">
-        <v>1.109570041608877</v>
-      </c>
-      <c r="I64" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" t="n">
-        <v>0</v>
-      </c>
-      <c r="K64" t="n">
+      <c r="AF64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH64" t="n">
+        <v>0.02311604253351826</v>
+      </c>
+      <c r="AI64" t="n">
         <v>0.04623208506703652</v>
-      </c>
-      <c r="L64" t="n">
-        <v>0</v>
-      </c>
-      <c r="M64" t="n">
-        <v>0.04623208506703652</v>
-      </c>
-      <c r="N64" t="n">
-        <v>0</v>
-      </c>
-      <c r="O64" t="n">
-        <v>0</v>
-      </c>
-      <c r="P64" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
-      <c r="R64" t="n">
-        <v>0.02311604253351826</v>
-      </c>
-      <c r="S64" t="n">
-        <v>0</v>
-      </c>
-      <c r="T64" t="n">
-        <v>0</v>
-      </c>
-      <c r="U64" t="n">
-        <v>0</v>
-      </c>
-      <c r="V64" t="n">
-        <v>0</v>
-      </c>
-      <c r="W64" t="n">
-        <v>0.02311604253351826</v>
-      </c>
-      <c r="X64" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y64" t="n">
-        <v>0.6472491909385114</v>
-      </c>
-      <c r="Z64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB64" t="n">
-        <v>0.1386962552011096</v>
-      </c>
-      <c r="AC64" t="n">
-        <v>0.3929727230698105</v>
-      </c>
-      <c r="AD64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG64" t="n">
-        <v>0.02311604253351826</v>
-      </c>
-      <c r="AH64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI64" t="n">
-        <v>0.02311604253351826</v>
       </c>
     </row>
     <row r="65">
@@ -7492,22 +7492,22 @@
         <v>0</v>
       </c>
       <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
         <v>7.76</v>
-      </c>
-      <c r="I65" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" t="n">
-        <v>0</v>
-      </c>
-      <c r="K65" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" t="n">
-        <v>0</v>
-      </c>
-      <c r="M65" t="n">
-        <v>0</v>
       </c>
       <c r="N65" t="n">
         <v>0</v>
@@ -7589,7 +7589,7 @@
         <v>2</v>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>0.05443658138268917</v>
       </c>
       <c r="E66" t="n">
         <v>0</v>
@@ -7598,80 +7598,80 @@
         <v>0</v>
       </c>
       <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.1088731627653783</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0.1633097441480675</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0.2721829069134458</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0.326619488296135</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>0.5443658138268916</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
+      </c>
+      <c r="V66" t="n">
+        <v>0</v>
+      </c>
+      <c r="W66" t="n">
+        <v>0</v>
+      </c>
+      <c r="X66" t="n">
+        <v>0.1633097441480675</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC66" t="n">
         <v>0.05443658138268917</v>
       </c>
-      <c r="H66" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" t="n">
-        <v>0</v>
-      </c>
-      <c r="K66" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" t="n">
-        <v>0</v>
-      </c>
-      <c r="M66" t="n">
-        <v>0.326619488296135</v>
-      </c>
-      <c r="N66" t="n">
-        <v>0.1633097441480675</v>
-      </c>
-      <c r="O66" t="n">
+      <c r="AD66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="n">
         <v>0.05443658138268917</v>
       </c>
-      <c r="P66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
-      <c r="R66" t="n">
-        <v>0</v>
-      </c>
-      <c r="S66" t="n">
-        <v>0</v>
-      </c>
-      <c r="T66" t="n">
-        <v>0</v>
-      </c>
-      <c r="U66" t="n">
-        <v>0</v>
-      </c>
-      <c r="V66" t="n">
-        <v>0.5443658138268916</v>
-      </c>
-      <c r="W66" t="n">
-        <v>0</v>
-      </c>
-      <c r="X66" t="n">
-        <v>0.05443658138268917</v>
-      </c>
-      <c r="Y66" t="n">
-        <v>0.1088731627653783</v>
-      </c>
-      <c r="Z66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC66" t="n">
-        <v>0.1633097441480675</v>
-      </c>
-      <c r="AD66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE66" t="n">
-        <v>0</v>
-      </c>
       <c r="AF66" t="n">
         <v>0</v>
       </c>
@@ -7679,7 +7679,7 @@
         <v>0</v>
       </c>
       <c r="AH66" t="n">
-        <v>0.2721829069134458</v>
+        <v>0</v>
       </c>
       <c r="AI66" t="n">
         <v>0</v>
@@ -7710,22 +7710,22 @@
         <v>0</v>
       </c>
       <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="n">
         <v>2.18</v>
-      </c>
-      <c r="I67" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" t="n">
-        <v>0</v>
-      </c>
-      <c r="K67" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" t="n">
-        <v>0</v>
-      </c>
-      <c r="M67" t="n">
-        <v>0</v>
       </c>
       <c r="N67" t="n">
         <v>0</v>
@@ -7807,7 +7807,7 @@
         <v>3</v>
       </c>
       <c r="D68" t="n">
-        <v>0</v>
+        <v>0.05374242720343951</v>
       </c>
       <c r="E68" t="n">
         <v>0</v>
@@ -7819,28 +7819,28 @@
         <v>0</v>
       </c>
       <c r="H68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="n">
         <v>0.0293140512018761</v>
       </c>
-      <c r="I68" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" t="n">
-        <v>0</v>
-      </c>
-      <c r="K68" t="n">
-        <v>0</v>
-      </c>
-      <c r="L68" t="n">
-        <v>0</v>
-      </c>
-      <c r="M68" t="n">
-        <v>0</v>
-      </c>
       <c r="N68" t="n">
         <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>0.05374242720343951</v>
+        <v>0</v>
       </c>
       <c r="P68" t="n">
         <v>0</v>
@@ -7885,16 +7885,16 @@
         <v>0</v>
       </c>
       <c r="AD68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="n">
         <v>0.01465702560093805</v>
-      </c>
-      <c r="AE68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG68" t="n">
-        <v>0</v>
       </c>
       <c r="AH68" t="n">
         <v>0</v>
@@ -7916,7 +7916,7 @@
         <v>3</v>
       </c>
       <c r="D69" t="n">
-        <v>0</v>
+        <v>0.6298629121896998</v>
       </c>
       <c r="E69" t="n">
         <v>0</v>
@@ -7934,32 +7934,32 @@
         <v>0</v>
       </c>
       <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" t="n">
         <v>0.005292965648652941</v>
       </c>
-      <c r="K69" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" t="n">
-        <v>0</v>
-      </c>
-      <c r="M69" t="n">
-        <v>0</v>
-      </c>
-      <c r="N69" t="n">
-        <v>0</v>
-      </c>
-      <c r="O69" t="n">
-        <v>0.6298629121896998</v>
-      </c>
-      <c r="P69" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
-      <c r="R69" t="n">
-        <v>0</v>
-      </c>
       <c r="S69" t="n">
         <v>0</v>
       </c>
@@ -7976,34 +7976,34 @@
         <v>0</v>
       </c>
       <c r="X69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC69" t="n">
         <v>0.02117186259461176</v>
       </c>
-      <c r="Y69" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC69" t="n">
-        <v>0</v>
-      </c>
       <c r="AD69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="n">
         <v>0.01058593129730588</v>
-      </c>
-      <c r="AE69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG69" t="n">
-        <v>0</v>
       </c>
       <c r="AH69" t="n">
         <v>0</v>
@@ -8037,23 +8037,23 @@
         <v>0</v>
       </c>
       <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="n">
         <v>5.23</v>
       </c>
-      <c r="I70" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" t="n">
-        <v>0</v>
-      </c>
-      <c r="L70" t="n">
-        <v>0</v>
-      </c>
-      <c r="M70" t="n">
-        <v>0</v>
-      </c>
       <c r="N70" t="n">
         <v>0</v>
       </c>
@@ -8088,7 +8088,7 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>5.11</v>
+        <v>0</v>
       </c>
       <c r="Z70" t="n">
         <v>0</v>
@@ -8143,13 +8143,13 @@
         <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -8197,7 +8197,7 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z71" t="n">
         <v>0</v>
@@ -8227,7 +8227,7 @@
         <v>0</v>
       </c>
       <c r="AI71" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/OLS_all.xlsx
+++ b/data/OLS_all.xlsx
@@ -441,162 +441,162 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>494</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>428</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>584</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>426</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>605</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>871</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>410</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>470</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>771</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>605</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>334</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>771</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>549</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>712</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>541</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>565</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>625</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>541</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>871</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>91</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>410</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>657</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>725</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>337</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>799</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>342</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>426</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>678</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>584</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>428</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>494</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>712</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>565</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>79</t>
         </is>
       </c>
     </row>
@@ -616,10 +616,10 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>0.2800517018526497</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6247307195174493</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0.02154243860404998</v>
@@ -628,82 +628,82 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.6247307195174493</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
         <v>0.2154243860404998</v>
       </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.1723395088323998</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
         <v>0.1938819474364498</v>
       </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
         <v>0.4523912106850495</v>
       </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0.2800517018526497</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
       <c r="AH2" t="n">
-        <v>0.1723395088323998</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -725,94 +725,94 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1.233162587744261</v>
       </c>
       <c r="F3" t="n">
+        <v>0.01897173211914248</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
         <v>0.834756213242269</v>
       </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
         <v>0.3035477139062797</v>
       </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.2466325175488522</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
         <v>0.1138303927148549</v>
       </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
         <v>0.3035477139062797</v>
       </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.233162587744261</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0.01897173211914248</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
       <c r="AH3" t="n">
-        <v>0.2466325175488522</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -834,94 +834,94 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>0.3068990915786889</v>
       </c>
       <c r="F4" t="n">
+        <v>0.01227596366314756</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.07365578197888534</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.02455192732629511</v>
+      </c>
+      <c r="K4" t="n">
         <v>0.7979376381045912</v>
       </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0.3068990915786889</v>
       </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
         <v>0.01227596366314756</v>
       </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.01227596366314756</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.01227596366314756</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.485391603240855</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
         <v>0.2332433095998036</v>
       </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
         <v>3.584581389639087</v>
       </c>
-      <c r="R4" t="n">
+      <c r="AH4" t="n">
         <v>0.01227596366314756</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.02455192732629511</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.07365578197888534</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0.3068990915786889</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0.01227596366314756</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0.01227596366314756</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0.01227596366314756</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.485391603240855</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -940,97 +940,97 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>0.002203759613901316</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>2.201555854287414</v>
       </c>
       <c r="F5" t="n">
-        <v>1.439055027877559</v>
+        <v>0.01542631729730921</v>
       </c>
       <c r="G5" t="n">
         <v>0.002203759613901316</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>0.002203759613901316</v>
       </c>
       <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.006611278841703947</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.439055027877559</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
         <v>0.2291909998457368</v>
       </c>
-      <c r="J5" t="n">
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.02203759613901316</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4.400907948960928</v>
+      </c>
+      <c r="AA5" t="n">
         <v>0.004407519227802631</v>
       </c>
-      <c r="K5" t="n">
-        <v>0.02203759613901316</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
         <v>0.1410406152896842</v>
       </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
         <v>2.053903960156026</v>
       </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0.006611278841703947</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.002203759613901316</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.201555854287414</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0.002203759613901316</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0.01542631729730921</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
       <c r="AH5" t="n">
-        <v>4.400907948960928</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1049,34 +1049,34 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00184060371801951</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00184060371801951</v>
+        <v>0.9147800478556966</v>
       </c>
       <c r="F6" t="n">
-        <v>1.006810233756672</v>
+        <v>0.03313086692435119</v>
       </c>
       <c r="G6" t="n">
         <v>0.003681207436039021</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>0.003681207436039021</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3349898766795509</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>0.007362414872078041</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1.006810233756672</v>
       </c>
       <c r="L6" t="n">
         <v>0.00184060371801951</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2043070127001657</v>
+        <v>0.3349898766795509</v>
       </c>
       <c r="N6" t="n">
         <v>0.00184060371801951</v>
@@ -1088,61 +1088,61 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
+        <v>0.00184060371801951</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.01288422602613657</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.00184060371801951</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.073071967605375</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.00184060371801951</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.2043070127001657</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.003681207436039021</v>
+      </c>
+      <c r="AG6" t="n">
         <v>3.740106755015645</v>
       </c>
-      <c r="R6" t="n">
-        <v>0.01288422602613657</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
         <v>0.007362414872078041</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0.007362414872078041</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.003681207436039021</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0.9147800478556966</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0.03313086692435119</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0.00184060371801951</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.073071967605375</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0.003681207436039021</v>
       </c>
     </row>
     <row r="7">
@@ -1270,94 +1270,94 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>0.2303868073238753</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4995756032496665</v>
+        <v>0.007275372862859222</v>
       </c>
       <c r="G8" t="n">
         <v>0.01455074572571844</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>0.004850248575239481</v>
       </c>
       <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.4995756032496665</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>0.2012853158724384</v>
       </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.009700497150478962</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.3904450103067782</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
         <v>0.2182611858857766</v>
       </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.00242512428761974</v>
+      </c>
+      <c r="AG8" t="n">
         <v>0.4680489875106099</v>
       </c>
-      <c r="R8" t="n">
-        <v>0.009700497150478962</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0.00242512428761974</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0.004850248575239481</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0.2303868073238753</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0.007275372862859222</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
       <c r="AH8" t="n">
-        <v>0.3904450103067782</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0.00242512428761974</v>
@@ -1485,100 +1485,100 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.2590210789567703</v>
+      </c>
+      <c r="F10" t="n">
         <v>0.005954507562224604</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.01488626890556151</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.008931761343336906</v>
+      </c>
+      <c r="K10" t="n">
         <v>1.155174467071573</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.4138382755746099</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0.002977253781112302</v>
       </c>
       <c r="M10" t="n">
+        <v>0.4138382755746099</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.005954507562224604</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.005954507562224604</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.3751339764201501</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
         <v>0.2768846016434441</v>
       </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
         <v>0.3989520066690485</v>
       </c>
-      <c r="R10" t="n">
-        <v>0.005954507562224604</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0.008931761343336906</v>
-      </c>
-      <c r="W10" t="n">
+      <c r="AH10" t="n">
+        <v>0.002977253781112302</v>
+      </c>
+      <c r="AI10" t="n">
         <v>0.06549958318447065</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0.01488626890556151</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0.2590210789567703</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0.002977253781112302</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0.005954507562224604</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0.3751339764201501</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1621,73 +1621,73 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
         <v>2.42</v>
       </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
         <v>0.57</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1706,7 +1706,7 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>0.05116398055768739</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -1718,25 +1718,25 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
+        <v>0.07674597083653108</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
         <v>0.0255819902788437</v>
       </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>11.97237145049885</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -1748,7 +1748,7 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>0.1534919416730622</v>
       </c>
       <c r="T12" t="n">
         <v>0.920951650038373</v>
@@ -1760,43 +1760,43 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>11.97237145049885</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
         <v>0.0255819902788437</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0.07674597083653108</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0.05116398055768739</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0.1534919416730622</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1812,10 +1812,10 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>0.02323660022720231</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>0.002581844469689146</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -1827,10 +1827,10 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1962201796963751</v>
+        <v>0.1187648456057007</v>
       </c>
       <c r="J13" t="n">
-        <v>0.01807291128782402</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1839,25 +1839,25 @@
         <v>0.06712795621191779</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>0.1962201796963751</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1394196013632139</v>
+        <v>0.02323660022720231</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.007745533409067438</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.005163688939378292</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>0.002581844469689146</v>
       </c>
       <c r="T13" t="n">
         <v>0.3020758029536301</v>
@@ -1872,40 +1872,40 @@
         <v>0.005163688939378292</v>
       </c>
       <c r="X13" t="n">
-        <v>0.1187648456057007</v>
+        <v>0.1394196013632139</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.002581844469689146</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>0.01807291128782402</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
       </c>
       <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
         <v>0.02581844469689146</v>
       </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
       <c r="AE13" t="n">
-        <v>0.002581844469689146</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>0.007745533409067438</v>
       </c>
       <c r="AH13" t="n">
         <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>0.005163688939378292</v>
       </c>
     </row>
     <row r="14">
@@ -1921,41 +1921,41 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.03969829297340214</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.05954743946010321</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.1984914648670107</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
         <v>0.6550218340611353</v>
       </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.1984914648670107</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0.8535132989281461</v>
-      </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
@@ -1966,7 +1966,7 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>0.01984914648670107</v>
       </c>
       <c r="T14" t="n">
         <v>0.6947201270345376</v>
@@ -1978,43 +1978,43 @@
         <v>0</v>
       </c>
       <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.8535132989281461</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.03969829297340214</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
         <v>0.01984914648670107</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0.05954743946010321</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0.03969829297340214</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>0.03969829297340214</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>0.01984914648670107</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -2030,40 +2030,40 @@
         <v>3</v>
       </c>
       <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.1847807827985889</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.05039475894506971</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
         <v>0.03359650596337981</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>4.905089870653452</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -2090,13 +2090,13 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.05039475894506971</v>
+        <v>4.905089870653452</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.1847807827985889</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2105,10 +2105,10 @@
         <v>0</v>
       </c>
       <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
         <v>0.520745842432387</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
@@ -2139,40 +2139,40 @@
         <v>3</v>
       </c>
       <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.00962186086789185</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.362166843067449</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.02405465216972963</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
         <v>0.04810930433945925</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.02405465216972963</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>2.732608486481285</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -2193,46 +2193,46 @@
         <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.00962186086789185</v>
       </c>
       <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.732608486481285</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.0577311652073511</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
         <v>0.03367651303762147</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.362166843067449</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0.00962186086789185</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0.00962186086789185</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0.0577311652073511</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2248,41 +2248,41 @@
         <v>3</v>
       </c>
       <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.01221478477549226</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.08550349342844579</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.06107392387746129</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
         <v>0.01710069868568916</v>
       </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.06107392387746129</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0.9258806859823131</v>
-      </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
@@ -2293,7 +2293,7 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>0.01465774173059071</v>
       </c>
       <c r="T17" t="n">
         <v>0.9429813846680022</v>
@@ -2302,46 +2302,46 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.01465774173059071</v>
       </c>
       <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.9258806859823131</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.06595983778765818</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
         <v>0.002442956955098451</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0.08550349342844579</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0.01221478477549226</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0.01465774173059071</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0.06595983778765818</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0.01465774173059071</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2372,7 +2372,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>0.2117522498676549</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2390,7 +2390,7 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0.9528851244044468</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -2417,7 +2417,7 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.2117522498676549</v>
+        <v>0.9528851244044468</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
@@ -2469,10 +2469,10 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>0.1510003775009437</v>
       </c>
       <c r="F19" t="n">
-        <v>1.006669183339625</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
         <v>0.01258336479174531</v>
@@ -2481,85 +2481,85 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.006669183339625</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
         <v>2.705423430225242</v>
       </c>
-      <c r="J19" t="n">
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.06291682395872657</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0.2642506606266515</v>
+      </c>
+      <c r="AA19" t="n">
         <v>0.01258336479174531</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
         <v>1.849754624386561</v>
       </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
         <v>0.01258336479174531</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
         <v>0.1761671070844344</v>
       </c>
-      <c r="R19" t="n">
-        <v>0.06291682395872657</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
         <v>0.01258336479174531</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0.1510003775009437</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>0.2642506606266515</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2590,7 +2590,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>0.0002414916455965206</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2608,34 +2608,34 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
         <v>0.002897899747158247</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0.0002414916455965206</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
@@ -2711,55 +2711,55 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
         <v>0.01444669170759896</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -2793,7 +2793,7 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.002372948388372553</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -2805,13 +2805,13 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.4018192604310856</v>
+        <v>0.01186474194186276</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2950365829543207</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -2826,19 +2826,19 @@
         <v>0.002372948388372553</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>0.002372948388372553</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>0.4018192604310856</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>0.002372948388372553</v>
       </c>
       <c r="S22" t="n">
-        <v>0.002372948388372553</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2856,13 +2856,13 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.01186474194186276</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>0.2950365829543207</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
@@ -2877,7 +2877,7 @@
         <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>0.1494957484674708</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -2886,7 +2886,7 @@
         <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>0.1494957484674708</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2902,41 +2902,41 @@
         <v>3</v>
       </c>
       <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.005098659052669148</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.1325651353693978</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.06118390863202978</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
         <v>0.02804262478968031</v>
       </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.06118390863202978</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0.8999133227961047</v>
-      </c>
       <c r="P23" t="n">
         <v>0</v>
       </c>
@@ -2947,7 +2947,7 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>0.0101973181053383</v>
       </c>
       <c r="T23" t="n">
         <v>1.371539285168001</v>
@@ -2956,46 +2956,46 @@
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.01529597715800744</v>
       </c>
       <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0.8999133227961047</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.03314128384234946</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="n">
         <v>0.1223678172640596</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0.1325651353693978</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>0.005098659052669148</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>0.01529597715800744</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>0.03314128384234946</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>0.0101973181053383</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -3011,41 +3011,41 @@
         <v>2</v>
       </c>
       <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.009720298413161283</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.05346164127238706</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.3669412650968384</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
         <v>0.0461714174625161</v>
       </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.3669412650968384</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>2.605039974727224</v>
-      </c>
       <c r="P24" t="n">
         <v>0</v>
       </c>
@@ -3056,7 +3056,7 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>0.0121503730164516</v>
       </c>
       <c r="T24" t="n">
         <v>3.251439819202449</v>
@@ -3068,43 +3068,43 @@
         <v>0</v>
       </c>
       <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>2.605039974727224</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.06561201428883867</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="n">
         <v>0.01944059682632257</v>
-      </c>
-      <c r="X24" t="n">
-        <v>0.05346164127238706</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>0.009720298413161283</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>0.06561201428883867</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>0.0121503730164516</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -3123,7 +3123,7 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>0.004966229638458482</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3138,7 +3138,7 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0.004966229638458482</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -3147,13 +3147,13 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.09435836313071116</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>0.124155740961462</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -3180,7 +3180,7 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>0.124155740961462</v>
       </c>
       <c r="Y25" t="n">
         <v>0</v>
@@ -3189,17 +3189,17 @@
         <v>0.004966229638458482</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>0.004966229638458482</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
       </c>
       <c r="AC25" t="n">
+        <v>0.09435836313071116</v>
+      </c>
+      <c r="AD25" t="n">
         <v>0.004966229638458482</v>
       </c>
-      <c r="AD25" t="n">
-        <v>0</v>
-      </c>
       <c r="AE25" t="n">
         <v>0</v>
       </c>
@@ -3210,7 +3210,7 @@
         <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>0.004966229638458482</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3229,13 +3229,13 @@
         <v>2</v>
       </c>
       <c r="D26" t="n">
-        <v>0.005749770009199632</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0.03737350505979761</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0.327736890524379</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
         <v>0.0718721251149954</v>
@@ -3244,85 +3244,85 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>0.8825896964121436</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0.4312327506899724</v>
+        <v>0.04024839006439743</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>0.327736890524379</v>
       </c>
       <c r="L26" t="n">
         <v>0.2932382704691812</v>
       </c>
       <c r="M26" t="n">
+        <v>0.8825896964121436</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.005749770009199632</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.03737350505979761</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1.138454461821527</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.02874885004599816</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0.002874885004599816</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0.005749770009199632</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0.4312327506899724</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
         <v>0.8107175712971482</v>
       </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0.02299908003679853</v>
+      </c>
+      <c r="AG26" t="n">
         <v>0.002874885004599816</v>
       </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0.002874885004599816</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0.02874885004599816</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0.04024839006439743</v>
-      </c>
-      <c r="W26" t="n">
+      <c r="AH26" t="n">
+        <v>0.008624655013799448</v>
+      </c>
+      <c r="AI26" t="n">
         <v>0.06324747010119594</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>0.008624655013799448</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.138454461821527</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>0.005749770009199632</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>0.02299908003679853</v>
       </c>
     </row>
     <row r="27">
@@ -3350,64 +3350,64 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.3998310944551476</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
         <v>0.3166978965981368</v>
       </c>
-      <c r="I27" t="n">
-        <v>0.3998310944551476</v>
-      </c>
-      <c r="J27" t="n">
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
         <v>0.001319574569158903</v>
       </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
       <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0.00395872370747671</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
         <v>0.001319574569158903</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0.00395872370747671</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
@@ -3556,100 +3556,100 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>0.01173846695621552</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0.03521540086864655</v>
+        <v>0.03912822318738506</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1486872481120632</v>
+        <v>0.003912822318738506</v>
       </c>
       <c r="G29" t="n">
         <v>1.737293109519897</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>0.05477951246233909</v>
       </c>
       <c r="I29" t="n">
-        <v>7.160464843291465</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0.4617130336111437</v>
+        <v>0.1056462026059397</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>0.1486872481120632</v>
       </c>
       <c r="L29" t="n">
         <v>0.4069335211488046</v>
       </c>
       <c r="M29" t="n">
+        <v>7.160464843291465</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.01173846695621552</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.03521540086864655</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1.475134014164417</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0.1095590249246782</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0.01173846695621552</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0.4617130336111437</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
         <v>5.157099816097351</v>
       </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
         <v>0.01173846695621552</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="AF29" t="n">
+        <v>0.4030206988300661</v>
+      </c>
+      <c r="AG29" t="n">
         <v>0.007825644637477012</v>
       </c>
-      <c r="R29" t="n">
-        <v>0.1095590249246782</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0.1056462026059397</v>
-      </c>
-      <c r="W29" t="n">
+      <c r="AH29" t="n">
+        <v>0.03130257854990805</v>
+      </c>
+      <c r="AI29" t="n">
         <v>1.498610948076848</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>0.05477951246233909</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>0.03912822318738506</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0.03130257854990805</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.475134014164417</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>0.003912822318738506</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>0.01173846695621552</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>0.4030206988300661</v>
       </c>
     </row>
     <row r="30">
@@ -3668,7 +3668,7 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>0.1151410477835348</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -3680,7 +3680,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0.134331222414124</v>
+        <v>1.823066589905968</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3692,22 +3692,22 @@
         <v>0.05757052389176742</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>0.134331222414124</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>0.5757052389176741</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.01919017463058914</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>0.01919017463058914</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -3722,16 +3722,16 @@
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>0.01919017463058914</v>
       </c>
       <c r="X30" t="n">
-        <v>1.823066589905968</v>
+        <v>0.5757052389176741</v>
       </c>
       <c r="Y30" t="n">
         <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.1151410477835348</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -3740,11 +3740,11 @@
         <v>0</v>
       </c>
       <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
         <v>0.268662444828248</v>
       </c>
-      <c r="AD30" t="n">
-        <v>0</v>
-      </c>
       <c r="AE30" t="n">
         <v>0</v>
       </c>
@@ -3752,7 +3752,7 @@
         <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>0.01919017463058914</v>
       </c>
       <c r="AH30" t="n">
         <v>0</v>
@@ -3774,7 +3774,7 @@
         <v>2</v>
       </c>
       <c r="D31" t="n">
-        <v>0.01793239487133507</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -3789,10 +3789,10 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>0.6276338204967273</v>
+        <v>0.1613915538420156</v>
       </c>
       <c r="J31" t="n">
-        <v>0.008966197435667534</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -3801,19 +3801,19 @@
         <v>0.0403478884605039</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>0.6276338204967273</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>0.1748408499955169</v>
+        <v>0.01793239487133507</v>
       </c>
       <c r="P31" t="n">
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.004483098717833767</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -3831,29 +3831,29 @@
         <v>0</v>
       </c>
       <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0.1748408499955169</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
         <v>0.008966197435667534</v>
       </c>
-      <c r="X31" t="n">
-        <v>0.1613915538420156</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0</v>
-      </c>
       <c r="AB31" t="n">
         <v>0</v>
       </c>
       <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="n">
         <v>0.008966197435667534</v>
       </c>
-      <c r="AD31" t="n">
-        <v>0</v>
-      </c>
       <c r="AE31" t="n">
         <v>0</v>
       </c>
@@ -3861,13 +3861,13 @@
         <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>0.004483098717833767</v>
       </c>
       <c r="AH31" t="n">
         <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>0.008966197435667534</v>
       </c>
     </row>
     <row r="32">
@@ -3992,83 +3992,83 @@
         <v>3</v>
       </c>
       <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.02963255630185697</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.01975503753457131</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.009877518767285657</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.0493875938364283</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
         <v>0.09877518767285659</v>
       </c>
-      <c r="E33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0.0493875938364283</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0.0691426313709996</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0.03951007506914263</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0.009877518767285657</v>
+      </c>
+      <c r="AC33" t="n">
         <v>0.1481627815092849</v>
       </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0.0691426313709996</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="n">
-        <v>0.009877518767285657</v>
-      </c>
-      <c r="W33" t="n">
-        <v>0</v>
-      </c>
-      <c r="X33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>0.02963255630185697</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>0</v>
-      </c>
       <c r="AD33" t="n">
         <v>0</v>
       </c>
@@ -4076,13 +4076,13 @@
         <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.01975503753457131</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.009877518767285657</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>0.03951007506914263</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4101,83 +4101,83 @@
         <v>2</v>
       </c>
       <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.6771397616468039</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
         <v>0.1625135427952329</v>
       </c>
-      <c r="E34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0.6771397616468039</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0.9750812567713976</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
         <v>0.5958829902491874</v>
       </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" t="n">
-        <v>0</v>
-      </c>
-      <c r="X34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>0</v>
-      </c>
       <c r="AD34" t="n">
         <v>0</v>
       </c>
@@ -4191,7 +4191,7 @@
         <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>0.9750812567713976</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4243,34 +4243,34 @@
         <v>0</v>
       </c>
       <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
         <v>0.55</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" t="n">
-        <v>0</v>
-      </c>
-      <c r="W35" t="n">
-        <v>0</v>
-      </c>
-      <c r="X35" t="n">
-        <v>0</v>
       </c>
       <c r="Y35" t="n">
         <v>0</v>
@@ -4319,100 +4319,100 @@
         <v>1</v>
       </c>
       <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.432809899413851</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
         <v>0.01447282726680657</v>
       </c>
-      <c r="E36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>1.432809899413851</v>
-      </c>
-      <c r="J36" t="n">
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
         <v>0.003618206816701643</v>
       </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
+      <c r="Z36" t="n">
+        <v>0.2098559953686953</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0.003618206816701643</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
         <v>0.01447282726680657</v>
       </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0.003618206816701643</v>
-      </c>
-      <c r="V36" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" t="n">
+      <c r="AD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="n">
         <v>3.097185035096606</v>
-      </c>
-      <c r="X36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>0.2098559953686953</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -4428,13 +4428,13 @@
         <v>2</v>
       </c>
       <c r="D37" t="n">
-        <v>0.1323348070618665</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>0.006015218502812114</v>
       </c>
       <c r="G37" t="n">
         <v>0.03007609251406057</v>
@@ -4443,85 +4443,85 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.006015218502812114</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
         <v>0.8631838551535385</v>
       </c>
-      <c r="J37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" t="n">
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.1323348070618665</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0.006015218502812114</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0.06917501278233933</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
         <v>0.2917380973863876</v>
       </c>
-      <c r="N37" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0.006015218502812114</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" t="n">
-        <v>0.006015218502812114</v>
-      </c>
-      <c r="W37" t="n">
+      <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0.003007609251406057</v>
+      </c>
+      <c r="AI37" t="n">
         <v>0.0210532647598424</v>
-      </c>
-      <c r="X37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>0.003007609251406057</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>0.006015218502812114</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>0.06917501278233933</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -4537,13 +4537,13 @@
         <v>2</v>
       </c>
       <c r="D38" t="n">
-        <v>0.08154478439559006</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>0.009785374127470806</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>0.006523582751647205</v>
       </c>
       <c r="G38" t="n">
         <v>0.001630895687911801</v>
@@ -4552,85 +4552,85 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.009785374127470806</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
         <v>0.06686672320438386</v>
       </c>
-      <c r="J38" t="n">
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.08154478439559006</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0.04240328788570683</v>
+      </c>
+      <c r="AA38" t="n">
         <v>0.008154478439559005</v>
       </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" t="n">
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
         <v>0.1908147954856807</v>
       </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" t="n">
-        <v>0.009785374127470806</v>
-      </c>
-      <c r="W38" t="n">
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="n">
         <v>0.004892687063735403</v>
-      </c>
-      <c r="X38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>0.009785374127470806</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>0.006523582751647205</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>0.04240328788570683</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -4661,7 +4661,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>0.05782822874277147</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4679,7 +4679,7 @@
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>0.04926108374384236</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
         <v>0</v>
@@ -4706,7 +4706,7 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>0.05782822874277147</v>
+        <v>0.04926108374384236</v>
       </c>
       <c r="Y39" t="n">
         <v>0</v>
@@ -4770,7 +4770,7 @@
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>0.07260318727992159</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>0.1899783400491282</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
         <v>0</v>
@@ -4815,7 +4815,7 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>0.07260318727992159</v>
+        <v>0.1899783400491282</v>
       </c>
       <c r="Y40" t="n">
         <v>0</v>
@@ -5000,73 +5000,73 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" t="n">
         <v>0.007502719735904265</v>
       </c>
-      <c r="N42" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" t="n">
-        <v>0</v>
-      </c>
-      <c r="S42" t="n">
-        <v>0</v>
-      </c>
-      <c r="T42" t="n">
-        <v>0</v>
-      </c>
-      <c r="U42" t="n">
-        <v>0</v>
-      </c>
-      <c r="V42" t="n">
-        <v>0</v>
-      </c>
-      <c r="W42" t="n">
+      <c r="AD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="n">
         <v>0.003751359867952133</v>
-      </c>
-      <c r="X42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -5097,7 +5097,7 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1679966400671987</v>
+        <v>0.2099958000839983</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -5109,19 +5109,19 @@
         <v>0.1679966400671987</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>0.1679966400671987</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>1.007979840403192</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.04199916001679967</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -5139,43 +5139,43 @@
         <v>0</v>
       </c>
       <c r="W43" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" t="n">
+        <v>1.007979840403192</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>0.04199916001679967</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="n">
         <v>0.02099958000839983</v>
-      </c>
-      <c r="X43" t="n">
-        <v>0.2099958000839983</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -5224,7 +5224,7 @@
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>0.1675206937327552</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
@@ -5251,7 +5251,7 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>0.1675206937327552</v>
       </c>
       <c r="Y44" t="n">
         <v>0</v>
@@ -5412,7 +5412,7 @@
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>0.03638470764213619</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -5424,7 +5424,7 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>0.001347581764523563</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5475,7 +5475,7 @@
         <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>0.03638470764213619</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -5484,7 +5484,7 @@
         <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>0.001347581764523563</v>
       </c>
       <c r="AD46" t="n">
         <v>0</v>
@@ -5575,43 +5575,43 @@
         <v>0</v>
       </c>
       <c r="W47" t="n">
+        <v>0</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="n">
         <v>0.004311273981461522</v>
-      </c>
-      <c r="X47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -5627,11 +5627,11 @@
         <v>3</v>
       </c>
       <c r="D48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" t="n">
         <v>0.005966349787200191</v>
       </c>
-      <c r="E48" t="n">
-        <v>0</v>
-      </c>
       <c r="F48" t="n">
         <v>0</v>
       </c>
@@ -5642,10 +5642,10 @@
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>0.04773079829760152</v>
+        <v>0.5568593134720178</v>
       </c>
       <c r="J48" t="n">
-        <v>0.001988783262400064</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -5654,13 +5654,13 @@
         <v>0.02585418241120083</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>0.04773079829760152</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>1.25293345531204</v>
+        <v>0.005966349787200191</v>
       </c>
       <c r="P48" t="n">
         <v>0</v>
@@ -5672,7 +5672,7 @@
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>0.003977566524800128</v>
       </c>
       <c r="T48" t="n">
         <v>0.09745037985760312</v>
@@ -5687,28 +5687,28 @@
         <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>0.5568593134720178</v>
+        <v>1.25293345531204</v>
       </c>
       <c r="Y48" t="n">
         <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>0.005966349787200191</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>0.001988783262400064</v>
       </c>
       <c r="AB48" t="n">
         <v>0</v>
       </c>
       <c r="AC48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD48" t="n">
         <v>0.01193269957440038</v>
       </c>
-      <c r="AD48" t="n">
-        <v>0</v>
-      </c>
       <c r="AE48" t="n">
-        <v>0.003977566524800128</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
         <v>0</v>
@@ -5769,7 +5769,7 @@
         <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>0.01404889013767912</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
         <v>0</v>
@@ -5796,7 +5796,7 @@
         <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>0.01404889013767912</v>
       </c>
       <c r="Y49" t="n">
         <v>0</v>
@@ -5996,22 +5996,22 @@
         <v>0</v>
       </c>
       <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" t="n">
+        <v>0</v>
+      </c>
+      <c r="W51" t="n">
         <v>0.04099598670866957</v>
-      </c>
-      <c r="S51" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" t="n">
-        <v>0</v>
-      </c>
-      <c r="U51" t="n">
-        <v>0</v>
-      </c>
-      <c r="V51" t="n">
-        <v>0</v>
-      </c>
-      <c r="W51" t="n">
-        <v>0</v>
       </c>
       <c r="X51" t="n">
         <v>0</v>
@@ -6099,53 +6099,53 @@
         <v>0</v>
       </c>
       <c r="P52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" t="n">
+        <v>0</v>
+      </c>
+      <c r="W52" t="n">
+        <v>0</v>
+      </c>
+      <c r="X52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>0.005456331162926049</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>0.003637554108617366</v>
+      </c>
+      <c r="AE52" t="n">
         <v>0.01273143938016078</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
-      <c r="R52" t="n">
-        <v>0</v>
-      </c>
-      <c r="S52" t="n">
-        <v>0</v>
-      </c>
-      <c r="T52" t="n">
-        <v>0</v>
-      </c>
-      <c r="U52" t="n">
-        <v>0</v>
-      </c>
-      <c r="V52" t="n">
-        <v>0</v>
-      </c>
-      <c r="W52" t="n">
-        <v>0</v>
-      </c>
-      <c r="X52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>0.003637554108617366</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE52" t="n">
-        <v>0</v>
-      </c>
       <c r="AF52" t="n">
         <v>0</v>
       </c>
@@ -6153,7 +6153,7 @@
         <v>0</v>
       </c>
       <c r="AH52" t="n">
-        <v>0.005456331162926049</v>
+        <v>0</v>
       </c>
       <c r="AI52" t="n">
         <v>0</v>
@@ -6178,76 +6178,76 @@
         <v>0</v>
       </c>
       <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
         <v>0.0007963178263708611</v>
       </c>
-      <c r="G53" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" t="n">
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0.001194476739556292</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
         <v>0.0007963178263708611</v>
       </c>
-      <c r="I53" t="n">
-        <v>0.001194476739556292</v>
-      </c>
-      <c r="J53" t="n">
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" t="n">
+        <v>0</v>
+      </c>
+      <c r="W53" t="n">
+        <v>0</v>
+      </c>
+      <c r="X53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA53" t="n">
         <v>0.0003981589131854306</v>
       </c>
-      <c r="K53" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" t="n">
+      <c r="AB53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC53" t="n">
         <v>0.0007963178263708611</v>
-      </c>
-      <c r="N53" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
-      <c r="R53" t="n">
-        <v>0</v>
-      </c>
-      <c r="S53" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" t="n">
-        <v>0</v>
-      </c>
-      <c r="U53" t="n">
-        <v>0</v>
-      </c>
-      <c r="V53" t="n">
-        <v>0</v>
-      </c>
-      <c r="W53" t="n">
-        <v>0</v>
-      </c>
-      <c r="X53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>0</v>
       </c>
       <c r="AD53" t="n">
         <v>0</v>
@@ -6284,7 +6284,7 @@
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>0.264812975835816</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -6347,7 +6347,7 @@
         <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>0.264812975835816</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -6417,55 +6417,55 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" t="n">
+        <v>0</v>
+      </c>
+      <c r="W55" t="n">
+        <v>0</v>
+      </c>
+      <c r="X55" t="n">
+        <v>0.005725190839694656</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC55" t="n">
         <v>0.001908396946564886</v>
-      </c>
-      <c r="N55" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" t="n">
-        <v>0.005725190839694656</v>
-      </c>
-      <c r="P55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
-      <c r="R55" t="n">
-        <v>0</v>
-      </c>
-      <c r="S55" t="n">
-        <v>0</v>
-      </c>
-      <c r="T55" t="n">
-        <v>0</v>
-      </c>
-      <c r="U55" t="n">
-        <v>0</v>
-      </c>
-      <c r="V55" t="n">
-        <v>0</v>
-      </c>
-      <c r="W55" t="n">
-        <v>0</v>
-      </c>
-      <c r="X55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>0</v>
       </c>
       <c r="AD55" t="n">
         <v>0</v>
@@ -6526,55 +6526,55 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" t="n">
+        <v>0</v>
+      </c>
+      <c r="W56" t="n">
+        <v>0</v>
+      </c>
+      <c r="X56" t="n">
+        <v>0.003489305279318887</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC56" t="n">
         <v>0.01744652639659444</v>
-      </c>
-      <c r="N56" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" t="n">
-        <v>0.003489305279318887</v>
-      </c>
-      <c r="P56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" t="n">
-        <v>0</v>
-      </c>
-      <c r="S56" t="n">
-        <v>0</v>
-      </c>
-      <c r="T56" t="n">
-        <v>0</v>
-      </c>
-      <c r="U56" t="n">
-        <v>0</v>
-      </c>
-      <c r="V56" t="n">
-        <v>0</v>
-      </c>
-      <c r="W56" t="n">
-        <v>0</v>
-      </c>
-      <c r="X56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>0</v>
       </c>
       <c r="AD56" t="n">
         <v>0</v>
@@ -6611,7 +6611,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>0.09247738507583145</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -6623,62 +6623,62 @@
         <v>0</v>
       </c>
       <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
         <v>0.1723442176413222</v>
       </c>
-      <c r="J57" t="n">
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" t="n">
+        <v>0</v>
+      </c>
+      <c r="W57" t="n">
+        <v>0</v>
+      </c>
+      <c r="X57" t="n">
+        <v>0.01849547701516629</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>0.03110602952550695</v>
+      </c>
+      <c r="AA57" t="n">
         <v>0.9390658102700339</v>
       </c>
-      <c r="K57" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" t="n">
-        <v>0.01849547701516629</v>
-      </c>
-      <c r="P57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
-      <c r="R57" t="n">
-        <v>0</v>
-      </c>
-      <c r="S57" t="n">
-        <v>0</v>
-      </c>
-      <c r="T57" t="n">
-        <v>0</v>
-      </c>
-      <c r="U57" t="n">
-        <v>0</v>
-      </c>
-      <c r="V57" t="n">
-        <v>0</v>
-      </c>
-      <c r="W57" t="n">
-        <v>0</v>
-      </c>
-      <c r="X57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>0.09247738507583145</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>0</v>
-      </c>
       <c r="AB57" t="n">
         <v>0</v>
       </c>
@@ -6698,7 +6698,7 @@
         <v>0</v>
       </c>
       <c r="AH57" t="n">
-        <v>0.03110602952550695</v>
+        <v>0</v>
       </c>
       <c r="AI57" t="n">
         <v>0</v>
@@ -6717,7 +6717,7 @@
         <v>1</v>
       </c>
       <c r="D58" t="n">
-        <v>0.07710100231303006</v>
+        <v>0</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
@@ -6732,7 +6732,7 @@
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>1.264456437933693</v>
+        <v>0.1233616037008481</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6744,25 +6744,25 @@
         <v>0.01542020046260601</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>1.264456437933693</v>
       </c>
       <c r="N58" t="n">
         <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>0.2158828064764842</v>
+        <v>0.07710100231303006</v>
       </c>
       <c r="P58" t="n">
         <v>0</v>
       </c>
       <c r="Q58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
         <v>0.01542020046260601</v>
-      </c>
-      <c r="R58" t="n">
-        <v>0.04626060138781804</v>
-      </c>
-      <c r="S58" t="n">
-        <v>0</v>
       </c>
       <c r="T58" t="n">
         <v>0.06168080185042405</v>
@@ -6774,10 +6774,10 @@
         <v>0</v>
       </c>
       <c r="W58" t="n">
-        <v>0</v>
+        <v>0.04626060138781804</v>
       </c>
       <c r="X58" t="n">
-        <v>0.1233616037008481</v>
+        <v>0.2158828064764842</v>
       </c>
       <c r="Y58" t="n">
         <v>0</v>
@@ -6792,19 +6792,19 @@
         <v>0</v>
       </c>
       <c r="AC58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD58" t="n">
         <v>0.01542020046260601</v>
       </c>
-      <c r="AD58" t="n">
-        <v>0</v>
-      </c>
       <c r="AE58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="n">
         <v>0.01542020046260601</v>
-      </c>
-      <c r="AF58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG58" t="n">
-        <v>0</v>
       </c>
       <c r="AH58" t="n">
         <v>0</v>
@@ -6829,7 +6829,7 @@
         <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>0.1152737752161383</v>
+        <v>0</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
@@ -6841,10 +6841,10 @@
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>1.364073006724304</v>
+        <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>3.150816522574448</v>
+        <v>0.1152737752161383</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
@@ -6853,73 +6853,73 @@
         <v>2.708933717579251</v>
       </c>
       <c r="M59" t="n">
+        <v>1.364073006724304</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0.1152737752161383</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
+        <v>8.93371757925072</v>
+      </c>
+      <c r="T59" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" t="n">
+        <v>0</v>
+      </c>
+      <c r="W59" t="n">
+        <v>0</v>
+      </c>
+      <c r="X59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>3.150816522574448</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC59" t="n">
         <v>1.325648414985591</v>
       </c>
-      <c r="N59" t="n">
-        <v>0</v>
-      </c>
-      <c r="O59" t="n">
-        <v>0</v>
-      </c>
-      <c r="P59" t="n">
+      <c r="AD59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="n">
         <v>0.01921229586935639</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
-      <c r="R59" t="n">
-        <v>0</v>
-      </c>
-      <c r="S59" t="n">
-        <v>0</v>
-      </c>
-      <c r="T59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U59" t="n">
-        <v>0</v>
-      </c>
-      <c r="V59" t="n">
-        <v>0.1152737752161383</v>
-      </c>
-      <c r="W59" t="n">
+      <c r="AF59" t="n">
+        <v>0.01921229586935639</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH59" t="n">
+        <v>0.07684918347742556</v>
+      </c>
+      <c r="AI59" t="n">
         <v>0.1536983669548511</v>
-      </c>
-      <c r="X59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB59" t="n">
-        <v>0.07684918347742556</v>
-      </c>
-      <c r="AC59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE59" t="n">
-        <v>8.93371757925072</v>
-      </c>
-      <c r="AF59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI59" t="n">
-        <v>0.01921229586935639</v>
       </c>
     </row>
     <row r="60">
@@ -6935,100 +6935,100 @@
         <v>1</v>
       </c>
       <c r="D60" t="n">
-        <v>0.007006971937077392</v>
+        <v>0.003503485968538696</v>
       </c>
       <c r="E60" t="n">
-        <v>0.2032021861752444</v>
+        <v>0.03503485968538696</v>
       </c>
       <c r="F60" t="n">
-        <v>0.1681673264898574</v>
+        <v>0.003503485968538696</v>
       </c>
       <c r="G60" t="n">
         <v>0.1086080650246996</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>0.003503485968538696</v>
       </c>
       <c r="I60" t="n">
-        <v>1.261254948673931</v>
+        <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>3.619101005500473</v>
+        <v>0.07006971937077391</v>
       </c>
       <c r="K60" t="n">
-        <v>0.003503485968538696</v>
+        <v>0.1681673264898574</v>
       </c>
       <c r="L60" t="n">
         <v>3.051536278597204</v>
       </c>
       <c r="M60" t="n">
+        <v>1.261254948673931</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0.007006971937077392</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0.2032021861752444</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10.57352065304979</v>
+      </c>
+      <c r="T60" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0.003503485968538696</v>
+      </c>
+      <c r="V60" t="n">
+        <v>0</v>
+      </c>
+      <c r="W60" t="n">
+        <v>0.02102091581123218</v>
+      </c>
+      <c r="X60" t="n">
+        <v>0.04204183162246435</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>0.05255228952808044</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>3.619101005500473</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC60" t="n">
         <v>0.9459412115054479</v>
       </c>
-      <c r="N60" t="n">
-        <v>0</v>
-      </c>
-      <c r="O60" t="n">
+      <c r="AD60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>0.01051045790561609</v>
+      </c>
+      <c r="AF60" t="n">
+        <v>0.02102091581123218</v>
+      </c>
+      <c r="AG60" t="n">
+        <v>0.007006971937077392</v>
+      </c>
+      <c r="AH60" t="n">
         <v>0.04204183162246435</v>
       </c>
-      <c r="P60" t="n">
-        <v>0.01051045790561609</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>0.007006971937077392</v>
-      </c>
-      <c r="R60" t="n">
-        <v>0.02102091581123218</v>
-      </c>
-      <c r="S60" t="n">
-        <v>0</v>
-      </c>
-      <c r="T60" t="n">
-        <v>0</v>
-      </c>
-      <c r="U60" t="n">
-        <v>0</v>
-      </c>
-      <c r="V60" t="n">
-        <v>0.07006971937077391</v>
-      </c>
-      <c r="W60" t="n">
+      <c r="AI60" t="n">
         <v>0.1331324668044704</v>
-      </c>
-      <c r="X60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y60" t="n">
-        <v>0.003503485968538696</v>
-      </c>
-      <c r="Z60" t="n">
-        <v>0.03503485968538696</v>
-      </c>
-      <c r="AA60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB60" t="n">
-        <v>0.04204183162246435</v>
-      </c>
-      <c r="AC60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD60" t="n">
-        <v>0.003503485968538696</v>
-      </c>
-      <c r="AE60" t="n">
-        <v>10.57352065304979</v>
-      </c>
-      <c r="AF60" t="n">
-        <v>0.003503485968538696</v>
-      </c>
-      <c r="AG60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH60" t="n">
-        <v>0.05255228952808044</v>
-      </c>
-      <c r="AI60" t="n">
-        <v>0.02102091581123218</v>
       </c>
     </row>
     <row r="61">
@@ -7044,11 +7044,11 @@
         <v>1</v>
       </c>
       <c r="D61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" t="n">
         <v>0.003558845510516389</v>
       </c>
-      <c r="E61" t="n">
-        <v>0</v>
-      </c>
       <c r="F61" t="n">
         <v>0</v>
       </c>
@@ -7059,10 +7059,10 @@
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>0.05872095092352041</v>
+        <v>0.09786825153920069</v>
       </c>
       <c r="J61" t="n">
-        <v>0.005338268265774583</v>
+        <v>0</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
@@ -7071,19 +7071,19 @@
         <v>0.03380903234990569</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>0.05872095092352041</v>
       </c>
       <c r="N61" t="n">
         <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>0.5195914445353927</v>
+        <v>0.003558845510516389</v>
       </c>
       <c r="P61" t="n">
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.005338268265774583</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
         <v>0</v>
@@ -7101,43 +7101,43 @@
         <v>0</v>
       </c>
       <c r="W61" t="n">
+        <v>0</v>
+      </c>
+      <c r="X61" t="n">
+        <v>0.5195914445353927</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>0.005338268265774583</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>0.005338268265774583</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="n">
+        <v>0.005338268265774583</v>
+      </c>
+      <c r="AH61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI61" t="n">
         <v>0.003558845510516389</v>
-      </c>
-      <c r="X61" t="n">
-        <v>0.09786825153920069</v>
-      </c>
-      <c r="Y61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z61" t="n">
-        <v>0.003558845510516389</v>
-      </c>
-      <c r="AA61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC61" t="n">
-        <v>0.005338268265774583</v>
-      </c>
-      <c r="AD61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI61" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -7153,100 +7153,100 @@
         <v>2</v>
       </c>
       <c r="D62" t="n">
-        <v>0.07437709185570844</v>
+        <v>0</v>
       </c>
       <c r="E62" t="n">
         <v>0</v>
       </c>
       <c r="F62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.03718854592785422</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0.1115656377835627</v>
+      </c>
+      <c r="K62" t="n">
         <v>0.05578281889178133</v>
-      </c>
-      <c r="G62" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" t="n">
-        <v>0.3904797322424693</v>
-      </c>
-      <c r="J62" t="n">
-        <v>0.3161026403867608</v>
-      </c>
-      <c r="K62" t="n">
-        <v>0</v>
       </c>
       <c r="L62" t="n">
         <v>0.2789140944589066</v>
       </c>
       <c r="M62" t="n">
+        <v>0.3904797322424693</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0.07437709185570844</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0.7809594644849386</v>
+      </c>
+      <c r="T62" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W62" t="n">
+        <v>0</v>
+      </c>
+      <c r="X62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>0.3161026403867608</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC62" t="n">
         <v>0.2975083674228338</v>
       </c>
-      <c r="N62" t="n">
-        <v>0</v>
-      </c>
-      <c r="O62" t="n">
-        <v>0</v>
-      </c>
-      <c r="P62" t="n">
+      <c r="AD62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="n">
         <v>0.01859427296392711</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
-      <c r="R62" t="n">
-        <v>0</v>
-      </c>
-      <c r="S62" t="n">
-        <v>0</v>
-      </c>
-      <c r="T62" t="n">
-        <v>0</v>
-      </c>
-      <c r="U62" t="n">
-        <v>0</v>
-      </c>
-      <c r="V62" t="n">
-        <v>0.1115656377835627</v>
-      </c>
-      <c r="W62" t="n">
+      <c r="AF62" t="n">
+        <v>0.05578281889178133</v>
+      </c>
+      <c r="AG62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH62" t="n">
+        <v>0.05578281889178133</v>
+      </c>
+      <c r="AI62" t="n">
         <v>0.03718854592785422</v>
-      </c>
-      <c r="X62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y62" t="n">
-        <v>0.03718854592785422</v>
-      </c>
-      <c r="Z62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB62" t="n">
-        <v>0.05578281889178133</v>
-      </c>
-      <c r="AC62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE62" t="n">
-        <v>0.7809594644849386</v>
-      </c>
-      <c r="AF62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI62" t="n">
-        <v>0.05578281889178133</v>
       </c>
     </row>
     <row r="63">
@@ -7262,100 +7262,100 @@
         <v>2</v>
       </c>
       <c r="D63" t="n">
-        <v>0.008722197993894461</v>
+        <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>0.02616659398168339</v>
+        <v>0.00436109899694723</v>
       </c>
       <c r="F63" t="n">
-        <v>0.06541648495420846</v>
+        <v>0</v>
       </c>
       <c r="G63" t="n">
         <v>0.04797208896641954</v>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>0.00436109899694723</v>
       </c>
       <c r="I63" t="n">
-        <v>0.5276929786306149</v>
+        <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>0.4491931966855648</v>
+        <v>0.01308329699084169</v>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>0.06541648495420846</v>
       </c>
       <c r="L63" t="n">
         <v>0.3576101177496729</v>
       </c>
       <c r="M63" t="n">
-        <v>1.142607937200175</v>
+        <v>0.5276929786306149</v>
       </c>
       <c r="N63" t="n">
         <v>0</v>
       </c>
       <c r="O63" t="n">
+        <v>0.008722197993894461</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>0.02616659398168339</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" t="n">
+        <v>1.626689925861317</v>
+      </c>
+      <c r="T63" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" t="n">
+        <v>0</v>
+      </c>
+      <c r="W63" t="n">
+        <v>0</v>
+      </c>
+      <c r="X63" t="n">
         <v>0.00436109899694723</v>
       </c>
-      <c r="P63" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
-      <c r="R63" t="n">
-        <v>0</v>
-      </c>
-      <c r="S63" t="n">
-        <v>0</v>
-      </c>
-      <c r="T63" t="n">
-        <v>0</v>
-      </c>
-      <c r="U63" t="n">
-        <v>0</v>
-      </c>
-      <c r="V63" t="n">
-        <v>0.01308329699084169</v>
-      </c>
-      <c r="W63" t="n">
-        <v>0.07849978194505015</v>
-      </c>
-      <c r="X63" t="n">
-        <v>0</v>
-      </c>
       <c r="Y63" t="n">
-        <v>0.00436109899694723</v>
+        <v>0</v>
       </c>
       <c r="Z63" t="n">
         <v>0.00436109899694723</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>0.4491931966855648</v>
       </c>
       <c r="AB63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>1.142607937200175</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="n">
+        <v>0.02616659398168339</v>
+      </c>
+      <c r="AG63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH63" t="n">
         <v>0.01308329699084169</v>
       </c>
-      <c r="AC63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE63" t="n">
-        <v>1.626689925861317</v>
-      </c>
-      <c r="AF63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH63" t="n">
-        <v>0.00436109899694723</v>
-      </c>
       <c r="AI63" t="n">
-        <v>0.02616659398168339</v>
+        <v>0.07849978194505015</v>
       </c>
     </row>
     <row r="64">
@@ -7374,10 +7374,10 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>0.02311604253351826</v>
       </c>
       <c r="F64" t="n">
-        <v>0.1618122977346279</v>
+        <v>0</v>
       </c>
       <c r="G64" t="n">
         <v>0.02311604253351826</v>
@@ -7386,19 +7386,19 @@
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>0.6472491909385114</v>
+        <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>0.3929727230698105</v>
+        <v>0.02311604253351826</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>0.1618122977346279</v>
       </c>
       <c r="L64" t="n">
         <v>0.4160887656033287</v>
       </c>
       <c r="M64" t="n">
-        <v>1.109570041608877</v>
+        <v>0.6472491909385114</v>
       </c>
       <c r="N64" t="n">
         <v>0</v>
@@ -7410,13 +7410,13 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.04623208506703652</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>0</v>
+        <v>1.363846509477578</v>
       </c>
       <c r="T64" t="n">
         <v>0</v>
@@ -7425,10 +7425,10 @@
         <v>0</v>
       </c>
       <c r="V64" t="n">
-        <v>0.02311604253351826</v>
+        <v>0</v>
       </c>
       <c r="W64" t="n">
-        <v>0.1386962552011096</v>
+        <v>0</v>
       </c>
       <c r="X64" t="n">
         <v>0</v>
@@ -7440,31 +7440,31 @@
         <v>0.02311604253351826</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>0.3929727230698105</v>
       </c>
       <c r="AB64" t="n">
-        <v>0.02311604253351826</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
-        <v>0</v>
+        <v>1.109570041608877</v>
       </c>
       <c r="AD64" t="n">
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>1.363846509477578</v>
+        <v>0</v>
       </c>
       <c r="AF64" t="n">
-        <v>0</v>
+        <v>0.04623208506703652</v>
       </c>
       <c r="AG64" t="n">
-        <v>0</v>
+        <v>0.04623208506703652</v>
       </c>
       <c r="AH64" t="n">
         <v>0.02311604253351826</v>
       </c>
       <c r="AI64" t="n">
-        <v>0.04623208506703652</v>
+        <v>0.1386962552011096</v>
       </c>
     </row>
     <row r="65">
@@ -7507,55 +7507,55 @@
         <v>0</v>
       </c>
       <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
+      </c>
+      <c r="V65" t="n">
+        <v>0</v>
+      </c>
+      <c r="W65" t="n">
+        <v>0</v>
+      </c>
+      <c r="X65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC65" t="n">
         <v>7.76</v>
-      </c>
-      <c r="N65" t="n">
-        <v>0</v>
-      </c>
-      <c r="O65" t="n">
-        <v>0</v>
-      </c>
-      <c r="P65" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
-      <c r="R65" t="n">
-        <v>0</v>
-      </c>
-      <c r="S65" t="n">
-        <v>0</v>
-      </c>
-      <c r="T65" t="n">
-        <v>0</v>
-      </c>
-      <c r="U65" t="n">
-        <v>0</v>
-      </c>
-      <c r="V65" t="n">
-        <v>0</v>
-      </c>
-      <c r="W65" t="n">
-        <v>0</v>
-      </c>
-      <c r="X65" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y65" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC65" t="n">
-        <v>0</v>
       </c>
       <c r="AD65" t="n">
         <v>0</v>
@@ -7589,52 +7589,52 @@
         <v>2</v>
       </c>
       <c r="D66" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.1633097441480675</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0.1088731627653783</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" t="n">
         <v>0.05443658138268917</v>
       </c>
-      <c r="E66" t="n">
-        <v>0</v>
-      </c>
-      <c r="F66" t="n">
-        <v>0</v>
-      </c>
-      <c r="G66" t="n">
-        <v>0</v>
-      </c>
-      <c r="H66" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" t="n">
-        <v>0.1088731627653783</v>
-      </c>
-      <c r="J66" t="n">
-        <v>0.1633097441480675</v>
-      </c>
-      <c r="K66" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" t="n">
-        <v>0</v>
-      </c>
-      <c r="M66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N66" t="n">
-        <v>0</v>
-      </c>
-      <c r="O66" t="n">
-        <v>0.2721829069134458</v>
-      </c>
       <c r="P66" t="n">
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.326619488296135</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>0</v>
+        <v>0.05443658138268917</v>
       </c>
       <c r="T66" t="n">
         <v>0.5443658138268916</v>
@@ -7649,34 +7649,34 @@
         <v>0</v>
       </c>
       <c r="X66" t="n">
+        <v>0.2721829069134458</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA66" t="n">
         <v>0.1633097441480675</v>
       </c>
-      <c r="Y66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA66" t="n">
-        <v>0</v>
-      </c>
       <c r="AB66" t="n">
         <v>0</v>
       </c>
       <c r="AC66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD66" t="n">
         <v>0.05443658138268917</v>
       </c>
-      <c r="AD66" t="n">
-        <v>0</v>
-      </c>
       <c r="AE66" t="n">
-        <v>0.05443658138268917</v>
+        <v>0</v>
       </c>
       <c r="AF66" t="n">
         <v>0</v>
       </c>
       <c r="AG66" t="n">
-        <v>0</v>
+        <v>0.326619488296135</v>
       </c>
       <c r="AH66" t="n">
         <v>0</v>
@@ -7725,55 +7725,55 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
+      </c>
+      <c r="V67" t="n">
+        <v>0</v>
+      </c>
+      <c r="W67" t="n">
+        <v>0</v>
+      </c>
+      <c r="X67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC67" t="n">
         <v>2.18</v>
-      </c>
-      <c r="N67" t="n">
-        <v>0</v>
-      </c>
-      <c r="O67" t="n">
-        <v>0</v>
-      </c>
-      <c r="P67" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
-      <c r="R67" t="n">
-        <v>0</v>
-      </c>
-      <c r="S67" t="n">
-        <v>0</v>
-      </c>
-      <c r="T67" t="n">
-        <v>0</v>
-      </c>
-      <c r="U67" t="n">
-        <v>0</v>
-      </c>
-      <c r="V67" t="n">
-        <v>0</v>
-      </c>
-      <c r="W67" t="n">
-        <v>0</v>
-      </c>
-      <c r="X67" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y67" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC67" t="n">
-        <v>0</v>
       </c>
       <c r="AD67" t="n">
         <v>0</v>
@@ -7807,83 +7807,83 @@
         <v>3</v>
       </c>
       <c r="D68" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" t="n">
         <v>0.05374242720343951</v>
       </c>
-      <c r="E68" t="n">
-        <v>0</v>
-      </c>
-      <c r="F68" t="n">
-        <v>0</v>
-      </c>
-      <c r="G68" t="n">
-        <v>0</v>
-      </c>
-      <c r="H68" t="n">
-        <v>0</v>
-      </c>
-      <c r="I68" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" t="n">
-        <v>0</v>
-      </c>
-      <c r="K68" t="n">
-        <v>0</v>
-      </c>
-      <c r="L68" t="n">
-        <v>0</v>
-      </c>
-      <c r="M68" t="n">
+      <c r="P68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>0</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
+      </c>
+      <c r="V68" t="n">
+        <v>0</v>
+      </c>
+      <c r="W68" t="n">
+        <v>0</v>
+      </c>
+      <c r="X68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>0.01465702560093805</v>
+      </c>
+      <c r="AC68" t="n">
         <v>0.0293140512018761</v>
       </c>
-      <c r="N68" t="n">
-        <v>0</v>
-      </c>
-      <c r="O68" t="n">
-        <v>0</v>
-      </c>
-      <c r="P68" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
-      <c r="R68" t="n">
-        <v>0</v>
-      </c>
-      <c r="S68" t="n">
-        <v>0</v>
-      </c>
-      <c r="T68" t="n">
-        <v>0</v>
-      </c>
-      <c r="U68" t="n">
-        <v>0</v>
-      </c>
-      <c r="V68" t="n">
-        <v>0</v>
-      </c>
-      <c r="W68" t="n">
-        <v>0</v>
-      </c>
-      <c r="X68" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y68" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC68" t="n">
-        <v>0</v>
-      </c>
       <c r="AD68" t="n">
         <v>0</v>
       </c>
@@ -7894,7 +7894,7 @@
         <v>0</v>
       </c>
       <c r="AG68" t="n">
-        <v>0.01465702560093805</v>
+        <v>0</v>
       </c>
       <c r="AH68" t="n">
         <v>0</v>
@@ -7916,41 +7916,41 @@
         <v>3</v>
       </c>
       <c r="D69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" t="n">
         <v>0.6298629121896998</v>
       </c>
-      <c r="E69" t="n">
-        <v>0</v>
-      </c>
-      <c r="F69" t="n">
-        <v>0</v>
-      </c>
-      <c r="G69" t="n">
-        <v>0</v>
-      </c>
-      <c r="H69" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" t="n">
-        <v>0</v>
-      </c>
-      <c r="K69" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" t="n">
-        <v>0</v>
-      </c>
-      <c r="M69" t="n">
-        <v>0</v>
-      </c>
-      <c r="N69" t="n">
-        <v>0</v>
-      </c>
-      <c r="O69" t="n">
-        <v>0</v>
-      </c>
       <c r="P69" t="n">
         <v>0</v>
       </c>
@@ -7958,23 +7958,23 @@
         <v>0</v>
       </c>
       <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
+      </c>
+      <c r="V69" t="n">
+        <v>0</v>
+      </c>
+      <c r="W69" t="n">
         <v>0.005292965648652941</v>
       </c>
-      <c r="S69" t="n">
-        <v>0</v>
-      </c>
-      <c r="T69" t="n">
-        <v>0</v>
-      </c>
-      <c r="U69" t="n">
-        <v>0</v>
-      </c>
-      <c r="V69" t="n">
-        <v>0</v>
-      </c>
-      <c r="W69" t="n">
-        <v>0</v>
-      </c>
       <c r="X69" t="n">
         <v>0</v>
       </c>
@@ -7988,14 +7988,14 @@
         <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>0.01058593129730588</v>
       </c>
       <c r="AC69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD69" t="n">
         <v>0.02117186259461176</v>
       </c>
-      <c r="AD69" t="n">
-        <v>0</v>
-      </c>
       <c r="AE69" t="n">
         <v>0</v>
       </c>
@@ -8003,7 +8003,7 @@
         <v>0</v>
       </c>
       <c r="AG69" t="n">
-        <v>0.01058593129730588</v>
+        <v>0</v>
       </c>
       <c r="AH69" t="n">
         <v>0</v>
@@ -8040,67 +8040,67 @@
         <v>0</v>
       </c>
       <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="n">
         <v>5.11</v>
       </c>
-      <c r="J70" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" t="n">
-        <v>0</v>
-      </c>
-      <c r="L70" t="n">
-        <v>0</v>
-      </c>
-      <c r="M70" t="n">
+      <c r="N70" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>0</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
+      </c>
+      <c r="V70" t="n">
+        <v>0</v>
+      </c>
+      <c r="W70" t="n">
+        <v>0</v>
+      </c>
+      <c r="X70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC70" t="n">
         <v>5.23</v>
-      </c>
-      <c r="N70" t="n">
-        <v>0</v>
-      </c>
-      <c r="O70" t="n">
-        <v>0</v>
-      </c>
-      <c r="P70" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
-      <c r="R70" t="n">
-        <v>0</v>
-      </c>
-      <c r="S70" t="n">
-        <v>0</v>
-      </c>
-      <c r="T70" t="n">
-        <v>0</v>
-      </c>
-      <c r="U70" t="n">
-        <v>0</v>
-      </c>
-      <c r="V70" t="n">
-        <v>0</v>
-      </c>
-      <c r="W70" t="n">
-        <v>0</v>
-      </c>
-      <c r="X70" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y70" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC70" t="n">
-        <v>0</v>
       </c>
       <c r="AD70" t="n">
         <v>0</v>
@@ -8149,19 +8149,19 @@
         <v>0</v>
       </c>
       <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" t="n">
         <v>1.25</v>
-      </c>
-      <c r="J71" t="n">
-        <v>0</v>
-      </c>
-      <c r="K71" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" t="n">
-        <v>0</v>
-      </c>
-      <c r="M71" t="n">
-        <v>0</v>
       </c>
       <c r="N71" t="n">
         <v>0</v>

--- a/data/OLS_all.xlsx
+++ b/data/OLS_all.xlsx
@@ -441,162 +441,162 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>771</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>565</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>678</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>426</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>871</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>428</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>410</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>725</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>712</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>605</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>470</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>584</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>541</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
           <t>494</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>334</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>428</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>584</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>426</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>605</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>871</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>549</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>410</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>470</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>771</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>799</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>712</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>541</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>337</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>342</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>565</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>625</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>657</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>725</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>678</t>
         </is>
       </c>
     </row>
@@ -616,97 +616,97 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
         <v>0.2800517018526497</v>
       </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
+      <c r="L2" t="n">
+        <v>0.1723395088323998</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
         <v>0.02154243860404998</v>
       </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.4523912106850495</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.1938819474364498</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
         <v>0.6247307195174493</v>
       </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="n">
         <v>0.2154243860404998</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0.1723395088323998</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0.1938819474364498</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0.4523912106850495</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -725,97 +725,97 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.01897173211914248</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
         <v>1.233162587744261</v>
       </c>
-      <c r="F3" t="n">
-        <v>0.01897173211914248</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
+        <v>0.2466325175488522</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.3035477139062797</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.1138303927148549</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
         <v>0.834756213242269</v>
       </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="n">
         <v>0.3035477139062797</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0.2466325175488522</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0.1138303927148549</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0.3035477139062797</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -834,52 +834,52 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.01227596366314756</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.01227596366314756</v>
+      </c>
+      <c r="K4" t="n">
         <v>0.3068990915786889</v>
       </c>
-      <c r="F4" t="n">
-        <v>0.01227596366314756</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
+      <c r="L4" t="n">
+        <v>1.485391603240855</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.02455192732629511</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
         <v>0.07365578197888534</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.02455192732629511</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.7979376381045912</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.3068990915786889</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.01227596366314756</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
       </c>
       <c r="U4" t="n">
         <v>0.01227596366314756</v>
@@ -888,25 +888,25 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>3.584581389639087</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.2332433095998036</v>
+      </c>
+      <c r="AA4" t="n">
         <v>0.01227596366314756</v>
       </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.485391603240855</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>0.7979376381045912</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.2332433095998036</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
@@ -915,16 +915,16 @@
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>0.01227596366314756</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.584581389639087</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.01227596366314756</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>0.3068990915786889</v>
       </c>
     </row>
     <row r="5">
@@ -940,100 +940,100 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.01542631729730921</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.201555854287414</v>
+      </c>
+      <c r="L5" t="n">
+        <v>4.400907948960928</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.004407519227802631</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.006611278841703947</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
         <v>0.002203759613901316</v>
       </c>
-      <c r="E5" t="n">
-        <v>2.201555854287414</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.01542631729730921</v>
-      </c>
-      <c r="G5" t="n">
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
         <v>0.002203759613901316</v>
       </c>
-      <c r="H5" t="n">
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.053903960156026</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.1410406152896842</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.439055027877559</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.02203759613901316</v>
+      </c>
+      <c r="AG5" t="n">
         <v>0.002203759613901316</v>
       </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.006611278841703947</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1.439055027877559</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
         <v>0.2291909998457368</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0.02203759613901316</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>4.400907948960928</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0.004407519227802631</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0.1410406152896842</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>2.053903960156026</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1052,80 +1052,80 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.003681207436039021</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.03313086692435119</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.01288422602613657</v>
+      </c>
+      <c r="K6" t="n">
         <v>0.9147800478556966</v>
       </c>
-      <c r="F6" t="n">
-        <v>0.03313086692435119</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.003681207436039021</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.003681207436039021</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.007362414872078041</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1.006810233756672</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.00184060371801951</v>
+        <v>1.073071967605375</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3349898766795509</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0.00184060371801951</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0.00184060371801951</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.007362414872078041</v>
       </c>
       <c r="Q6" t="n">
         <v>0.00184060371801951</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>0.007362414872078041</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>0.00184060371801951</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.003681207436039021</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.00184060371801951</v>
       </c>
       <c r="W6" t="n">
-        <v>0.01288422602613657</v>
+        <v>0.003681207436039021</v>
       </c>
       <c r="X6" t="n">
         <v>0.00184060371801951</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>3.740106755015645</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.073071967605375</v>
+        <v>0.2043070127001657</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
+        <v>1.006810233756672</v>
+      </c>
+      <c r="AC6" t="n">
         <v>0.00184060371801951</v>
       </c>
-      <c r="AC6" t="n">
-        <v>0.2043070127001657</v>
-      </c>
       <c r="AD6" t="n">
         <v>0</v>
       </c>
@@ -1133,16 +1133,16 @@
         <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.003681207436039021</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.740106755015645</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.007362414872078041</v>
+        <v>0.3349898766795509</v>
       </c>
     </row>
     <row r="7">
@@ -1270,97 +1270,97 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.00242512428761974</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.007275372862859222</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.009700497150478962</v>
+      </c>
+      <c r="K8" t="n">
         <v>0.2303868073238753</v>
       </c>
-      <c r="F8" t="n">
-        <v>0.007275372862859222</v>
-      </c>
-      <c r="G8" t="n">
+      <c r="L8" t="n">
+        <v>0.3904450103067782</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.00242512428761974</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.004850248575239481</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
         <v>0.01455074572571844</v>
       </c>
-      <c r="H8" t="n">
-        <v>0.004850248575239481</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.4680489875106099</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.2182611858857766</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
         <v>0.4995756032496665</v>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
         <v>0.2012853158724384</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0.009700497150478962</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0.3904450103067782</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0.2182611858857766</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0.00242512428761974</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0.4680489875106099</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0.00242512428761974</v>
       </c>
     </row>
     <row r="9">
@@ -1488,97 +1488,97 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.005954507562224604</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.005954507562224604</v>
+      </c>
+      <c r="K10" t="n">
         <v>0.2590210789567703</v>
       </c>
-      <c r="F10" t="n">
+      <c r="L10" t="n">
+        <v>0.3751339764201501</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.06549958318447065</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.008931761343336906</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.002977253781112302</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.01488626890556151</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.002977253781112302</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.3989520066690485</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.2768846016434441</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.155174467071573</v>
+      </c>
+      <c r="AC10" t="n">
         <v>0.005954507562224604</v>
       </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.01488626890556151</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.008931761343336906</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1.155174467071573</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.002977253781112302</v>
-      </c>
-      <c r="M10" t="n">
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
         <v>0.4138382755746099</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0.005954507562224604</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0.005954507562224604</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0.3751339764201501</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0.2768846016434441</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0.3989520066690485</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0.002977253781112302</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0.06549958318447065</v>
       </c>
     </row>
     <row r="11">
@@ -1630,7 +1630,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>0.57</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1660,7 +1660,7 @@
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1669,7 +1669,7 @@
         <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -1687,7 +1687,7 @@
         <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1706,85 +1706,85 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.920951650038373</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
         <v>0.05116398055768739</v>
       </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>11.97237145049885</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.0255819902788437</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.1534919416730622</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
         <v>0.07674597083653108</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0.0255819902788437</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0.1534919416730622</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0.920951650038373</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>11.97237145049885</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -1815,97 +1815,97 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
+        <v>0.02581844469689146</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.3020758029536301</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.005163688939378292</v>
+      </c>
+      <c r="K13" t="n">
         <v>0.002581844469689146</v>
       </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.01807291128782402</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.1394196013632139</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.005163688939378292</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.06712795621191779</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.007745533409067438</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.002581844469689146</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.02323660022720231</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
         <v>0.1187648456057007</v>
       </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.06712795621191779</v>
-      </c>
-      <c r="M13" t="n">
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
         <v>0.1962201796963751</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0.02323660022720231</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0.002581844469689146</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0.3020758029536301</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0.005163688939378292</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0.1394196013632139</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0.01807291128782402</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0.02581844469689146</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0.007745533409067438</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0.005163688939378292</v>
       </c>
     </row>
     <row r="14">
@@ -1930,91 +1930,91 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>0.6947201270345376</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.03969829297340214</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.8535132989281461</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.01984914648670107</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.01984914648670107</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0.6550218340611353</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
         <v>0.05954743946010321</v>
       </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
         <v>0.1984914648670107</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0.6550218340611353</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.01984914648670107</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0.6947201270345376</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0.8535132989281461</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0.03969829297340214</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0.01984914648670107</v>
       </c>
     </row>
     <row r="15">
@@ -2033,85 +2033,85 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
+        <v>0.520745842432387</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>13.50579539727868</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
         <v>0.1847807827985889</v>
       </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>4.905089870653452</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0.03359650596337981</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
         <v>0.05039475894506971</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0.03359650596337981</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>13.50579539727868</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>4.905089870653452</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0.520745842432387</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>0</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -2142,97 +2142,97 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
+        <v>0.0577311652073511</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>3.651496199364957</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
         <v>0.00962186086789185</v>
       </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.732608486481285</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.03367651303762147</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0.04810930433945925</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
         <v>2.362166843067449</v>
       </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0.00962186086789185</v>
+      </c>
+      <c r="AI16" t="n">
         <v>0.02405465216972963</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0.04810930433945925</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.651496199364957</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0.00962186086789185</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.732608486481285</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0.0577311652073511</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>0.03367651303762147</v>
       </c>
     </row>
     <row r="17">
@@ -2251,97 +2251,97 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
+        <v>0.06595983778765818</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.9429813846680022</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
         <v>0.01221478477549226</v>
       </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.9258806859823131</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.002442956955098451</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.01465774173059071</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0.01710069868568916</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
         <v>0.08550349342844579</v>
       </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0.01465774173059071</v>
+      </c>
+      <c r="AI17" t="n">
         <v>0.06107392387746129</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0.01710069868568916</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0.01465774173059071</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0.9429813846680022</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0.01465774173059071</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0.9258806859823131</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0.06595983778765818</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>0.002442956955098451</v>
       </c>
     </row>
     <row r="18">
@@ -2366,79 +2366,79 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1.058761249338274</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.9528851244044468</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
         <v>0.2117522498676549</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.058761249338274</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0.9528851244044468</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>0</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -2469,97 +2469,97 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.06291682395872657</v>
+      </c>
+      <c r="K19" t="n">
         <v>0.1510003775009437</v>
       </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
+      <c r="L19" t="n">
+        <v>0.2642506606266515</v>
+      </c>
+      <c r="M19" t="n">
         <v>0.01258336479174531</v>
       </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
+      <c r="N19" t="n">
+        <v>0.01258336479174531</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.01258336479174531</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.01258336479174531</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.1761671070844344</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.849754624386561</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
         <v>1.006669183339625</v>
       </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
         <v>2.705423430225242</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0.06291682395872657</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0.2642506606266515</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0.01258336479174531</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.849754624386561</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>0.01258336479174531</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>0.1761671070844344</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>0.01258336479174531</v>
       </c>
     </row>
     <row r="20">
@@ -2590,73 +2590,73 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.002897899747158247</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
         <v>0.0002414916455965206</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0.002897899747158247</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>0</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
         <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>0.01444669170759896</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -2759,7 +2759,7 @@
         <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.01444669170759896</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -2793,83 +2793,83 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>0.002372948388372553</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>0.1494957484674708</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
+        <v>0.4018192604310856</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.2950365829543207</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
         <v>0.01186474194186276</v>
       </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
         <v>0.002372948388372553</v>
       </c>
-      <c r="O22" t="n">
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
         <v>0.002372948388372553</v>
       </c>
-      <c r="P22" t="n">
-        <v>0.4018192604310856</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0.002372948388372553</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0.2950365829543207</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>0</v>
-      </c>
       <c r="AD22" t="n">
         <v>0</v>
       </c>
@@ -2877,7 +2877,7 @@
         <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.1494957484674708</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -2905,97 +2905,97 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
+        <v>0.03314128384234946</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1.371539285168001</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
         <v>0.005098659052669148</v>
       </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.8999133227961047</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.1223678172640596</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0.0101973181053383</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0.02804262478968031</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
         <v>0.1325651353693978</v>
       </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0.01529597715800744</v>
+      </c>
+      <c r="AI23" t="n">
         <v>0.06118390863202978</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0.02804262478968031</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0.0101973181053383</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1.371539285168001</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0.01529597715800744</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0.8999133227961047</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0.03314128384234946</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>0.1223678172640596</v>
       </c>
     </row>
     <row r="24">
@@ -3014,97 +3014,97 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
+        <v>0.06561201428883867</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>3.251439819202449</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
         <v>0.009720298413161283</v>
       </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>2.605039974727224</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.01944059682632257</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.0121503730164516</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0.0461714174625161</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
         <v>0.05346164127238706</v>
       </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="n">
         <v>0.3669412650968384</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0.0461714174625161</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0.0121503730164516</v>
-      </c>
-      <c r="T24" t="n">
-        <v>3.251439819202449</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" t="n">
-        <v>2.605039974727224</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>0.06561201428883867</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>0.01944059682632257</v>
       </c>
     </row>
     <row r="25">
@@ -3141,19 +3141,19 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>0.004966229638458482</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>0.004966229638458482</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>0.004966229638458482</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>0.124155740961462</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -3168,37 +3168,37 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
         <v>0.009932459276916964</v>
       </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
       <c r="X25" t="n">
-        <v>0.124155740961462</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
         <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.004966229638458482</v>
+        <v>0.09435836313071116</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.004966229638458482</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.09435836313071116</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.004966229638458482</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -3235,10 +3235,10 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>0.02299908003679853</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0718721251149954</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -3247,65 +3247,65 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0.04024839006439743</v>
+        <v>0.02874885004599816</v>
       </c>
       <c r="K26" t="n">
-        <v>0.327736890524379</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0.2932382704691812</v>
+        <v>0.005749770009199632</v>
       </c>
       <c r="M26" t="n">
-        <v>0.8825896964121436</v>
+        <v>0.4312327506899724</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>0.005749770009199632</v>
+        <v>0.002874885004599816</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>0.06324747010119594</v>
       </c>
       <c r="Q26" t="n">
         <v>0.03737350505979761</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>0.04024839006439743</v>
       </c>
       <c r="S26" t="n">
+        <v>0.2932382704691812</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.008624655013799448</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.0718721251149954</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0.002874885004599816</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0.8107175712971482</v>
+      </c>
+      <c r="AA26" t="n">
         <v>1.138454461821527</v>
       </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0.02874885004599816</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0.002874885004599816</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z26" t="n">
+      <c r="AB26" t="n">
+        <v>0.327736890524379</v>
+      </c>
+      <c r="AC26" t="n">
         <v>0.005749770009199632</v>
       </c>
-      <c r="AA26" t="n">
-        <v>0.4312327506899724</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>0.8107175712971482</v>
-      </c>
       <c r="AD26" t="n">
         <v>0</v>
       </c>
@@ -3313,16 +3313,16 @@
         <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>0.02299908003679853</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.002874885004599816</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>0.008624655013799448</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>0.06324747010119594</v>
+        <v>0.8825896964121436</v>
       </c>
     </row>
     <row r="27">
@@ -3338,7 +3338,7 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>0.001319574569158903</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -3350,7 +3350,7 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>0.3166978965981368</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -3365,73 +3365,73 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
+        <v>0.001319574569158903</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.00395872370747671</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="n">
         <v>0.3998310944551476</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0.3166978965981368</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0.001319574569158903</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>0.00395872370747671</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0.001319574569158903</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -3559,97 +3559,97 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.4030206988300661</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.003912822318738506</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.1095590249246782</v>
+      </c>
+      <c r="K29" t="n">
         <v>0.03912822318738506</v>
       </c>
-      <c r="F29" t="n">
-        <v>0.003912822318738506</v>
-      </c>
-      <c r="G29" t="n">
-        <v>1.737293109519897</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.05477951246233909</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.1056462026059397</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0.1486872481120632</v>
-      </c>
       <c r="L29" t="n">
-        <v>0.4069335211488046</v>
+        <v>0.01173846695621552</v>
       </c>
       <c r="M29" t="n">
-        <v>7.160464843291465</v>
+        <v>0.4617130336111437</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>0.01173846695621552</v>
       </c>
       <c r="O29" t="n">
-        <v>0.01173846695621552</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1.498610948076848</v>
       </c>
       <c r="Q29" t="n">
         <v>0.03521540086864655</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>0.1056462026059397</v>
       </c>
       <c r="S29" t="n">
+        <v>0.4069335211488046</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0.05477951246233909</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0.03130257854990805</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.737293109519897</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0.007825644637477012</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>5.157099816097351</v>
+      </c>
+      <c r="AA29" t="n">
         <v>1.475134014164417</v>
       </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0.1095590249246782</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z29" t="n">
+      <c r="AB29" t="n">
+        <v>0.1486872481120632</v>
+      </c>
+      <c r="AC29" t="n">
         <v>0.01173846695621552</v>
       </c>
-      <c r="AA29" t="n">
-        <v>0.4617130336111437</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>5.157099816097351</v>
-      </c>
       <c r="AD29" t="n">
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>0.01173846695621552</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.4030206988300661</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.007825644637477012</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>0.03130257854990805</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.498610948076848</v>
+        <v>7.160464843291465</v>
       </c>
     </row>
     <row r="30">
@@ -3668,97 +3668,97 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
+        <v>0.268662444828248</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
         <v>0.1151410477835348</v>
       </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.01919017463058914</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.1151410477835348</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.5757052389176741</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0.05757052389176742</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0.01919017463058914</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
         <v>1.823066589905968</v>
       </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0.05757052389176742</v>
-      </c>
-      <c r="M30" t="n">
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="n">
         <v>0.134331222414124</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0.1151410477835348</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0.01919017463058914</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0.5757052389176741</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>0.268662444828248</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>0.01919017463058914</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -3777,97 +3777,97 @@
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>0.008966197435667534</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>0.192773244866852</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
       </c>
       <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.008966197435667534</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.1748408499955169</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.008966197435667534</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.0403478884605039</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0.004483098717833767</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0.01793239487133507</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
         <v>0.1613915538420156</v>
       </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0.0403478884605039</v>
-      </c>
-      <c r="M31" t="n">
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="n">
         <v>0.6276338204967273</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0.01793239487133507</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0.192773244866852</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0.1748408499955169</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0.008966197435667534</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>0.008966197435667534</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>0.004483098717833767</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>0.008966197435667534</v>
       </c>
     </row>
     <row r="32">
@@ -3995,97 +3995,97 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.01975503753457131</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
         <v>0.02963255630185697</v>
       </c>
-      <c r="F33" t="n">
-        <v>0.01975503753457131</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" t="n">
+      <c r="L33" t="n">
+        <v>0.03951007506914263</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.0691426313709996</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
         <v>0.009877518767285657</v>
       </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0.009877518767285657</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0.1481627815092849</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0.09877518767285659</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="n">
         <v>0.0493875938364283</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0.09877518767285659</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" t="n">
-        <v>0</v>
-      </c>
-      <c r="X33" t="n">
-        <v>0.0691426313709996</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>0.03951007506914263</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>0.009877518767285657</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>0.1481627815092849</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -4125,76 +4125,76 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>0.9750812567713976</v>
       </c>
       <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0.5958829902491874</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0.1625135427952329</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="n">
         <v>0.6771397616468039</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0.1625135427952329</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" t="n">
-        <v>0</v>
-      </c>
-      <c r="X34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>0.9750812567713976</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>0.5958829902491874</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -4243,7 +4243,7 @@
         <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
@@ -4270,7 +4270,7 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
         <v>0</v>
@@ -4343,52 +4343,52 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>0.2098559953686953</v>
       </c>
       <c r="M36" t="n">
-        <v>1.432809899413851</v>
+        <v>0.003618206816701643</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
       </c>
       <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>3.097185035096606</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
         <v>0.01447282726680657</v>
       </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" t="n">
-        <v>0</v>
-      </c>
-      <c r="X36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>0.003618206816701643</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>0.2098559953686953</v>
-      </c>
       <c r="AA36" t="n">
-        <v>0.003618206816701643</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
         <v>0</v>
@@ -4397,7 +4397,7 @@
         <v>0.01447282726680657</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>0.003618206816701643</v>
       </c>
       <c r="AE36" t="n">
         <v>0</v>
@@ -4412,7 +4412,7 @@
         <v>0</v>
       </c>
       <c r="AI36" t="n">
-        <v>3.097185035096606</v>
+        <v>1.432809899413851</v>
       </c>
     </row>
     <row r="37">
@@ -4434,16 +4434,16 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
         <v>0.006015218502812114</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0.03007609251406057</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0</v>
       </c>
       <c r="J37" t="n">
         <v>0.006015218502812114</v>
@@ -4452,76 +4452,76 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>0.06917501278233933</v>
       </c>
       <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.0210532647598424</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0.006015218502812114</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0.003007609251406057</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0.03007609251406057</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0.2917380973863876</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0.1323348070618665</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="n">
         <v>0.8631838551535385</v>
-      </c>
-      <c r="N37" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0.1323348070618665</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" t="n">
-        <v>0</v>
-      </c>
-      <c r="W37" t="n">
-        <v>0.006015218502812114</v>
-      </c>
-      <c r="X37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>0.06917501278233933</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>0.2917380973863876</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>0.003007609251406057</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>0.0210532647598424</v>
       </c>
     </row>
     <row r="38">
@@ -4540,97 +4540,97 @@
         <v>0</v>
       </c>
       <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.006523582751647205</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
         <v>0.009785374127470806</v>
       </c>
-      <c r="F38" t="n">
-        <v>0.006523582751647205</v>
-      </c>
-      <c r="G38" t="n">
+      <c r="L38" t="n">
+        <v>0.04240328788570683</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.008154478439559005</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0.004892687063735403</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0.009785374127470806</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
         <v>0.001630895687911801</v>
       </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0.009785374127470806</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" t="n">
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0.1908147954856807</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0.08154478439559006</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="n">
         <v>0.06686672320438386</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0.08154478439559006</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" t="n">
-        <v>0</v>
-      </c>
-      <c r="W38" t="n">
-        <v>0</v>
-      </c>
-      <c r="X38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>0.04240328788570683</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>0.008154478439559005</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>0.1908147954856807</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>0.004892687063735403</v>
       </c>
     </row>
     <row r="39">
@@ -4655,79 +4655,79 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>0.5632897836795887</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.04926108374384236</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0.01713428999785821</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="n">
         <v>0.05782822874277147</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0.01713428999785821</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0.5632897836795887</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0</v>
-      </c>
-      <c r="W39" t="n">
-        <v>0</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0.04926108374384236</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>0</v>
       </c>
       <c r="AF39" t="n">
         <v>0</v>
@@ -4764,79 +4764,79 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>0.07744339976524969</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
       </c>
       <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.1899783400491282</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0.001210053121332026</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="n">
         <v>0.07260318727992159</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" t="n">
-        <v>0.001210053121332026</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" t="n">
-        <v>0.07744339976524969</v>
-      </c>
-      <c r="U40" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" t="n">
-        <v>0</v>
-      </c>
-      <c r="W40" t="n">
-        <v>0</v>
-      </c>
-      <c r="X40" t="n">
-        <v>0.1899783400491282</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>0</v>
       </c>
       <c r="AF40" t="n">
         <v>0</v>
@@ -5009,7 +5009,7 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>0.003751359867952133</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -5039,7 +5039,7 @@
         <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>0.007502719735904265</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5048,7 +5048,7 @@
         <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>0.007502719735904265</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
         <v>0</v>
@@ -5066,7 +5066,7 @@
         <v>0</v>
       </c>
       <c r="AI42" t="n">
-        <v>0.003751359867952133</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -5091,91 +5091,91 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>4.262914741705166</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
       </c>
       <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>1.007979840403192</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0.02099958000839983</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0.1679966400671987</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>0.04199916001679967</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="n">
         <v>0.2099958000839983</v>
       </c>
-      <c r="J43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" t="n">
+      <c r="AF43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="n">
         <v>0.1679966400671987</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0.1679966400671987</v>
-      </c>
-      <c r="N43" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" t="n">
-        <v>4.262914741705166</v>
-      </c>
-      <c r="U43" t="n">
-        <v>0</v>
-      </c>
-      <c r="V43" t="n">
-        <v>0</v>
-      </c>
-      <c r="W43" t="n">
-        <v>0</v>
-      </c>
-      <c r="X43" t="n">
-        <v>1.007979840403192</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>0.04199916001679967</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>0.02099958000839983</v>
       </c>
     </row>
     <row r="44">
@@ -5200,7 +5200,7 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>0.04927079227433977</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -5224,7 +5224,7 @@
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>0.1675206937327552</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
@@ -5239,7 +5239,7 @@
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>0.04927079227433977</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
@@ -5251,7 +5251,7 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>0.1675206937327552</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
         <v>0</v>
@@ -5309,7 +5309,7 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -5348,7 +5348,7 @@
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
         <v>0</v>
@@ -5412,71 +5412,71 @@
         <v>0</v>
       </c>
       <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
         <v>0.03638470764213619</v>
       </c>
-      <c r="F46" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z46" t="n">
         <v>0.001347581764523563</v>
       </c>
-      <c r="N46" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" t="n">
-        <v>0</v>
-      </c>
-      <c r="U46" t="n">
-        <v>0</v>
-      </c>
-      <c r="V46" t="n">
-        <v>0</v>
-      </c>
-      <c r="W46" t="n">
-        <v>0</v>
-      </c>
-      <c r="X46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>0</v>
-      </c>
       <c r="AA46" t="n">
         <v>0</v>
       </c>
@@ -5484,25 +5484,25 @@
         <v>0</v>
       </c>
       <c r="AC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI46" t="n">
         <v>0.001347581764523563</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -5554,7 +5554,7 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>0.004311273981461522</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -5611,7 +5611,7 @@
         <v>0</v>
       </c>
       <c r="AI47" t="n">
-        <v>0.004311273981461522</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -5630,97 +5630,97 @@
         <v>0</v>
       </c>
       <c r="E48" t="n">
+        <v>0.01193269957440038</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.09745037985760312</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
         <v>0.005966349787200191</v>
       </c>
-      <c r="F48" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" t="n">
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.001988783262400064</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>1.25293345531204</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0.02585418241120083</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>0.003977566524800128</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>0.005966349787200191</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="n">
         <v>0.5568593134720178</v>
       </c>
-      <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0.02585418241120083</v>
-      </c>
-      <c r="M48" t="n">
+      <c r="AF48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="n">
         <v>0.04773079829760152</v>
-      </c>
-      <c r="N48" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" t="n">
-        <v>0.005966349787200191</v>
-      </c>
-      <c r="P48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" t="n">
-        <v>0.003977566524800128</v>
-      </c>
-      <c r="T48" t="n">
-        <v>0.09745037985760312</v>
-      </c>
-      <c r="U48" t="n">
-        <v>0</v>
-      </c>
-      <c r="V48" t="n">
-        <v>0</v>
-      </c>
-      <c r="W48" t="n">
-        <v>0</v>
-      </c>
-      <c r="X48" t="n">
-        <v>1.25293345531204</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>0.001988783262400064</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>0.01193269957440038</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -5745,7 +5745,7 @@
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>0.1264400112391121</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -5769,7 +5769,7 @@
         <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>0.01404889013767912</v>
       </c>
       <c r="P49" t="n">
         <v>0</v>
@@ -5784,7 +5784,7 @@
         <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>0.1264400112391121</v>
+        <v>0</v>
       </c>
       <c r="U49" t="n">
         <v>0</v>
@@ -5796,7 +5796,7 @@
         <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>0.01404889013767912</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="n">
         <v>0</v>
@@ -5854,7 +5854,7 @@
         <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -5893,7 +5893,7 @@
         <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="U50" t="n">
         <v>0</v>
@@ -5972,7 +5972,7 @@
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>0.04099598670866957</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
@@ -6011,7 +6011,7 @@
         <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>0.04099598670866957</v>
+        <v>0</v>
       </c>
       <c r="X51" t="n">
         <v>0</v>
@@ -6066,7 +6066,7 @@
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>0.003637554108617366</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -6087,13 +6087,13 @@
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>0.005456331162926049</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>0.01273143938016078</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6129,7 +6129,7 @@
         <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>0.005456331162926049</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -6141,10 +6141,10 @@
         <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>0.003637554108617366</v>
+        <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>0.01273143938016078</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
         <v>0</v>
@@ -6184,7 +6184,7 @@
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>0.0007963178263708611</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
@@ -6193,79 +6193,79 @@
         <v>0</v>
       </c>
       <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0.0003981589131854306</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" t="n">
+        <v>0</v>
+      </c>
+      <c r="W53" t="n">
+        <v>0</v>
+      </c>
+      <c r="X53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z53" t="n">
         <v>0.0007963178263708611</v>
       </c>
-      <c r="L53" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" t="n">
+      <c r="AA53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>0.0007963178263708611</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI53" t="n">
         <v>0.001194476739556292</v>
-      </c>
-      <c r="N53" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" t="n">
-        <v>0.0007963178263708611</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
-      <c r="R53" t="n">
-        <v>0</v>
-      </c>
-      <c r="S53" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" t="n">
-        <v>0</v>
-      </c>
-      <c r="U53" t="n">
-        <v>0</v>
-      </c>
-      <c r="V53" t="n">
-        <v>0</v>
-      </c>
-      <c r="W53" t="n">
-        <v>0</v>
-      </c>
-      <c r="X53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>0.0003981589131854306</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>0.0007963178263708611</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI53" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -6284,25 +6284,25 @@
         <v>0</v>
       </c>
       <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
         <v>0.264812975835816</v>
-      </c>
-      <c r="F54" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
@@ -6423,7 +6423,7 @@
         <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>0.005725190839694656</v>
       </c>
       <c r="P55" t="n">
         <v>0</v>
@@ -6450,13 +6450,13 @@
         <v>0</v>
       </c>
       <c r="X55" t="n">
-        <v>0.005725190839694656</v>
+        <v>0</v>
       </c>
       <c r="Y55" t="n">
         <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>0.001908396946564886</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -6465,7 +6465,7 @@
         <v>0</v>
       </c>
       <c r="AC55" t="n">
-        <v>0.001908396946564886</v>
+        <v>0</v>
       </c>
       <c r="AD55" t="n">
         <v>0</v>
@@ -6532,7 +6532,7 @@
         <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>0.003489305279318887</v>
       </c>
       <c r="P56" t="n">
         <v>0</v>
@@ -6559,13 +6559,13 @@
         <v>0</v>
       </c>
       <c r="X56" t="n">
-        <v>0.003489305279318887</v>
+        <v>0</v>
       </c>
       <c r="Y56" t="n">
         <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>0.01744652639659444</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -6574,7 +6574,7 @@
         <v>0</v>
       </c>
       <c r="AC56" t="n">
-        <v>0.01744652639659444</v>
+        <v>0</v>
       </c>
       <c r="AD56" t="n">
         <v>0</v>
@@ -6611,97 +6611,97 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
         <v>0.09247738507583145</v>
       </c>
-      <c r="F57" t="n">
-        <v>0</v>
-      </c>
-      <c r="G57" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
-      </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>0.03110602952550695</v>
       </c>
       <c r="M57" t="n">
+        <v>0.9390658102700339</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0.01849547701516629</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" t="n">
+        <v>0</v>
+      </c>
+      <c r="W57" t="n">
+        <v>0</v>
+      </c>
+      <c r="X57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI57" t="n">
         <v>0.1723442176413222</v>
-      </c>
-      <c r="N57" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
-      <c r="R57" t="n">
-        <v>0</v>
-      </c>
-      <c r="S57" t="n">
-        <v>0</v>
-      </c>
-      <c r="T57" t="n">
-        <v>0</v>
-      </c>
-      <c r="U57" t="n">
-        <v>0</v>
-      </c>
-      <c r="V57" t="n">
-        <v>0</v>
-      </c>
-      <c r="W57" t="n">
-        <v>0</v>
-      </c>
-      <c r="X57" t="n">
-        <v>0.01849547701516629</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>0.03110602952550695</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>0.9390658102700339</v>
-      </c>
-      <c r="AB57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI57" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -6720,37 +6720,37 @@
         <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>0.01542020046260601</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>0.06168080185042405</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>0.1233616037008481</v>
+        <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>0.04626060138781804</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>0.01542020046260601</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>1.264456437933693</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
         <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>0.07710100231303006</v>
+        <v>0.2158828064764842</v>
       </c>
       <c r="P58" t="n">
         <v>0</v>
@@ -6765,7 +6765,7 @@
         <v>0.01542020046260601</v>
       </c>
       <c r="T58" t="n">
-        <v>0.06168080185042405</v>
+        <v>0</v>
       </c>
       <c r="U58" t="n">
         <v>0</v>
@@ -6774,43 +6774,43 @@
         <v>0</v>
       </c>
       <c r="W58" t="n">
-        <v>0.04626060138781804</v>
+        <v>0</v>
       </c>
       <c r="X58" t="n">
-        <v>0.2158828064764842</v>
+        <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>0.01542020046260601</v>
       </c>
       <c r="Z58" t="n">
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>0.01542020046260601</v>
       </c>
       <c r="AB58" t="n">
         <v>0</v>
       </c>
       <c r="AC58" t="n">
-        <v>0</v>
+        <v>0.07710100231303006</v>
       </c>
       <c r="AD58" t="n">
-        <v>0.01542020046260601</v>
+        <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>0.1233616037008481</v>
       </c>
       <c r="AF58" t="n">
         <v>0</v>
       </c>
       <c r="AG58" t="n">
-        <v>0.01542020046260601</v>
+        <v>0</v>
       </c>
       <c r="AH58" t="n">
         <v>0</v>
       </c>
       <c r="AI58" t="n">
-        <v>0</v>
+        <v>1.264456437933693</v>
       </c>
     </row>
     <row r="59">
@@ -6832,10 +6832,10 @@
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>0.01921229586935639</v>
       </c>
       <c r="G59" t="n">
-        <v>0.03842459173871278</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -6844,82 +6844,82 @@
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>0.1152737752161383</v>
+        <v>0</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>2.708933717579251</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>1.364073006724304</v>
+        <v>3.150816522574448</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>0.01921229586935639</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>0.1536983669548511</v>
       </c>
       <c r="Q59" t="n">
         <v>0.1152737752161383</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>0.1152737752161383</v>
       </c>
       <c r="S59" t="n">
+        <v>2.708933717579251</v>
+      </c>
+      <c r="T59" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0.07684918347742556</v>
+      </c>
+      <c r="V59" t="n">
+        <v>0</v>
+      </c>
+      <c r="W59" t="n">
+        <v>0.03842459173871278</v>
+      </c>
+      <c r="X59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>1.325648414985591</v>
+      </c>
+      <c r="AA59" t="n">
         <v>8.93371757925072</v>
       </c>
-      <c r="T59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U59" t="n">
-        <v>0</v>
-      </c>
-      <c r="V59" t="n">
-        <v>0</v>
-      </c>
-      <c r="W59" t="n">
-        <v>0</v>
-      </c>
-      <c r="X59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA59" t="n">
-        <v>3.150816522574448</v>
-      </c>
       <c r="AB59" t="n">
         <v>0</v>
       </c>
       <c r="AC59" t="n">
-        <v>1.325648414985591</v>
+        <v>0</v>
       </c>
       <c r="AD59" t="n">
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>0.01921229586935639</v>
+        <v>0</v>
       </c>
       <c r="AF59" t="n">
-        <v>0.01921229586935639</v>
+        <v>0</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
       </c>
       <c r="AH59" t="n">
-        <v>0.07684918347742556</v>
+        <v>0</v>
       </c>
       <c r="AI59" t="n">
-        <v>0.1536983669548511</v>
+        <v>1.364073006724304</v>
       </c>
     </row>
     <row r="60">
@@ -6935,100 +6935,100 @@
         <v>1</v>
       </c>
       <c r="D60" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.02102091581123218</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
         <v>0.003503485968538696</v>
       </c>
-      <c r="E60" t="n">
+      <c r="J60" t="n">
+        <v>0.02102091581123218</v>
+      </c>
+      <c r="K60" t="n">
         <v>0.03503485968538696</v>
       </c>
-      <c r="F60" t="n">
-        <v>0.003503485968538696</v>
-      </c>
-      <c r="G60" t="n">
-        <v>0.1086080650246996</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0.003503485968538696</v>
-      </c>
-      <c r="I60" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" t="n">
-        <v>0.07006971937077391</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0.1681673264898574</v>
-      </c>
       <c r="L60" t="n">
-        <v>3.051536278597204</v>
+        <v>0.05255228952808044</v>
       </c>
       <c r="M60" t="n">
-        <v>1.261254948673931</v>
+        <v>3.619101005500473</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>0.01051045790561609</v>
       </c>
       <c r="O60" t="n">
-        <v>0.007006971937077392</v>
+        <v>0.04204183162246435</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>0.1331324668044704</v>
       </c>
       <c r="Q60" t="n">
         <v>0.2032021861752444</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>0.07006971937077391</v>
       </c>
       <c r="S60" t="n">
+        <v>3.051536278597204</v>
+      </c>
+      <c r="T60" t="n">
+        <v>0.003503485968538696</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0.04204183162246435</v>
+      </c>
+      <c r="V60" t="n">
+        <v>0</v>
+      </c>
+      <c r="W60" t="n">
+        <v>0.1086080650246996</v>
+      </c>
+      <c r="X60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>0.007006971937077392</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>0.9459412115054479</v>
+      </c>
+      <c r="AA60" t="n">
         <v>10.57352065304979</v>
       </c>
-      <c r="T60" t="n">
-        <v>0</v>
-      </c>
-      <c r="U60" t="n">
+      <c r="AB60" t="n">
+        <v>0.1681673264898574</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>0.007006971937077392</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="n">
         <v>0.003503485968538696</v>
       </c>
-      <c r="V60" t="n">
-        <v>0</v>
-      </c>
-      <c r="W60" t="n">
-        <v>0.02102091581123218</v>
-      </c>
-      <c r="X60" t="n">
-        <v>0.04204183162246435</v>
-      </c>
-      <c r="Y60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z60" t="n">
-        <v>0.05255228952808044</v>
-      </c>
-      <c r="AA60" t="n">
-        <v>3.619101005500473</v>
-      </c>
-      <c r="AB60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC60" t="n">
-        <v>0.9459412115054479</v>
-      </c>
-      <c r="AD60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE60" t="n">
-        <v>0.01051045790561609</v>
-      </c>
-      <c r="AF60" t="n">
-        <v>0.02102091581123218</v>
-      </c>
       <c r="AG60" t="n">
-        <v>0.007006971937077392</v>
+        <v>0.003503485968538696</v>
       </c>
       <c r="AH60" t="n">
-        <v>0.04204183162246435</v>
+        <v>0</v>
       </c>
       <c r="AI60" t="n">
-        <v>0.1331324668044704</v>
+        <v>1.261254948673931</v>
       </c>
     </row>
     <row r="61">
@@ -7047,97 +7047,97 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
+        <v>0.005338268265774583</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.1334567066443646</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="n">
         <v>0.003558845510516389</v>
       </c>
-      <c r="F61" t="n">
-        <v>0</v>
-      </c>
-      <c r="G61" t="n">
-        <v>0</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" t="n">
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.005338268265774583</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0.5195914445353927</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0.003558845510516389</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0.03380903234990569</v>
+      </c>
+      <c r="T61" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V61" t="n">
+        <v>0</v>
+      </c>
+      <c r="W61" t="n">
+        <v>0</v>
+      </c>
+      <c r="X61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>0.005338268265774583</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>0.003558845510516389</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="n">
         <v>0.09786825153920069</v>
       </c>
-      <c r="J61" t="n">
-        <v>0</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" t="n">
-        <v>0.03380903234990569</v>
-      </c>
-      <c r="M61" t="n">
+      <c r="AF61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI61" t="n">
         <v>0.05872095092352041</v>
-      </c>
-      <c r="N61" t="n">
-        <v>0</v>
-      </c>
-      <c r="O61" t="n">
-        <v>0.003558845510516389</v>
-      </c>
-      <c r="P61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
-      <c r="R61" t="n">
-        <v>0</v>
-      </c>
-      <c r="S61" t="n">
-        <v>0</v>
-      </c>
-      <c r="T61" t="n">
-        <v>0.1334567066443646</v>
-      </c>
-      <c r="U61" t="n">
-        <v>0</v>
-      </c>
-      <c r="V61" t="n">
-        <v>0</v>
-      </c>
-      <c r="W61" t="n">
-        <v>0</v>
-      </c>
-      <c r="X61" t="n">
-        <v>0.5195914445353927</v>
-      </c>
-      <c r="Y61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA61" t="n">
-        <v>0.005338268265774583</v>
-      </c>
-      <c r="AB61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD61" t="n">
-        <v>0.005338268265774583</v>
-      </c>
-      <c r="AE61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG61" t="n">
-        <v>0.005338268265774583</v>
-      </c>
-      <c r="AH61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI61" t="n">
-        <v>0.003558845510516389</v>
       </c>
     </row>
     <row r="62">
@@ -7159,94 +7159,94 @@
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>0.05578281889178133</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0.3161026403867608</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0.01859427296392711</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="n">
         <v>0.03718854592785422</v>
       </c>
-      <c r="I62" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" t="n">
+      <c r="Q62" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" t="n">
         <v>0.1115656377835627</v>
       </c>
-      <c r="K62" t="n">
+      <c r="S62" t="n">
+        <v>0.2789140944589066</v>
+      </c>
+      <c r="T62" t="n">
+        <v>0.03718854592785422</v>
+      </c>
+      <c r="U62" t="n">
         <v>0.05578281889178133</v>
       </c>
-      <c r="L62" t="n">
-        <v>0.2789140944589066</v>
-      </c>
-      <c r="M62" t="n">
+      <c r="V62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W62" t="n">
+        <v>0</v>
+      </c>
+      <c r="X62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>0.2975083674228338</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>0.7809594644849386</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>0.05578281889178133</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>0.07437709185570844</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI62" t="n">
         <v>0.3904797322424693</v>
-      </c>
-      <c r="N62" t="n">
-        <v>0</v>
-      </c>
-      <c r="O62" t="n">
-        <v>0.07437709185570844</v>
-      </c>
-      <c r="P62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
-      <c r="R62" t="n">
-        <v>0</v>
-      </c>
-      <c r="S62" t="n">
-        <v>0.7809594644849386</v>
-      </c>
-      <c r="T62" t="n">
-        <v>0</v>
-      </c>
-      <c r="U62" t="n">
-        <v>0</v>
-      </c>
-      <c r="V62" t="n">
-        <v>0</v>
-      </c>
-      <c r="W62" t="n">
-        <v>0</v>
-      </c>
-      <c r="X62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA62" t="n">
-        <v>0.3161026403867608</v>
-      </c>
-      <c r="AB62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC62" t="n">
-        <v>0.2975083674228338</v>
-      </c>
-      <c r="AD62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE62" t="n">
-        <v>0.01859427296392711</v>
-      </c>
-      <c r="AF62" t="n">
-        <v>0.05578281889178133</v>
-      </c>
-      <c r="AG62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH62" t="n">
-        <v>0.05578281889178133</v>
-      </c>
-      <c r="AI62" t="n">
-        <v>0.03718854592785422</v>
       </c>
     </row>
     <row r="63">
@@ -7265,79 +7265,79 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.02616659398168339</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
         <v>0.00436109899694723</v>
       </c>
-      <c r="F63" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" t="n">
-        <v>0.04797208896641954</v>
-      </c>
-      <c r="H63" t="n">
+      <c r="L63" t="n">
         <v>0.00436109899694723</v>
       </c>
-      <c r="I63" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" t="n">
-        <v>0.01308329699084169</v>
-      </c>
-      <c r="K63" t="n">
-        <v>0.06541648495420846</v>
-      </c>
-      <c r="L63" t="n">
-        <v>0.3576101177496729</v>
-      </c>
       <c r="M63" t="n">
-        <v>0.5276929786306149</v>
+        <v>0.4491931966855648</v>
       </c>
       <c r="N63" t="n">
         <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>0.008722197993894461</v>
+        <v>0.00436109899694723</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>0.07849978194505015</v>
       </c>
       <c r="Q63" t="n">
         <v>0.02616659398168339</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>0.01308329699084169</v>
       </c>
       <c r="S63" t="n">
+        <v>0.3576101177496729</v>
+      </c>
+      <c r="T63" t="n">
+        <v>0.00436109899694723</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0.01308329699084169</v>
+      </c>
+      <c r="V63" t="n">
+        <v>0</v>
+      </c>
+      <c r="W63" t="n">
+        <v>0.04797208896641954</v>
+      </c>
+      <c r="X63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>1.142607937200175</v>
+      </c>
+      <c r="AA63" t="n">
         <v>1.626689925861317</v>
       </c>
-      <c r="T63" t="n">
-        <v>0</v>
-      </c>
-      <c r="U63" t="n">
-        <v>0</v>
-      </c>
-      <c r="V63" t="n">
-        <v>0</v>
-      </c>
-      <c r="W63" t="n">
-        <v>0</v>
-      </c>
-      <c r="X63" t="n">
-        <v>0.00436109899694723</v>
-      </c>
-      <c r="Y63" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z63" t="n">
-        <v>0.00436109899694723</v>
-      </c>
-      <c r="AA63" t="n">
-        <v>0.4491931966855648</v>
-      </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>0.06541648495420846</v>
       </c>
       <c r="AC63" t="n">
-        <v>1.142607937200175</v>
+        <v>0.008722197993894461</v>
       </c>
       <c r="AD63" t="n">
         <v>0</v>
@@ -7346,16 +7346,16 @@
         <v>0</v>
       </c>
       <c r="AF63" t="n">
-        <v>0.02616659398168339</v>
+        <v>0</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
       </c>
       <c r="AH63" t="n">
-        <v>0.01308329699084169</v>
+        <v>0</v>
       </c>
       <c r="AI63" t="n">
-        <v>0.07849978194505015</v>
+        <v>0.5276929786306149</v>
       </c>
     </row>
     <row r="64">
@@ -7374,97 +7374,97 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.04623208506703652</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="n">
         <v>0.02311604253351826</v>
       </c>
-      <c r="F64" t="n">
-        <v>0</v>
-      </c>
-      <c r="G64" t="n">
+      <c r="L64" t="n">
         <v>0.02311604253351826</v>
       </c>
-      <c r="H64" t="n">
-        <v>0</v>
-      </c>
-      <c r="I64" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" t="n">
+      <c r="M64" t="n">
+        <v>0.3929727230698105</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0.1386962552011096</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" t="n">
         <v>0.02311604253351826</v>
       </c>
-      <c r="K64" t="n">
+      <c r="S64" t="n">
+        <v>0.4160887656033287</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0.02311604253351826</v>
+      </c>
+      <c r="V64" t="n">
+        <v>0</v>
+      </c>
+      <c r="W64" t="n">
+        <v>0.02311604253351826</v>
+      </c>
+      <c r="X64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>0.04623208506703652</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>1.109570041608877</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>1.363846509477578</v>
+      </c>
+      <c r="AB64" t="n">
         <v>0.1618122977346279</v>
       </c>
-      <c r="L64" t="n">
-        <v>0.4160887656033287</v>
-      </c>
-      <c r="M64" t="n">
+      <c r="AC64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI64" t="n">
         <v>0.6472491909385114</v>
-      </c>
-      <c r="N64" t="n">
-        <v>0</v>
-      </c>
-      <c r="O64" t="n">
-        <v>0</v>
-      </c>
-      <c r="P64" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
-      <c r="R64" t="n">
-        <v>0</v>
-      </c>
-      <c r="S64" t="n">
-        <v>1.363846509477578</v>
-      </c>
-      <c r="T64" t="n">
-        <v>0</v>
-      </c>
-      <c r="U64" t="n">
-        <v>0</v>
-      </c>
-      <c r="V64" t="n">
-        <v>0</v>
-      </c>
-      <c r="W64" t="n">
-        <v>0</v>
-      </c>
-      <c r="X64" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y64" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z64" t="n">
-        <v>0.02311604253351826</v>
-      </c>
-      <c r="AA64" t="n">
-        <v>0.3929727230698105</v>
-      </c>
-      <c r="AB64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC64" t="n">
-        <v>1.109570041608877</v>
-      </c>
-      <c r="AD64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF64" t="n">
-        <v>0.04623208506703652</v>
-      </c>
-      <c r="AG64" t="n">
-        <v>0.04623208506703652</v>
-      </c>
-      <c r="AH64" t="n">
-        <v>0.02311604253351826</v>
-      </c>
-      <c r="AI64" t="n">
-        <v>0.1386962552011096</v>
       </c>
     </row>
     <row r="65">
@@ -7546,7 +7546,7 @@
         <v>0</v>
       </c>
       <c r="Z65" t="n">
-        <v>0</v>
+        <v>7.76</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -7555,7 +7555,7 @@
         <v>0</v>
       </c>
       <c r="AC65" t="n">
-        <v>7.76</v>
+        <v>0</v>
       </c>
       <c r="AD65" t="n">
         <v>0</v>
@@ -7592,97 +7592,97 @@
         <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>0</v>
+        <v>0.05443658138268917</v>
       </c>
       <c r="F66" t="n">
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>0.5443658138268916</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
       </c>
       <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
         <v>0.1633097441480675</v>
       </c>
-      <c r="J66" t="n">
-        <v>0</v>
-      </c>
-      <c r="K66" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" t="n">
-        <v>0</v>
-      </c>
-      <c r="M66" t="n">
+      <c r="N66" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0.2721829069134458</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>0</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
+      </c>
+      <c r="V66" t="n">
+        <v>0</v>
+      </c>
+      <c r="W66" t="n">
+        <v>0</v>
+      </c>
+      <c r="X66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>0.326619488296135</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>0.05443658138268917</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>0.05443658138268917</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>0.1633097441480675</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI66" t="n">
         <v>0.1088731627653783</v>
-      </c>
-      <c r="N66" t="n">
-        <v>0</v>
-      </c>
-      <c r="O66" t="n">
-        <v>0.05443658138268917</v>
-      </c>
-      <c r="P66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
-      <c r="R66" t="n">
-        <v>0</v>
-      </c>
-      <c r="S66" t="n">
-        <v>0.05443658138268917</v>
-      </c>
-      <c r="T66" t="n">
-        <v>0.5443658138268916</v>
-      </c>
-      <c r="U66" t="n">
-        <v>0</v>
-      </c>
-      <c r="V66" t="n">
-        <v>0</v>
-      </c>
-      <c r="W66" t="n">
-        <v>0</v>
-      </c>
-      <c r="X66" t="n">
-        <v>0.2721829069134458</v>
-      </c>
-      <c r="Y66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA66" t="n">
-        <v>0.1633097441480675</v>
-      </c>
-      <c r="AB66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD66" t="n">
-        <v>0.05443658138268917</v>
-      </c>
-      <c r="AE66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG66" t="n">
-        <v>0.326619488296135</v>
-      </c>
-      <c r="AH66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI66" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -7764,7 +7764,7 @@
         <v>0</v>
       </c>
       <c r="Z67" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -7773,7 +7773,7 @@
         <v>0</v>
       </c>
       <c r="AC67" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AD67" t="n">
         <v>0</v>
@@ -7840,49 +7840,49 @@
         <v>0</v>
       </c>
       <c r="O68" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>0</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
+      </c>
+      <c r="V68" t="n">
+        <v>0.01465702560093805</v>
+      </c>
+      <c r="W68" t="n">
+        <v>0</v>
+      </c>
+      <c r="X68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>0.0293140512018761</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC68" t="n">
         <v>0.05374242720343951</v>
-      </c>
-      <c r="P68" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
-      <c r="R68" t="n">
-        <v>0</v>
-      </c>
-      <c r="S68" t="n">
-        <v>0</v>
-      </c>
-      <c r="T68" t="n">
-        <v>0</v>
-      </c>
-      <c r="U68" t="n">
-        <v>0</v>
-      </c>
-      <c r="V68" t="n">
-        <v>0</v>
-      </c>
-      <c r="W68" t="n">
-        <v>0</v>
-      </c>
-      <c r="X68" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y68" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB68" t="n">
-        <v>0.01465702560093805</v>
-      </c>
-      <c r="AC68" t="n">
-        <v>0.0293140512018761</v>
       </c>
       <c r="AD68" t="n">
         <v>0</v>
@@ -7919,7 +7919,7 @@
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>0</v>
+        <v>0.02117186259461176</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
@@ -7934,7 +7934,7 @@
         <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>0.005292965648652941</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
@@ -7949,52 +7949,52 @@
         <v>0</v>
       </c>
       <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
+      </c>
+      <c r="V69" t="n">
+        <v>0.01058593129730588</v>
+      </c>
+      <c r="W69" t="n">
+        <v>0</v>
+      </c>
+      <c r="X69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC69" t="n">
         <v>0.6298629121896998</v>
       </c>
-      <c r="P69" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
-      <c r="R69" t="n">
-        <v>0</v>
-      </c>
-      <c r="S69" t="n">
-        <v>0</v>
-      </c>
-      <c r="T69" t="n">
-        <v>0</v>
-      </c>
-      <c r="U69" t="n">
-        <v>0</v>
-      </c>
-      <c r="V69" t="n">
-        <v>0</v>
-      </c>
-      <c r="W69" t="n">
-        <v>0.005292965648652941</v>
-      </c>
-      <c r="X69" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y69" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB69" t="n">
-        <v>0.01058593129730588</v>
-      </c>
-      <c r="AC69" t="n">
-        <v>0</v>
-      </c>
       <c r="AD69" t="n">
-        <v>0.02117186259461176</v>
+        <v>0</v>
       </c>
       <c r="AE69" t="n">
         <v>0</v>
@@ -8052,73 +8052,73 @@
         <v>0</v>
       </c>
       <c r="M70" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>0</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
+      </c>
+      <c r="V70" t="n">
+        <v>0</v>
+      </c>
+      <c r="W70" t="n">
+        <v>0</v>
+      </c>
+      <c r="X70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI70" t="n">
         <v>5.11</v>
-      </c>
-      <c r="N70" t="n">
-        <v>0</v>
-      </c>
-      <c r="O70" t="n">
-        <v>0</v>
-      </c>
-      <c r="P70" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
-      <c r="R70" t="n">
-        <v>0</v>
-      </c>
-      <c r="S70" t="n">
-        <v>0</v>
-      </c>
-      <c r="T70" t="n">
-        <v>0</v>
-      </c>
-      <c r="U70" t="n">
-        <v>0</v>
-      </c>
-      <c r="V70" t="n">
-        <v>0</v>
-      </c>
-      <c r="W70" t="n">
-        <v>0</v>
-      </c>
-      <c r="X70" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y70" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC70" t="n">
-        <v>5.23</v>
-      </c>
-      <c r="AD70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH70" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI70" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -8143,91 +8143,91 @@
         <v>0</v>
       </c>
       <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>0</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
+      </c>
+      <c r="V71" t="n">
+        <v>0</v>
+      </c>
+      <c r="W71" t="n">
         <v>2.3</v>
       </c>
-      <c r="H71" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" t="n">
-        <v>0</v>
-      </c>
-      <c r="K71" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" t="n">
-        <v>0</v>
-      </c>
-      <c r="M71" t="n">
+      <c r="X71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI71" t="n">
         <v>1.25</v>
-      </c>
-      <c r="N71" t="n">
-        <v>0</v>
-      </c>
-      <c r="O71" t="n">
-        <v>0</v>
-      </c>
-      <c r="P71" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
-      <c r="R71" t="n">
-        <v>0</v>
-      </c>
-      <c r="S71" t="n">
-        <v>0</v>
-      </c>
-      <c r="T71" t="n">
-        <v>0</v>
-      </c>
-      <c r="U71" t="n">
-        <v>0</v>
-      </c>
-      <c r="V71" t="n">
-        <v>0</v>
-      </c>
-      <c r="W71" t="n">
-        <v>0</v>
-      </c>
-      <c r="X71" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y71" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI71" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/OLS_all.xlsx
+++ b/data/OLS_all.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,184 +417,184 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Sites</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>799</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>494</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>410</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>416</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>565</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>428</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>605</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>725</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>445</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>488</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>712</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>678</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>871</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>426</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>424</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
         <is>
           <t>140</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>771</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>337</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>565</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>625</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>657</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>678</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>426</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>871</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>428</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>334</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>410</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>725</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>712</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>605</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>470</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>342</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>584</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>541</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>494</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>549</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>site_1</t>
+          <t>Site_1</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -634,10 +622,10 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2800517018526497</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1723395088323998</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -670,22 +658,22 @@
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.02154243860404998</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.4523912106850495</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.1938819474364498</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.6247307195174493</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -706,20 +694,20 @@
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.2154243860404998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>site_2</t>
+          <t>Site_2</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -731,22 +719,22 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>4.262914741705166</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01897173211914248</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>1.233162587744261</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2466325175488522</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -758,13 +746,13 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.1679966400671987</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>0.04199916001679967</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -782,19 +770,19 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.02099958000839983</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.3035477139062797</v>
+        <v>0.1679966400671987</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.1138303927148549</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.834756213242269</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -815,20 +803,20 @@
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.3035477139062797</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>site_3</t>
+          <t>Site_3</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -846,16 +834,16 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01227596366314756</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01227596366314756</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3068990915786889</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1.485391603240855</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -873,16 +861,16 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.02455192732629511</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.07365578197888534</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01227596366314756</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -894,16 +882,16 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.584581389639087</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.2332433095998036</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.01227596366314756</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.7979376381045912</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -915,7 +903,7 @@
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.01227596366314756</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
@@ -924,16 +912,16 @@
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.3068990915786889</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>site_4</t>
+          <t>Site_4</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -949,25 +937,25 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>0.009932459276916964</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>0.009932459276916964</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01542631729730921</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>2.201555854287414</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>4.400907948960928</v>
+        <v>0.004966229638458482</v>
       </c>
       <c r="M5" t="n">
-        <v>0.004407519227802631</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -982,98 +970,98 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.006611278841703947</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>0.1589193484306714</v>
       </c>
       <c r="T5" t="n">
-        <v>0.002203759613901316</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>0.004966229638458482</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.002203759613901316</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.053903960156026</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.1410406152896842</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.439055027877559</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>0.004966229638458482</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>0.004966229638458482</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.02203759613901316</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.002203759613901316</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.2291909998457368</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" t="n">
         <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>site_5</t>
+          <t>Site_5</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>0.008624655013799448</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.003681207436039021</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>0.0718721251149954</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03313086692435119</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01288422602613657</v>
+        <v>0.008624655013799448</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9147800478556966</v>
+        <v>0.002874885004599816</v>
       </c>
       <c r="L6" t="n">
-        <v>1.073071967605375</v>
+        <v>0.005749770009199632</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1082,49 +1070,49 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.00184060371801951</v>
+        <v>0.327736890524379</v>
       </c>
       <c r="P6" t="n">
-        <v>0.007362414872078041</v>
+        <v>0.8825896964121436</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.00184060371801951</v>
+        <v>0.02874885004599816</v>
       </c>
       <c r="R6" t="n">
-        <v>0.007362414872078041</v>
+        <v>0.002874885004599816</v>
       </c>
       <c r="S6" t="n">
-        <v>0.00184060371801951</v>
+        <v>0.04599816007359706</v>
       </c>
       <c r="T6" t="n">
-        <v>0.003681207436039021</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>0.00184060371801951</v>
+        <v>0.008624655013799448</v>
       </c>
       <c r="W6" t="n">
-        <v>0.003681207436039021</v>
+        <v>1.138454461821527</v>
       </c>
       <c r="X6" t="n">
-        <v>0.00184060371801951</v>
+        <v>0.06324747010119594</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.740106755015645</v>
+        <v>0.2932382704691812</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.2043070127001657</v>
+        <v>0.04024839006439743</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>0.03737350505979761</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.006810233756672</v>
+        <v>0.002874885004599816</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.00184060371801951</v>
+        <v>0.4312327506899724</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1136,26 +1124,26 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>0.02299908003679853</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.3349898766795509</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" t="n">
         <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>site_6</t>
+          <t>Site_6</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -1194,7 +1182,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.3998310944551476</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1233,7 +1221,7 @@
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>0.001319574569158903</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -1255,16 +1243,16 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" t="n">
         <v>7</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>site_7</t>
+          <t>Site_7</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -1273,7 +1261,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.00242512428761974</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -1282,16 +1270,16 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.007275372862859222</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.009700497150478962</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2303868073238753</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3904450103067782</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1303,7 +1291,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0.00242512428761974</v>
+        <v>5.11</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1315,7 +1303,7 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.004850248575239481</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -1324,22 +1312,22 @@
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.01455074572571844</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.4680489875106099</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.2182611858857766</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.4995756032496665</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1360,20 +1348,20 @@
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.2012853158724384</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" t="n">
         <v>8</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>site_8</t>
+          <t>Site_8</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -1388,7 +1376,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>0.01258336479174531</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1400,7 +1388,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.2642506606266515</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1409,25 +1397,25 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.006669183339625</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.705423430225242</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>0.06291682395872657</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>0.1761671070844344</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>0.1132502831257078</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>0.06291682395872657</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>0.1510003775009437</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1436,7 +1424,7 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.01258336479174531</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1448,10 +1436,10 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>0.01258336479174531</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>0.01258336479174531</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1466,32 +1454,32 @@
         <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>0.01258336479174531</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" t="n">
         <v>9</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>site_9</t>
+          <t>Site_9</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>0.0007909827961241842</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>0.002372948388372553</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -1500,19 +1488,19 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0.005954507562224604</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0.005954507562224604</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2590210789567703</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3751339764201501</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>0.01186474194186276</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1521,22 +1509,22 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0.06549958318447065</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.008931761343336906</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.002977253781112302</v>
+        <v>0.003163931184496737</v>
       </c>
       <c r="T10" t="n">
-        <v>0.01488626890556151</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0.002977253781112302</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1548,19 +1536,19 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.3989520066690485</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.2768846016434441</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.155174467071573</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.005954507562224604</v>
+        <v>0.2950365829543207</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1572,26 +1560,26 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>0.1494957484674708</v>
       </c>
       <c r="AH10" t="n">
         <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.4138382755746099</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" t="n">
         <v>10</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>site_10</t>
+          <t>Site_10</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -1603,13 +1591,13 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1.371539285168001</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>0.01529597715800744</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1630,7 +1618,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0.57</v>
+        <v>0.06118390863202978</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1645,22 +1633,22 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>0.005098659052669148</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.0101973181053383</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>0.1223678172640596</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1672,7 +1660,7 @@
         <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>0.03314128384234946</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1691,16 +1679,16 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" t="n">
         <v>11</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>site_11</t>
+          <t>Site_11</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -1712,7 +1700,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.920951650038373</v>
+        <v>3.251439819202449</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1724,7 +1712,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.05116398055768739</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1736,10 +1724,10 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>11.97237145049885</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>0.0255819902788437</v>
+        <v>0.3669412650968384</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -1754,16 +1742,16 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>0.009720298413161283</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.0121503730164516</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>0.01944059682632257</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
@@ -1772,7 +1760,7 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.1534919416730622</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
@@ -1781,10 +1769,10 @@
         <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>0.06561201428883867</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.07674597083653108</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -1796,32 +1784,32 @@
         <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.0255819902788437</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" t="n">
         <v>12</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>site_12</t>
+          <t>Site_12</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.02581844469689146</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3020758029536301</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1830,37 +1818,37 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0.005163688939378292</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.002581844469689146</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0.01807291128782402</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1394196013632139</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0.005163688939378292</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>0.04099598670866957</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.06712795621191779</v>
+        <v>0.002157683510982609</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>0.01941915159884348</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -1875,25 +1863,25 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.007745533409067438</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.002581844469689146</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.02323660022720231</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.1187648456057007</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -1905,32 +1893,32 @@
         <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.1962201796963751</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" t="n">
         <v>13</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>site_13</t>
+          <t>Site_13</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0.03969829297340214</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6947201270345376</v>
+        <v>1.058761249338274</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1942,7 +1930,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.03969829297340214</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1954,10 +1942,10 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0.8535132989281461</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>0.01984914648670107</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -1990,19 +1978,19 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.01984914648670107</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.6550218340611353</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.05954743946010321</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -2014,32 +2002,32 @@
         <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.1984914648670107</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" t="n">
         <v>14</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>site_14</t>
+          <t>Site_14</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0.520745842432387</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>13.50579539727868</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -2051,7 +2039,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1847807827985889</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2063,10 +2051,10 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>4.905089870653452</v>
+        <v>0.0007963178263708611</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>0.001194476739556292</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2102,16 +2090,16 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>0.001592635652741722</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.03359650596337981</v>
+        <v>0.0003981589131854306</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.05039475894506971</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -2127,12 +2115,12 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" t="n">
         <v>15</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>site_15</t>
+          <t>Site_15</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -2142,13 +2130,13 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0577311652073511</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>3.651496199364957</v>
+        <v>13.50579539727868</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -2160,7 +2148,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.00962186086789185</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2172,10 +2160,10 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>2.732608486481285</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0.03367651303762147</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2190,7 +2178,7 @@
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>0.1847807827985889</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -2214,13 +2202,13 @@
         <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.04810930433945925</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>0.520745842432387</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.362166843067449</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -2229,19 +2217,19 @@
         <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.00962186086789185</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.02405465216972963</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" t="n">
         <v>16</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>site_16</t>
+          <t>Site_16</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2251,25 +2239,25 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0.06595983778765818</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9429813846680022</v>
+        <v>3.651496199364957</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>0.00962186086789185</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.01221478477549226</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2281,10 +2269,10 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0.9258806859823131</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0.002442956955098451</v>
+        <v>0.02405465216972963</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -2299,7 +2287,7 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>0.00962186086789185</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -2308,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.03367651303762147</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
@@ -2317,19 +2305,19 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.01465774173059071</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.01710069868568916</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>0.0577311652073511</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.08550349342844579</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -2338,23 +2326,23 @@
         <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.01465774173059071</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.06107392387746129</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" t="n">
         <v>17</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>site_17</t>
+          <t>Site_17</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -2366,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>1.058761249338274</v>
+        <v>0.9429813846680022</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>0.01465774173059071</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2390,10 +2378,10 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0.9528851244044468</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.06107392387746129</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -2408,16 +2396,16 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>0.01221478477549226</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.01465774173059071</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.002442956955098451</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
@@ -2435,10 +2423,10 @@
         <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>0.06595983778765818</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.2117522498676549</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -2454,16 +2442,16 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" t="n">
         <v>18</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>site_18</t>
+          <t>Site_18</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -2475,7 +2463,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>0.6947201270345376</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -2484,25 +2472,25 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0.06291682395872657</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1510003775009437</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2642506606266515</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.01258336479174531</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0.01258336479174531</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0.01258336479174531</v>
+        <v>0.1984914648670107</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -2517,34 +2505,34 @@
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>0.03969829297340214</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.01258336479174531</v>
+        <v>0.01984914648670107</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.01984914648670107</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.1761671070844344</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.849754624386561</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.006669183339625</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>0.03969829297340214</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -2559,20 +2547,20 @@
         <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>2.705423430225242</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" t="n">
         <v>19</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>site_19</t>
+          <t>Site_19</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -2584,7 +2572,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>0.920951650038373</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -2608,10 +2596,10 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0.002897899747158247</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>0.0255819902788437</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -2626,16 +2614,16 @@
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>0.05116398055768739</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.1534919416730622</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.0255819902788437</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
@@ -2656,7 +2644,7 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.0002414916455965206</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -2672,16 +2660,16 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" t="n">
         <v>20</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>site_20</t>
+          <t>Site_20</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -2693,7 +2681,7 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>0.3020758029536301</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -2720,37 +2708,37 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>0.1962201796963751</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>0.005163688939378292</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>0.007745533409067438</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>0.005163688939378292</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>0.002581844469689146</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.01032737787875658</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.002581844469689146</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>0.005163688939378292</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>0.06712795621191779</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.01444669170759896</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -2759,10 +2747,10 @@
         <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>0.01807291128782402</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>0.02581844469689146</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -2781,31 +2769,31 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" t="n">
         <v>21</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>site_21</t>
+          <t>Site_21</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>0.002372948388372553</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1494957484674708</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.4018192604310856</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -2820,7 +2808,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2950365829543207</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2841,7 +2829,7 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>0.01186474194186276</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -2853,7 +2841,7 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.002372948388372553</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
         <v>0</v>
@@ -2868,7 +2856,7 @@
         <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.002372948388372553</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
@@ -2890,121 +2878,121 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" t="n">
         <v>22</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>site_22</t>
+          <t>Site_22</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>0.01173846695621552</v>
       </c>
       <c r="E23" t="n">
-        <v>0.03314128384234946</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>1.371539285168001</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1.737293109519897</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>0.03130257854990805</v>
       </c>
       <c r="K23" t="n">
-        <v>0.005098659052669148</v>
+        <v>0.01956411159369253</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>0.01173846695621552</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>0.05477951246233909</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>0.8999133227961047</v>
+        <v>0.1486872481120632</v>
       </c>
       <c r="P23" t="n">
-        <v>0.1223678172640596</v>
+        <v>7.160464843291465</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>0.1095590249246782</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>0.007825644637477012</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>0.03521540086864655</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>0.03912822318738506</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>0.03912822318738506</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.01565128927495402</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.475134014164417</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.498610948076848</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>0.4069335211488046</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>0.1056462026059397</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.0101973181053383</v>
+        <v>0.03521540086864655</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>0.007825644637477012</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.02804262478968031</v>
+        <v>0.4617130336111437</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.1325651353693978</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>0.003912822318738506</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>0.4030206988300661</v>
       </c>
       <c r="AH23" t="n">
-        <v>0.01529597715800744</v>
+        <v>0.01173846695621552</v>
       </c>
       <c r="AI23" t="n">
-        <v>0.06118390863202978</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" t="n">
         <v>23</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>site_23</t>
+          <t>Site_23</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -3014,13 +3002,13 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0.06561201428883867</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>3.251439819202449</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -3032,7 +3020,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0.009720298413161283</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -3044,10 +3032,10 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>2.605039974727224</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>0.01944059682632257</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -3071,7 +3059,7 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>0.57</v>
       </c>
       <c r="Y24" t="n">
         <v>0</v>
@@ -3080,19 +3068,19 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.0121503730164516</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.0461714174625161</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>0.05346164127238706</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -3104,16 +3092,16 @@
         <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>0.3669412650968384</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" t="n">
         <v>24</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>site_24</t>
+          <t>Site_24</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -3123,16 +3111,16 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>0.004966229638458482</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>0.00184060371801951</v>
       </c>
       <c r="G25" t="n">
-        <v>0.009932459276916964</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>0.003681207436039021</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -3141,58 +3129,58 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0.004966229638458482</v>
+        <v>0.00184060371801951</v>
       </c>
       <c r="L25" t="n">
-        <v>0.004966229638458482</v>
+        <v>1.073071967605375</v>
       </c>
       <c r="M25" t="n">
-        <v>0.004966229638458482</v>
+        <v>0.003681207436039021</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>0.00184060371801951</v>
       </c>
       <c r="O25" t="n">
-        <v>0.124155740961462</v>
+        <v>1.006810233756672</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>0.3349898766795509</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>0.01288422602613657</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>3.740106755015645</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>0.2190318424443217</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>0.09018958218295602</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>0.9147800478556966</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>0.003681207436039021</v>
       </c>
       <c r="W25" t="n">
-        <v>0.009932459276916964</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>0.007362414872078041</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>0.00184060371801951</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.09435836313071116</v>
+        <v>0.007362414872078041</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>0.00184060371801951</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>0.02944965948831216</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3201,13 +3189,13 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>0.00184060371801951</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>0.03313086692435119</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>0.003681207436039021</v>
       </c>
       <c r="AH25" t="n">
         <v>0</v>
@@ -3217,94 +3205,94 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" t="n">
         <v>25</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>site_25</t>
+          <t>Site_25</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>0.002203759613901316</v>
       </c>
       <c r="F26" t="n">
-        <v>0.02299908003679853</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>0.002203759613901316</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0.02874885004599816</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0.005749770009199632</v>
+        <v>4.400907948960928</v>
       </c>
       <c r="M26" t="n">
-        <v>0.4312327506899724</v>
+        <v>0.002203759613901316</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>0.002874885004599816</v>
+        <v>1.439055027877559</v>
       </c>
       <c r="P26" t="n">
-        <v>0.06324747010119594</v>
+        <v>0.2291909998457368</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.03737350505979761</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>0.04024839006439743</v>
+        <v>2.053903960156026</v>
       </c>
       <c r="S26" t="n">
-        <v>0.2932382704691812</v>
+        <v>0.1234105383784737</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>0.06390902880313816</v>
       </c>
       <c r="U26" t="n">
-        <v>0.008624655013799448</v>
+        <v>2.201555854287414</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>0.0718721251149954</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.002874885004599816</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.8107175712971482</v>
+        <v>0.006611278841703947</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.138454461821527</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.327736890524379</v>
+        <v>0.02424135575291447</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.005749770009199632</v>
+        <v>0.004407519227802631</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>
@@ -3313,7 +3301,7 @@
         <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>0.01542631729730921</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -3322,23 +3310,23 @@
         <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>0.8825896964121436</v>
+        <v>0.02203759613901316</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" t="n">
         <v>26</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>site_26</t>
+          <t>Site_26</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D27" t="n">
-        <v>0.001319574569158903</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -3350,79 +3338,79 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3166978965981368</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>0.002977253781112302</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>0.3751339764201501</v>
       </c>
       <c r="M27" t="n">
-        <v>0.001319574569158903</v>
+        <v>0.01488626890556151</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>1.155174467071573</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>0.4138382755746099</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>0.005954507562224604</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>0.3989520066690485</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>0.226271287364535</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>0.08038585209003216</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>0.2590210789567703</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>0.002977253781112302</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>0.06549958318447065</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>0.002977253781112302</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>0.008931761343336906</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>0.01786352268667381</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.00395872370747671</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>0.005954507562224604</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -3431,20 +3419,20 @@
         <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>0.3998310944551476</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" t="n">
         <v>27</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>site_27</t>
+          <t>Site_27</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -3544,12 +3532,12 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" t="n">
         <v>28</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>site_28</t>
+          <t>Site_28</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -3562,7 +3550,7 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0.4030206988300661</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -3571,67 +3559,67 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>0.003912822318738506</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0.1095590249246782</v>
+        <v>0.01227596366314756</v>
       </c>
       <c r="K29" t="n">
-        <v>0.03912822318738506</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0.01173846695621552</v>
+        <v>1.485391603240855</v>
       </c>
       <c r="M29" t="n">
-        <v>0.4617130336111437</v>
+        <v>0.07365578197888534</v>
       </c>
       <c r="N29" t="n">
-        <v>0.01173846695621552</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>0.7979376381045912</v>
       </c>
       <c r="P29" t="n">
-        <v>1.498610948076848</v>
+        <v>0.3068990915786889</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.03521540086864655</v>
+        <v>0.01227596366314756</v>
       </c>
       <c r="R29" t="n">
-        <v>0.1056462026059397</v>
+        <v>3.584581389639087</v>
       </c>
       <c r="S29" t="n">
-        <v>0.4069335211488046</v>
+        <v>1.276700220967346</v>
       </c>
       <c r="T29" t="n">
-        <v>0.05477951246233909</v>
+        <v>0.6629020378099681</v>
       </c>
       <c r="U29" t="n">
-        <v>0.03130257854990805</v>
+        <v>0.3068990915786889</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.737293109519897</v>
+        <v>0.01227596366314756</v>
       </c>
       <c r="X29" t="n">
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.007825644637477012</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>5.157099816097351</v>
+        <v>0.02455192732629511</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.475134014164417</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.1486872481120632</v>
+        <v>0.07365578197888534</v>
       </c>
       <c r="AC29" t="n">
-        <v>0.01173846695621552</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
         <v>0</v>
@@ -3640,7 +3628,7 @@
         <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>0.01227596366314756</v>
       </c>
       <c r="AG29" t="n">
         <v>0</v>
@@ -3649,32 +3637,32 @@
         <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>7.160464843291465</v>
+        <v>0.01227596366314756</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" t="n">
         <v>29</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>site_29</t>
+          <t>Site_29</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0.268662444828248</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.1151410477835348</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -3683,13 +3671,13 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0.01919017463058914</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0.1151410477835348</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>0.2466325175488522</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -3698,25 +3686,25 @@
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>0.5757052389176741</v>
+        <v>0.834756213242269</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>0.3035477139062797</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>0.3035477139062797</v>
       </c>
       <c r="S30" t="n">
-        <v>0.05757052389176742</v>
+        <v>0.1138303927148549</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>0.07588692847656991</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.233162587744261</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -3728,7 +3716,7 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.01919017463058914</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
         <v>0</v>
@@ -3737,7 +3725,7 @@
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>0.01897173211914248</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -3746,10 +3734,10 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.823066589905968</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>0.01897173211914248</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
@@ -3758,16 +3746,16 @@
         <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.134331222414124</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" t="n">
         <v>30</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>site_30</t>
+          <t>Site_30</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -3777,16 +3765,16 @@
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0.008966197435667534</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.192773244866852</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>0.01455074572571844</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -3798,46 +3786,46 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>0.3904450103067782</v>
       </c>
       <c r="M31" t="n">
-        <v>0.008966197435667534</v>
+        <v>0.004850248575239481</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>0.1748408499955169</v>
+        <v>0.4995756032496665</v>
       </c>
       <c r="P31" t="n">
-        <v>0.008966197435667534</v>
+        <v>0.2012853158724384</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>0.009700497150478962</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>0.4680489875106099</v>
       </c>
       <c r="S31" t="n">
-        <v>0.0403478884605039</v>
+        <v>0.4122711288953559</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>0.04607736146477507</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>0.2303868073238753</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>0.009700497150478962</v>
       </c>
       <c r="W31" t="n">
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>0.00242512428761974</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.004483098717833767</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
         <v>0</v>
@@ -3846,41 +3834,41 @@
         <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>0.01697587001333818</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.01793239487133507</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.1613915538420156</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>0.007275372862859222</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>0.00242512428761974</v>
       </c>
       <c r="AH31" t="n">
         <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>0.6276338204967273</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" t="n">
         <v>31</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>site_31</t>
+          <t>Site_31</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
@@ -3895,7 +3883,7 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>0.02154243860404998</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -3907,7 +3895,7 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>0.1723395088323998</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -3916,25 +3904,25 @@
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>0.6247307195174493</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>0.2154243860404998</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>0.4523912106850495</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>0.1938819474364498</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>0.02154243860404998</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>0.2800517018526497</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -3955,7 +3943,7 @@
         <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>0.02154243860404998</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -3980,16 +3968,16 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" t="n">
         <v>32</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>site_32</t>
+          <t>Site_32</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -4007,16 +3995,16 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0.01975503753457131</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.02963255630185697</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0.03951007506914263</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -4025,7 +4013,7 @@
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>0.0691426313709996</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
@@ -4034,7 +4022,7 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>0.009877518767285657</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -4046,7 +4034,7 @@
         <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>0.009877518767285657</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
         <v>0</v>
@@ -4058,7 +4046,7 @@
         <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.1481627815092849</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4067,7 +4055,7 @@
         <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.09877518767285659</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
         <v>0</v>
@@ -4085,20 +4073,20 @@
         <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>0.0493875938364283</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" t="n">
         <v>33</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>site_33</t>
+          <t>Site_33</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
@@ -4110,7 +4098,7 @@
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>0.1151410477835348</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -4125,7 +4113,7 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0.9750812567713976</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -4137,13 +4125,13 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>0.134331222414124</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>0.01919017463058914</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>0.01919017463058914</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -4152,7 +4140,7 @@
         <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>0.1151410477835348</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -4164,10 +4152,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>0.05757052389176742</v>
       </c>
       <c r="Z34" t="n">
-        <v>0.5958829902491874</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4176,10 +4164,10 @@
         <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>0.1625135427952329</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>0.268662444828248</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>
@@ -4194,20 +4182,20 @@
         <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.6771397616468039</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" t="n">
         <v>34</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>site_34</t>
+          <t>Site_34</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -4219,7 +4207,7 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>0.192773244866852</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -4243,19 +4231,19 @@
         <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>0.6276338204967273</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>0.004483098717833767</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>0.01793239487133507</v>
       </c>
       <c r="T35" t="n">
         <v>0</v>
@@ -4270,10 +4258,10 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>0.008966197435667534</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>0.0403478884605039</v>
       </c>
       <c r="Z35" t="n">
         <v>0</v>
@@ -4285,10 +4273,10 @@
         <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>0.008966197435667534</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>0.008966197435667534</v>
       </c>
       <c r="AE35" t="n">
         <v>0</v>
@@ -4307,19 +4295,19 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" t="n">
         <v>35</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>site_35</t>
+          <t>Site_35</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>0.009877518767285657</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -4343,10 +4331,10 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0.2098559953686953</v>
+        <v>0.03951007506914263</v>
       </c>
       <c r="M36" t="n">
-        <v>0.003618206816701643</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -4355,7 +4343,7 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>3.097185035096606</v>
+        <v>0.0493875938364283</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -4367,10 +4355,10 @@
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>0.01975503753457131</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>0.02963255630185697</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -4385,7 +4373,7 @@
         <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>0.01447282726680657</v>
+        <v>0.009877518767285657</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -4394,16 +4382,16 @@
         <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.01447282726680657</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.003618206816701643</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>0.009877518767285657</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>0.01975503753457131</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -4412,16 +4400,16 @@
         <v>0</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.432809899413851</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" t="n">
         <v>36</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>site_36</t>
+          <t>Site_36</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -4443,16 +4431,16 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>0.006015218502812114</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>0.006015218502812114</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0.06917501278233933</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -4464,13 +4452,13 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0.0210532647598424</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>0.006015218502812114</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -4479,13 +4467,13 @@
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>0.003007609251406057</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>0.03007609251406057</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
         <v>0</v>
@@ -4494,7 +4482,7 @@
         <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>0.2917380973863876</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -4503,7 +4491,7 @@
         <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>0.1323348070618665</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
@@ -4521,16 +4509,16 @@
         <v>0</v>
       </c>
       <c r="AI37" t="n">
-        <v>0.8631838551535385</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" t="n">
         <v>37</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>site_37</t>
+          <t>Site_37</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -4552,19 +4540,19 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>0.006523582751647205</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>0.009785374127470806</v>
+        <v>0.02708559046587215</v>
       </c>
       <c r="L38" t="n">
-        <v>0.04240328788570683</v>
+        <v>0.9750812567713976</v>
       </c>
       <c r="M38" t="n">
-        <v>0.008154478439559005</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
@@ -4573,13 +4561,13 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>0.004892687063735403</v>
+        <v>0.6771397616468039</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>0.009785374127470806</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -4594,7 +4582,7 @@
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>0.001630895687911801</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
         <v>0</v>
@@ -4603,16 +4591,16 @@
         <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>0.1908147954856807</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>0.02708559046587215</v>
       </c>
       <c r="AC38" t="n">
-        <v>0.08154478439559006</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -4630,20 +4618,20 @@
         <v>0</v>
       </c>
       <c r="AI38" t="n">
-        <v>0.06686672320438386</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" t="n">
         <v>38</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>site_38</t>
+          <t>Site_38</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -4655,7 +4643,7 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0.5632897836795887</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -4670,7 +4658,7 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>0.2098559953686953</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -4679,10 +4667,10 @@
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>0.04926108374384236</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1.432809899413851</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -4691,7 +4679,7 @@
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>0.01713428999785821</v>
+        <v>0.07960054996743614</v>
       </c>
       <c r="T39" t="n">
         <v>0</v>
@@ -4706,7 +4694,7 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>3.097185035096606</v>
       </c>
       <c r="Y39" t="n">
         <v>0</v>
@@ -4721,13 +4709,13 @@
         <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>0.003618206816701643</v>
       </c>
       <c r="AD39" t="n">
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>0.05782822874277147</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
         <v>0</v>
@@ -4743,16 +4731,16 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" t="n">
         <v>39</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>site_39</t>
+          <t>Site_39</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
@@ -4764,10 +4752,10 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0.07744339976524969</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
@@ -4788,10 +4776,10 @@
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>0.1899783400491282</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -4800,7 +4788,7 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0.001210053121332026</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -4836,7 +4824,7 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0.07260318727992159</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
         <v>0</v>
@@ -4852,19 +4840,19 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" t="n">
         <v>40</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>site_40</t>
+          <t>Site_40</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>0.008154478439559005</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
@@ -4876,7 +4864,7 @@
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>0.001630895687911801</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -4885,22 +4873,22 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>0.006523582751647205</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>0.04240328788570683</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>0.001630895687911801</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>0.06686672320438386</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -4912,34 +4900,34 @@
         <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>0.01467806119120621</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>0.009785374127470806</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>0.004892687063735403</v>
       </c>
       <c r="W41" t="n">
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>0.004892687063735403</v>
       </c>
       <c r="Y41" t="n">
         <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>0.009785374127470806</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>0.008154478439559005</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>0.008154478439559005</v>
       </c>
       <c r="AD41" t="n">
         <v>0</v>
@@ -4948,7 +4936,7 @@
         <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>0.006523582751647205</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -4961,19 +4949,19 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" t="n">
         <v>41</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>site_41</t>
+          <t>Site_41</t>
         </is>
       </c>
       <c r="C42" t="n">
         <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>0.003007609251406057</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -4985,19 +4973,19 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>0.03007609251406057</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>0.003007609251406057</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>0.06917501278233933</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -5009,10 +4997,10 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>0.003751359867952133</v>
+        <v>0.8631838551535385</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>0.006015218502812114</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -5021,7 +5009,7 @@
         <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>0.05413696652530903</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
@@ -5033,19 +5021,19 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>0.0210532647598424</v>
       </c>
       <c r="Y42" t="n">
         <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>0.007502719735904265</v>
+        <v>0.006015218502812114</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>0.006015218502812114</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5057,7 +5045,7 @@
         <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>0.006015218502812114</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -5070,12 +5058,12 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" t="n">
         <v>42</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>site_42</t>
+          <t>Site_42</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -5091,7 +5079,7 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>4.262914741705166</v>
+        <v>0.5443658138268916</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -5115,19 +5103,19 @@
         <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>1.007979840403192</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>0.02099958000839983</v>
+        <v>0.1088731627653783</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>0.326619488296135</v>
       </c>
       <c r="S43" t="n">
-        <v>0.1679966400671987</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -5139,13 +5127,13 @@
         <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>0.05443658138268917</v>
       </c>
       <c r="X43" t="n">
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.04199916001679967</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
         <v>0</v>
@@ -5157,13 +5145,13 @@
         <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>0.1633097441480675</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>0.05443658138268917</v>
       </c>
       <c r="AE43" t="n">
-        <v>0.2099958000839983</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
         <v>0</v>
@@ -5175,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="AI43" t="n">
-        <v>0.1679966400671987</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" t="n">
         <v>43</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>site_43</t>
+          <t>Site_43</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -5200,7 +5188,7 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0.04927079227433977</v>
+        <v>0.5632897836795887</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -5212,7 +5200,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>0.008567144998929107</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -5224,7 +5212,7 @@
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>0.1675206937327552</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
@@ -5236,7 +5224,7 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>0.02141786249732277</v>
       </c>
       <c r="T44" t="n">
         <v>0</v>
@@ -5254,7 +5242,7 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>0.01713428999785821</v>
       </c>
       <c r="Z44" t="n">
         <v>0</v>
@@ -5288,16 +5276,16 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" t="n">
         <v>44</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>site_44</t>
+          <t>Site_44</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
@@ -5309,7 +5297,7 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -5360,7 +5348,7 @@
         <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>0.004311273981461522</v>
       </c>
       <c r="Y45" t="n">
         <v>0</v>
@@ -5397,12 +5385,12 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" t="n">
         <v>45</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>site_45</t>
+          <t>Site_45</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -5430,10 +5418,10 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>0.03638470764213619</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>0.005456331162926049</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -5475,7 +5463,7 @@
         <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>0.001347581764523563</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -5487,7 +5475,7 @@
         <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>0.003637554108617366</v>
       </c>
       <c r="AE46" t="n">
         <v>0</v>
@@ -5499,19 +5487,19 @@
         <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>0.01273143938016078</v>
       </c>
       <c r="AI46" t="n">
-        <v>0.001347581764523563</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" t="n">
         <v>46</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>site_46</t>
+          <t>Site_46</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -5527,7 +5515,7 @@
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>0.09745037985760312</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -5554,7 +5542,7 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>0.004311273981461522</v>
+        <v>0.04773079829760152</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -5563,25 +5551,25 @@
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>0.01591026609920051</v>
       </c>
       <c r="T47" t="n">
         <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>0.005966349787200191</v>
       </c>
       <c r="V47" t="n">
         <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>0.003977566524800128</v>
       </c>
       <c r="X47" t="n">
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>0.02585418241120083</v>
       </c>
       <c r="Z47" t="n">
         <v>0</v>
@@ -5593,10 +5581,10 @@
         <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>0.001988783262400064</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>0.01193269957440038</v>
       </c>
       <c r="AE47" t="n">
         <v>0</v>
@@ -5615,28 +5603,28 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" t="n">
         <v>47</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>site_47</t>
+          <t>Site_47</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>0.01193269957440038</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>0.09745037985760312</v>
+        <v>0.07744339976524969</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -5648,19 +5636,19 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>0.005966349787200191</v>
+        <v>0.001210053121332026</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.001988783262400064</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>1.25293345531204</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
         <v>0</v>
@@ -5672,7 +5660,7 @@
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>0.02585418241120083</v>
+        <v>0.01210053121332027</v>
       </c>
       <c r="T48" t="n">
         <v>0</v>
@@ -5690,25 +5678,25 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>0.001210053121332026</v>
       </c>
       <c r="Z48" t="n">
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.003977566524800128</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
         <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>0.005966349787200191</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>0.5568593134720178</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
         <v>0</v>
@@ -5720,16 +5708,16 @@
         <v>0</v>
       </c>
       <c r="AI48" t="n">
-        <v>0.04773079829760152</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" t="n">
         <v>48</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>site_48</t>
+          <t>Site_48</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -5745,7 +5733,7 @@
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>0.1264400112391121</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -5769,7 +5757,7 @@
         <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>0.01404889013767912</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
         <v>0</v>
@@ -5796,7 +5784,7 @@
         <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>0.003751359867952133</v>
       </c>
       <c r="Y49" t="n">
         <v>0</v>
@@ -5833,16 +5821,16 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" t="n">
         <v>49</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>site_49</t>
+          <t>Site_49</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -5854,7 +5842,7 @@
         <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -5890,7 +5878,7 @@
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>0.01444669170759896</v>
       </c>
       <c r="T50" t="n">
         <v>0</v>
@@ -5942,12 +5930,12 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" t="n">
         <v>50</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>site_50</t>
+          <t>Site_50</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -5963,7 +5951,7 @@
         <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>0.04927079227433977</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -5972,7 +5960,7 @@
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>0.04099598670866957</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
@@ -6051,12 +6039,12 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" t="n">
         <v>51</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>site_51</t>
+          <t>Site_51</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -6066,7 +6054,7 @@
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>0.003637554108617366</v>
+        <v>0</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -6087,13 +6075,13 @@
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>0.005456331162926049</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>0.01273143938016078</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6108,7 +6096,7 @@
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>0.01622428450905315</v>
       </c>
       <c r="T52" t="n">
         <v>0</v>
@@ -6160,12 +6148,12 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" t="n">
         <v>52</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>site_52</t>
+          <t>Site_52</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -6184,7 +6172,7 @@
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0.0007963178263708611</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
@@ -6199,7 +6187,7 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>0.0003981589131854306</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
         <v>0</v>
@@ -6223,7 +6211,7 @@
         <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>0.264812975835816</v>
       </c>
       <c r="V53" t="n">
         <v>0</v>
@@ -6238,13 +6226,13 @@
         <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>0.0007963178263708611</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>0.0007963178263708611</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6265,16 +6253,16 @@
         <v>0</v>
       </c>
       <c r="AI53" t="n">
-        <v>0.001194476739556292</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" t="n">
         <v>53</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>site_53</t>
+          <t>Site_53</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -6290,7 +6278,7 @@
         <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>0.1264400112391121</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -6302,7 +6290,7 @@
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>0.264812975835816</v>
+        <v>0</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
@@ -6378,12 +6366,12 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" t="n">
         <v>54</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>site_54</t>
+          <t>Site_54</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -6423,10 +6411,10 @@
         <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>0.005725190839694656</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>0.001347581764523563</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -6441,7 +6429,7 @@
         <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>0.03638470764213619</v>
       </c>
       <c r="V55" t="n">
         <v>0</v>
@@ -6456,7 +6444,7 @@
         <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>0.001908396946564886</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -6487,16 +6475,16 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" t="n">
         <v>55</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>site_55</t>
+          <t>Site_55</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D56" t="n">
         <v>0</v>
@@ -6532,7 +6520,7 @@
         <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>0.003489305279318887</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
         <v>0</v>
@@ -6544,7 +6532,7 @@
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>0.4059147579008408</v>
       </c>
       <c r="T56" t="n">
         <v>0</v>
@@ -6565,7 +6553,7 @@
         <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>0.01744652639659444</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -6596,16 +6584,16 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" t="n">
         <v>56</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>site_56</t>
+          <t>Site_56</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D57" t="n">
         <v>0</v>
@@ -6629,19 +6617,19 @@
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>0.09247738507583145</v>
+        <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>0.03110602952550695</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>0.9390658102700339</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
         <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>0.01849547701516629</v>
+        <v>0</v>
       </c>
       <c r="P57" t="n">
         <v>0</v>
@@ -6653,7 +6641,7 @@
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>0.005725190839694656</v>
       </c>
       <c r="T57" t="n">
         <v>0</v>
@@ -6701,32 +6689,32 @@
         <v>0</v>
       </c>
       <c r="AI57" t="n">
-        <v>0.1723442176413222</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" t="n">
         <v>57</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>site_57</t>
+          <t>Site_57</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D58" t="n">
         <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>0.01542020046260601</v>
+        <v>0</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>0.06168080185042405</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -6735,7 +6723,7 @@
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>0.04626060138781804</v>
+        <v>0</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
@@ -6750,7 +6738,7 @@
         <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>0.2158828064764842</v>
+        <v>0</v>
       </c>
       <c r="P58" t="n">
         <v>0</v>
@@ -6762,7 +6750,7 @@
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>0.01542020046260601</v>
+        <v>0.006978610558637775</v>
       </c>
       <c r="T58" t="n">
         <v>0</v>
@@ -6780,25 +6768,25 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>0.01542020046260601</v>
+        <v>0</v>
       </c>
       <c r="Z58" t="n">
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0.01542020046260601</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
         <v>0</v>
       </c>
       <c r="AC58" t="n">
-        <v>0.07710100231303006</v>
+        <v>0</v>
       </c>
       <c r="AD58" t="n">
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>0.1233616037008481</v>
+        <v>0</v>
       </c>
       <c r="AF58" t="n">
         <v>0</v>
@@ -6810,20 +6798,20 @@
         <v>0</v>
       </c>
       <c r="AI58" t="n">
-        <v>1.264456437933693</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" t="n">
         <v>58</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>site_58</t>
+          <t>Site_58</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D59" t="n">
         <v>0</v>
@@ -6832,7 +6820,7 @@
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>0.01921229586935639</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -6850,40 +6838,40 @@
         <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>0.03110602952550695</v>
       </c>
       <c r="M59" t="n">
-        <v>3.150816522574448</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>0.01921229586935639</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>0.1536983669548511</v>
+        <v>0.1723442176413222</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.1152737752161383</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>0.1152737752161383</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>2.708933717579251</v>
+        <v>0.0008407035006893769</v>
       </c>
       <c r="T59" t="n">
         <v>0</v>
       </c>
       <c r="U59" t="n">
-        <v>0.07684918347742556</v>
+        <v>0.09247738507583145</v>
       </c>
       <c r="V59" t="n">
         <v>0</v>
       </c>
       <c r="W59" t="n">
-        <v>0.03842459173871278</v>
+        <v>0</v>
       </c>
       <c r="X59" t="n">
         <v>0</v>
@@ -6892,16 +6880,16 @@
         <v>0</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.325648414985591</v>
+        <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>8.93371757925072</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
         <v>0</v>
       </c>
       <c r="AC59" t="n">
-        <v>0</v>
+        <v>0.9390658102700339</v>
       </c>
       <c r="AD59" t="n">
         <v>0</v>
@@ -6919,20 +6907,20 @@
         <v>0</v>
       </c>
       <c r="AI59" t="n">
-        <v>1.364073006724304</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" t="n">
         <v>59</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>site_59</t>
+          <t>Site_59</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D60" t="n">
         <v>0</v>
@@ -6941,7 +6929,7 @@
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>0.02102091581123218</v>
+        <v>0</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -6950,67 +6938,67 @@
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>0.003503485968538696</v>
+        <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>0.02102091581123218</v>
+        <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>0.03503485968538696</v>
+        <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>0.05255228952808044</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.619101005500473</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>0.01051045790561609</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>0.04204183162246435</v>
+        <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>0.1331324668044704</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.2032021861752444</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>0.07006971937077391</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>3.051536278597204</v>
+        <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>0.003503485968538696</v>
+        <v>0</v>
       </c>
       <c r="U60" t="n">
-        <v>0.04204183162246435</v>
+        <v>0</v>
       </c>
       <c r="V60" t="n">
         <v>0</v>
       </c>
       <c r="W60" t="n">
-        <v>0.1086080650246996</v>
+        <v>0</v>
       </c>
       <c r="X60" t="n">
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>0.007006971937077392</v>
+        <v>0</v>
       </c>
       <c r="Z60" t="n">
-        <v>0.9459412115054479</v>
+        <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>10.57352065304979</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>0.1681673264898574</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
-        <v>0.007006971937077392</v>
+        <v>0</v>
       </c>
       <c r="AD60" t="n">
         <v>0</v>
@@ -7019,68 +7007,68 @@
         <v>0</v>
       </c>
       <c r="AF60" t="n">
-        <v>0.003503485968538696</v>
+        <v>0</v>
       </c>
       <c r="AG60" t="n">
-        <v>0.003503485968538696</v>
+        <v>0</v>
       </c>
       <c r="AH60" t="n">
         <v>0</v>
       </c>
       <c r="AI60" t="n">
-        <v>1.261254948673931</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" t="n">
         <v>60</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>site_60</t>
+          <t>Site_60</t>
         </is>
       </c>
       <c r="C61" t="n">
         <v>1</v>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>0.01921229586935639</v>
       </c>
       <c r="E61" t="n">
-        <v>0.005338268265774583</v>
+        <v>0</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>0.1334567066443646</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>0.03842459173871278</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>0.07684918347742556</v>
       </c>
       <c r="K61" t="n">
-        <v>0.003558845510516389</v>
+        <v>0.03842459173871278</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>0.005338268265774583</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
         <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>0.5195914445353927</v>
+        <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>0.003558845510516389</v>
+        <v>1.364073006724304</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -7089,7 +7077,7 @@
         <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>0.03380903234990569</v>
+        <v>0.09606147934678194</v>
       </c>
       <c r="T61" t="n">
         <v>0</v>
@@ -7098,55 +7086,55 @@
         <v>0</v>
       </c>
       <c r="V61" t="n">
-        <v>0</v>
+        <v>0.01921229586935639</v>
       </c>
       <c r="W61" t="n">
-        <v>0</v>
+        <v>8.93371757925072</v>
       </c>
       <c r="X61" t="n">
-        <v>0</v>
+        <v>0.1536983669548511</v>
       </c>
       <c r="Y61" t="n">
-        <v>0.005338268265774583</v>
+        <v>2.708933717579251</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>0.1152737752161383</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>0.1152737752161383</v>
       </c>
       <c r="AB61" t="n">
         <v>0</v>
       </c>
       <c r="AC61" t="n">
-        <v>0.003558845510516389</v>
+        <v>3.150816522574448</v>
       </c>
       <c r="AD61" t="n">
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>0.09786825153920069</v>
+        <v>0</v>
       </c>
       <c r="AF61" t="n">
         <v>0</v>
       </c>
       <c r="AG61" t="n">
-        <v>0</v>
+        <v>0.01921229586935639</v>
       </c>
       <c r="AH61" t="n">
-        <v>0</v>
+        <v>0.01921229586935639</v>
       </c>
       <c r="AI61" t="n">
-        <v>0.05872095092352041</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" t="n">
         <v>61</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>site_61</t>
+          <t>Site_61</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -7159,20 +7147,20 @@
         <v>0</v>
       </c>
       <c r="F62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
         <v>0.05578281889178133</v>
       </c>
-      <c r="G62" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" t="n">
-        <v>0</v>
-      </c>
       <c r="K62" t="n">
         <v>0</v>
       </c>
@@ -7180,82 +7168,82 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
+        <v>0.03718854592785422</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0.05578281889178133</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0.3904797322424693</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0.1115656377835627</v>
+      </c>
+      <c r="T62" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W62" t="n">
+        <v>0.7809594644849386</v>
+      </c>
+      <c r="X62" t="n">
+        <v>0.03718854592785422</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>0.2789140944589066</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>0.1115656377835627</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC62" t="n">
         <v>0.3161026403867608</v>
       </c>
-      <c r="N62" t="n">
+      <c r="AD62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="n">
+        <v>0.05578281889178133</v>
+      </c>
+      <c r="AH62" t="n">
         <v>0.01859427296392711</v>
       </c>
-      <c r="O62" t="n">
-        <v>0</v>
-      </c>
-      <c r="P62" t="n">
-        <v>0.03718854592785422</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
-      <c r="R62" t="n">
-        <v>0.1115656377835627</v>
-      </c>
-      <c r="S62" t="n">
-        <v>0.2789140944589066</v>
-      </c>
-      <c r="T62" t="n">
-        <v>0.03718854592785422</v>
-      </c>
-      <c r="U62" t="n">
-        <v>0.05578281889178133</v>
-      </c>
-      <c r="V62" t="n">
-        <v>0</v>
-      </c>
-      <c r="W62" t="n">
-        <v>0</v>
-      </c>
-      <c r="X62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z62" t="n">
-        <v>0.2975083674228338</v>
-      </c>
-      <c r="AA62" t="n">
-        <v>0.7809594644849386</v>
-      </c>
-      <c r="AB62" t="n">
-        <v>0.05578281889178133</v>
-      </c>
-      <c r="AC62" t="n">
-        <v>0.07437709185570844</v>
-      </c>
-      <c r="AD62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH62" t="n">
-        <v>0</v>
-      </c>
       <c r="AI62" t="n">
-        <v>0.3904797322424693</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" t="n">
         <v>62</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>site_62</t>
+          <t>Site_62</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -7268,76 +7256,76 @@
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>0.02616659398168339</v>
+        <v>0</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>0.02311604253351826</v>
       </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
+        <v>0.02311604253351826</v>
       </c>
       <c r="K63" t="n">
-        <v>0.00436109899694723</v>
+        <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>0.00436109899694723</v>
+        <v>0.02311604253351826</v>
       </c>
       <c r="M63" t="n">
-        <v>0.4491931966855648</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
         <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>0.00436109899694723</v>
+        <v>0.1618122977346279</v>
       </c>
       <c r="P63" t="n">
-        <v>0.07849978194505015</v>
+        <v>0.6472491909385114</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.02616659398168339</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>0.01308329699084169</v>
+        <v>0.04623208506703652</v>
       </c>
       <c r="S63" t="n">
-        <v>0.3576101177496729</v>
+        <v>0.04623208506703652</v>
       </c>
       <c r="T63" t="n">
-        <v>0.00436109899694723</v>
+        <v>0</v>
       </c>
       <c r="U63" t="n">
-        <v>0.01308329699084169</v>
+        <v>0.02311604253351826</v>
       </c>
       <c r="V63" t="n">
         <v>0</v>
       </c>
       <c r="W63" t="n">
-        <v>0.04797208896641954</v>
+        <v>1.363846509477578</v>
       </c>
       <c r="X63" t="n">
-        <v>0</v>
+        <v>0.1386962552011096</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>0.4160887656033287</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.142607937200175</v>
+        <v>0.02311604253351826</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.626689925861317</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>0.06541648495420846</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
-        <v>0.008722197993894461</v>
+        <v>0.3929727230698105</v>
       </c>
       <c r="AD63" t="n">
         <v>0</v>
@@ -7349,22 +7337,22 @@
         <v>0</v>
       </c>
       <c r="AG63" t="n">
-        <v>0</v>
+        <v>0.04623208506703652</v>
       </c>
       <c r="AH63" t="n">
         <v>0</v>
       </c>
       <c r="AI63" t="n">
-        <v>0.5276929786306149</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" t="n">
         <v>63</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>site_63</t>
+          <t>Site_63</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -7377,76 +7365,76 @@
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>0.04623208506703652</v>
+        <v>0</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>0.04797208896641954</v>
       </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>0.01308329699084169</v>
       </c>
       <c r="K64" t="n">
-        <v>0.02311604253351826</v>
+        <v>0.01308329699084169</v>
       </c>
       <c r="L64" t="n">
-        <v>0.02311604253351826</v>
+        <v>0.00436109899694723</v>
       </c>
       <c r="M64" t="n">
-        <v>0.3929727230698105</v>
+        <v>0.00436109899694723</v>
       </c>
       <c r="N64" t="n">
         <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>0.06541648495420846</v>
       </c>
       <c r="P64" t="n">
-        <v>0.1386962552011096</v>
+        <v>0.5276929786306149</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>0.02311604253351826</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>0.4160887656033287</v>
+        <v>0.01744439598778892</v>
       </c>
       <c r="T64" t="n">
         <v>0</v>
       </c>
       <c r="U64" t="n">
-        <v>0.02311604253351826</v>
+        <v>0.00436109899694723</v>
       </c>
       <c r="V64" t="n">
-        <v>0</v>
+        <v>0.008722197993894461</v>
       </c>
       <c r="W64" t="n">
-        <v>0.02311604253351826</v>
+        <v>1.626689925861317</v>
       </c>
       <c r="X64" t="n">
-        <v>0</v>
+        <v>0.07849978194505015</v>
       </c>
       <c r="Y64" t="n">
-        <v>0.04623208506703652</v>
+        <v>0.3576101177496729</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.109570041608877</v>
+        <v>0.01308329699084169</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.363846509477578</v>
+        <v>0.02616659398168339</v>
       </c>
       <c r="AB64" t="n">
-        <v>0.1618122977346279</v>
+        <v>0.00436109899694723</v>
       </c>
       <c r="AC64" t="n">
-        <v>0</v>
+        <v>0.4491931966855648</v>
       </c>
       <c r="AD64" t="n">
         <v>0</v>
@@ -7458,32 +7446,32 @@
         <v>0</v>
       </c>
       <c r="AG64" t="n">
-        <v>0</v>
+        <v>0.02616659398168339</v>
       </c>
       <c r="AH64" t="n">
         <v>0</v>
       </c>
       <c r="AI64" t="n">
-        <v>0.6472491909385114</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" t="n">
         <v>64</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>site_64</t>
+          <t>Site_64</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D65" t="n">
-        <v>0</v>
+        <v>0.01051045790561609</v>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>0.003503485968538696</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -7492,70 +7480,70 @@
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>0.1086080650246996</v>
       </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>0</v>
+        <v>0.04204183162246435</v>
       </c>
       <c r="K65" t="n">
-        <v>0</v>
+        <v>0.003503485968538696</v>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>0.05255228952808044</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>0.003503485968538696</v>
       </c>
       <c r="N65" t="n">
         <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>0</v>
+        <v>0.1681673264898574</v>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>1.261254948673931</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>0.02102091581123218</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>0.007006971937077392</v>
       </c>
       <c r="S65" t="n">
-        <v>0</v>
+        <v>0.02802788774830957</v>
       </c>
       <c r="T65" t="n">
-        <v>0</v>
+        <v>0.007006971937077392</v>
       </c>
       <c r="U65" t="n">
-        <v>0</v>
+        <v>0.03503485968538696</v>
       </c>
       <c r="V65" t="n">
-        <v>0</v>
+        <v>0.01751742984269348</v>
       </c>
       <c r="W65" t="n">
-        <v>0</v>
+        <v>10.57352065304979</v>
       </c>
       <c r="X65" t="n">
-        <v>0</v>
+        <v>0.1331324668044704</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>3.051536278597204</v>
       </c>
       <c r="Z65" t="n">
-        <v>7.76</v>
+        <v>0.07006971937077391</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>0.2032021861752444</v>
       </c>
       <c r="AB65" t="n">
         <v>0</v>
       </c>
       <c r="AC65" t="n">
-        <v>0</v>
+        <v>3.619101005500473</v>
       </c>
       <c r="AD65" t="n">
         <v>0</v>
@@ -7564,41 +7552,41 @@
         <v>0</v>
       </c>
       <c r="AF65" t="n">
-        <v>0</v>
+        <v>0.003503485968538696</v>
       </c>
       <c r="AG65" t="n">
-        <v>0</v>
+        <v>0.02102091581123218</v>
       </c>
       <c r="AH65" t="n">
-        <v>0</v>
+        <v>0.01051045790561609</v>
       </c>
       <c r="AI65" t="n">
-        <v>0</v>
+        <v>0.003503485968538696</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" t="n">
         <v>65</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>site_65</t>
+          <t>Site_65</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D66" t="n">
         <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>0.05443658138268917</v>
+        <v>0</v>
       </c>
       <c r="F66" t="n">
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>0.5443658138268916</v>
+        <v>0.1334567066443646</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -7616,22 +7604,22 @@
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>0.1633097441480675</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
         <v>0</v>
       </c>
       <c r="O66" t="n">
-        <v>0.2721829069134458</v>
+        <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>0.05872095092352041</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>0.005338268265774583</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -7640,37 +7628,37 @@
         <v>0</v>
       </c>
       <c r="U66" t="n">
-        <v>0</v>
+        <v>0.003558845510516389</v>
       </c>
       <c r="V66" t="n">
-        <v>0</v>
+        <v>0.001779422755258194</v>
       </c>
       <c r="W66" t="n">
         <v>0</v>
       </c>
       <c r="X66" t="n">
-        <v>0</v>
+        <v>0.003558845510516389</v>
       </c>
       <c r="Y66" t="n">
-        <v>0.326619488296135</v>
+        <v>0.03380903234990569</v>
       </c>
       <c r="Z66" t="n">
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>0.05443658138268917</v>
+        <v>0</v>
       </c>
       <c r="AB66" t="n">
         <v>0</v>
       </c>
       <c r="AC66" t="n">
-        <v>0.05443658138268917</v>
+        <v>0.005338268265774583</v>
       </c>
       <c r="AD66" t="n">
-        <v>0</v>
+        <v>0.005338268265774583</v>
       </c>
       <c r="AE66" t="n">
-        <v>0.1633097441480675</v>
+        <v>0</v>
       </c>
       <c r="AF66" t="n">
         <v>0</v>
@@ -7682,20 +7670,20 @@
         <v>0</v>
       </c>
       <c r="AI66" t="n">
-        <v>0.1088731627653783</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" t="n">
         <v>66</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>site_66</t>
+          <t>Site_66</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D67" t="n">
         <v>0</v>
@@ -7707,7 +7695,7 @@
         <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>0.06168080185042405</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -7734,13 +7722,13 @@
         <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>1.264456437933693</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>0.04626060138781804</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>0.01542020046260601</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -7755,16 +7743,16 @@
         <v>0</v>
       </c>
       <c r="W67" t="n">
-        <v>0</v>
+        <v>0.01542020046260601</v>
       </c>
       <c r="X67" t="n">
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>0</v>
+        <v>0.01542020046260601</v>
       </c>
       <c r="Z67" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -7776,7 +7764,7 @@
         <v>0</v>
       </c>
       <c r="AD67" t="n">
-        <v>0</v>
+        <v>0.01542020046260601</v>
       </c>
       <c r="AE67" t="n">
         <v>0</v>
@@ -7795,12 +7783,12 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" t="n">
         <v>67</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>site_67</t>
+          <t>Site_67</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -7816,7 +7804,7 @@
         <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -7861,7 +7849,7 @@
         <v>0</v>
       </c>
       <c r="V68" t="n">
-        <v>0.01465702560093805</v>
+        <v>0</v>
       </c>
       <c r="W68" t="n">
         <v>0</v>
@@ -7873,7 +7861,7 @@
         <v>0</v>
       </c>
       <c r="Z68" t="n">
-        <v>0.0293140512018761</v>
+        <v>0</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -7882,7 +7870,7 @@
         <v>0</v>
       </c>
       <c r="AC68" t="n">
-        <v>0.05374242720343951</v>
+        <v>0</v>
       </c>
       <c r="AD68" t="n">
         <v>0</v>
@@ -7904,12 +7892,12 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" t="n">
         <v>68</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>site_68</t>
+          <t>Site_68</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -7919,13 +7907,13 @@
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>0.02117186259461176</v>
+        <v>0</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -7934,7 +7922,7 @@
         <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>0.005292965648652941</v>
+        <v>0</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
@@ -7970,7 +7958,7 @@
         <v>0</v>
       </c>
       <c r="V69" t="n">
-        <v>0.01058593129730588</v>
+        <v>0</v>
       </c>
       <c r="W69" t="n">
         <v>0</v>
@@ -7991,7 +7979,7 @@
         <v>0</v>
       </c>
       <c r="AC69" t="n">
-        <v>0.6298629121896998</v>
+        <v>0</v>
       </c>
       <c r="AD69" t="n">
         <v>0</v>
@@ -8013,16 +8001,16 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" t="n">
         <v>69</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>site_69</t>
+          <t>Site_69</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D70" t="n">
         <v>0</v>
@@ -8079,7 +8067,7 @@
         <v>0</v>
       </c>
       <c r="V70" t="n">
-        <v>0</v>
+        <v>0.004885675200312683</v>
       </c>
       <c r="W70" t="n">
         <v>0</v>
@@ -8091,13 +8079,13 @@
         <v>0</v>
       </c>
       <c r="Z70" t="n">
-        <v>5.23</v>
+        <v>0</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>0.004885675200312683</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8106,7 +8094,7 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>0</v>
+        <v>0.01465702560093805</v>
       </c>
       <c r="AF70" t="n">
         <v>0</v>
@@ -8118,20 +8106,20 @@
         <v>0</v>
       </c>
       <c r="AI70" t="n">
-        <v>5.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" t="n">
         <v>70</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>site_70</t>
+          <t>Site_70</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D71" t="n">
         <v>0</v>
@@ -8173,7 +8161,7 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>0.005292965648652941</v>
       </c>
       <c r="R71" t="n">
         <v>0</v>
@@ -8191,7 +8179,7 @@
         <v>0</v>
       </c>
       <c r="W71" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="X71" t="n">
         <v>0</v>
@@ -8206,16 +8194,16 @@
         <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>0.01058593129730588</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
       </c>
       <c r="AD71" t="n">
-        <v>0</v>
+        <v>0.02117186259461176</v>
       </c>
       <c r="AE71" t="n">
-        <v>0</v>
+        <v>0.01058593129730588</v>
       </c>
       <c r="AF71" t="n">
         <v>0</v>
@@ -8227,7 +8215,7 @@
         <v>0</v>
       </c>
       <c r="AI71" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
